--- a/機能設計書/DB設計書.xlsx
+++ b/機能設計書/DB設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\藤田\Desktop\FileManagementSystem_Doc\機能設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FileManagementSystem_Doc\機能設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B947D0E-29BD-4323-98A0-F450DD7C5FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C269131E-2CDD-47EF-B5F4-DEED4D41CE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-10410" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="10" r:id="rId1"/>
@@ -20,27 +20,29 @@
     <sheet name="ファイル管理" sheetId="14" r:id="rId5"/>
     <sheet name="会議参加者" sheetId="20" r:id="rId6"/>
     <sheet name="ユーザーマスタ" sheetId="15" r:id="rId7"/>
-    <sheet name="所属管理マスタ" sheetId="21" r:id="rId8"/>
-    <sheet name="所属マスタ" sheetId="16" r:id="rId9"/>
-    <sheet name="役職マスタ " sheetId="17" r:id="rId10"/>
-    <sheet name="ログ" sheetId="18" r:id="rId11"/>
-    <sheet name="排他ロック" sheetId="24" r:id="rId12"/>
+    <sheet name="外部ユーザーマスタ" sheetId="25" r:id="rId8"/>
+    <sheet name="所属管理マスタ" sheetId="21" r:id="rId9"/>
+    <sheet name="所属マスタ" sheetId="16" r:id="rId10"/>
+    <sheet name="役職マスタ " sheetId="17" r:id="rId11"/>
+    <sheet name="ログ" sheetId="18" r:id="rId12"/>
+    <sheet name="排他ロック" sheetId="24" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">DB一覧!$A$1:$AN$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">DB規約!$A$1:$AN$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">ファイル管理!$A$1:$AN$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">ユーザーマスタ!$A$1:$AN$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">ログ!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">ログ!$A$1:$AN$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">会議参加者!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">外部ユーザーマスタ!$A$1:$AN$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">更新履歴!$A$1:$AN$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">所属マスタ!$A$1:$AN$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">所属管理マスタ!$A$1:$AN$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">排他ロック!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">所属マスタ!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">所属管理マスタ!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">排他ロック!$A$1:$AN$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$AN$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'役職マスタ '!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'役職マスタ '!$A$1:$AN$33</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="178">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -1088,23 +1090,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>会議時間(to)</t>
-    <rPh sb="0" eb="2">
-      <t>カイギ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジカン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>会議時間(from)</t>
-    <rPh sb="0" eb="4">
-      <t>カイギジカン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>time</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1125,6 +1110,43 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外部ユーザーマスタ(m_external_user)</t>
+    <rPh sb="0" eb="2">
+      <t>ガイブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外部ユーザーのため所属マスタにおけるIDは「10:組織に属さない」となる</t>
+    <rPh sb="0" eb="2">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショゾク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>時間自</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>時間至</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イタル</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1850,6 +1872,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1976,6 +2007,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1985,35 +2028,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2265,271 +2287,271 @@
     <row r="7" spans="2:31" ht="14.1" customHeight="1"/>
     <row r="8" spans="2:31" ht="14.1" customHeight="1" thickBot="1"/>
     <row r="9" spans="2:31" ht="14.1" customHeight="1" thickTop="1">
-      <c r="J9" s="116" t="s">
+      <c r="J9" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="117"/>
-      <c r="O9" s="117"/>
-      <c r="P9" s="117"/>
-      <c r="Q9" s="117"/>
-      <c r="R9" s="117"/>
-      <c r="S9" s="117"/>
-      <c r="T9" s="117"/>
-      <c r="U9" s="117"/>
-      <c r="V9" s="117"/>
-      <c r="W9" s="117"/>
-      <c r="X9" s="117"/>
-      <c r="Y9" s="117"/>
-      <c r="Z9" s="117"/>
-      <c r="AA9" s="117"/>
-      <c r="AB9" s="117"/>
-      <c r="AC9" s="117"/>
-      <c r="AD9" s="117"/>
-      <c r="AE9" s="118"/>
+      <c r="K9" s="120"/>
+      <c r="L9" s="120"/>
+      <c r="M9" s="120"/>
+      <c r="N9" s="120"/>
+      <c r="O9" s="120"/>
+      <c r="P9" s="120"/>
+      <c r="Q9" s="120"/>
+      <c r="R9" s="120"/>
+      <c r="S9" s="120"/>
+      <c r="T9" s="120"/>
+      <c r="U9" s="120"/>
+      <c r="V9" s="120"/>
+      <c r="W9" s="120"/>
+      <c r="X9" s="120"/>
+      <c r="Y9" s="120"/>
+      <c r="Z9" s="120"/>
+      <c r="AA9" s="120"/>
+      <c r="AB9" s="120"/>
+      <c r="AC9" s="120"/>
+      <c r="AD9" s="120"/>
+      <c r="AE9" s="121"/>
     </row>
     <row r="10" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J10" s="119"/>
-      <c r="K10" s="120"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="120"/>
-      <c r="P10" s="120"/>
-      <c r="Q10" s="120"/>
-      <c r="R10" s="120"/>
-      <c r="S10" s="120"/>
-      <c r="T10" s="120"/>
-      <c r="U10" s="120"/>
-      <c r="V10" s="120"/>
-      <c r="W10" s="120"/>
-      <c r="X10" s="120"/>
-      <c r="Y10" s="120"/>
-      <c r="Z10" s="120"/>
-      <c r="AA10" s="120"/>
-      <c r="AB10" s="120"/>
-      <c r="AC10" s="120"/>
-      <c r="AD10" s="120"/>
-      <c r="AE10" s="121"/>
+      <c r="J10" s="122"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="123"/>
+      <c r="M10" s="123"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="123"/>
+      <c r="Q10" s="123"/>
+      <c r="R10" s="123"/>
+      <c r="S10" s="123"/>
+      <c r="T10" s="123"/>
+      <c r="U10" s="123"/>
+      <c r="V10" s="123"/>
+      <c r="W10" s="123"/>
+      <c r="X10" s="123"/>
+      <c r="Y10" s="123"/>
+      <c r="Z10" s="123"/>
+      <c r="AA10" s="123"/>
+      <c r="AB10" s="123"/>
+      <c r="AC10" s="123"/>
+      <c r="AD10" s="123"/>
+      <c r="AE10" s="124"/>
     </row>
     <row r="11" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J11" s="119"/>
-      <c r="K11" s="120"/>
-      <c r="L11" s="120"/>
-      <c r="M11" s="120"/>
-      <c r="N11" s="120"/>
-      <c r="O11" s="120"/>
-      <c r="P11" s="120"/>
-      <c r="Q11" s="120"/>
-      <c r="R11" s="120"/>
-      <c r="S11" s="120"/>
-      <c r="T11" s="120"/>
-      <c r="U11" s="120"/>
-      <c r="V11" s="120"/>
-      <c r="W11" s="120"/>
-      <c r="X11" s="120"/>
-      <c r="Y11" s="120"/>
-      <c r="Z11" s="120"/>
-      <c r="AA11" s="120"/>
-      <c r="AB11" s="120"/>
-      <c r="AC11" s="120"/>
-      <c r="AD11" s="120"/>
-      <c r="AE11" s="121"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="123"/>
+      <c r="M11" s="123"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="123"/>
+      <c r="R11" s="123"/>
+      <c r="S11" s="123"/>
+      <c r="T11" s="123"/>
+      <c r="U11" s="123"/>
+      <c r="V11" s="123"/>
+      <c r="W11" s="123"/>
+      <c r="X11" s="123"/>
+      <c r="Y11" s="123"/>
+      <c r="Z11" s="123"/>
+      <c r="AA11" s="123"/>
+      <c r="AB11" s="123"/>
+      <c r="AC11" s="123"/>
+      <c r="AD11" s="123"/>
+      <c r="AE11" s="124"/>
     </row>
     <row r="12" spans="2:31" ht="14.1" customHeight="1">
       <c r="B12" s="3"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="120"/>
-      <c r="L12" s="120"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="120"/>
-      <c r="P12" s="120"/>
-      <c r="Q12" s="120"/>
-      <c r="R12" s="120"/>
-      <c r="S12" s="120"/>
-      <c r="T12" s="120"/>
-      <c r="U12" s="120"/>
-      <c r="V12" s="120"/>
-      <c r="W12" s="120"/>
-      <c r="X12" s="120"/>
-      <c r="Y12" s="120"/>
-      <c r="Z12" s="120"/>
-      <c r="AA12" s="120"/>
-      <c r="AB12" s="120"/>
-      <c r="AC12" s="120"/>
-      <c r="AD12" s="120"/>
-      <c r="AE12" s="121"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="123"/>
+      <c r="N12" s="123"/>
+      <c r="O12" s="123"/>
+      <c r="P12" s="123"/>
+      <c r="Q12" s="123"/>
+      <c r="R12" s="123"/>
+      <c r="S12" s="123"/>
+      <c r="T12" s="123"/>
+      <c r="U12" s="123"/>
+      <c r="V12" s="123"/>
+      <c r="W12" s="123"/>
+      <c r="X12" s="123"/>
+      <c r="Y12" s="123"/>
+      <c r="Z12" s="123"/>
+      <c r="AA12" s="123"/>
+      <c r="AB12" s="123"/>
+      <c r="AC12" s="123"/>
+      <c r="AD12" s="123"/>
+      <c r="AE12" s="124"/>
     </row>
     <row r="13" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J13" s="119"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="120"/>
-      <c r="Q13" s="120"/>
-      <c r="R13" s="120"/>
-      <c r="S13" s="120"/>
-      <c r="T13" s="120"/>
-      <c r="U13" s="120"/>
-      <c r="V13" s="120"/>
-      <c r="W13" s="120"/>
-      <c r="X13" s="120"/>
-      <c r="Y13" s="120"/>
-      <c r="Z13" s="120"/>
-      <c r="AA13" s="120"/>
-      <c r="AB13" s="120"/>
-      <c r="AC13" s="120"/>
-      <c r="AD13" s="120"/>
-      <c r="AE13" s="121"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="123"/>
+      <c r="M13" s="123"/>
+      <c r="N13" s="123"/>
+      <c r="O13" s="123"/>
+      <c r="P13" s="123"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="123"/>
+      <c r="S13" s="123"/>
+      <c r="T13" s="123"/>
+      <c r="U13" s="123"/>
+      <c r="V13" s="123"/>
+      <c r="W13" s="123"/>
+      <c r="X13" s="123"/>
+      <c r="Y13" s="123"/>
+      <c r="Z13" s="123"/>
+      <c r="AA13" s="123"/>
+      <c r="AB13" s="123"/>
+      <c r="AC13" s="123"/>
+      <c r="AD13" s="123"/>
+      <c r="AE13" s="124"/>
     </row>
     <row r="14" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J14" s="119"/>
-      <c r="K14" s="120"/>
-      <c r="L14" s="120"/>
-      <c r="M14" s="120"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="120"/>
-      <c r="P14" s="120"/>
-      <c r="Q14" s="120"/>
-      <c r="R14" s="120"/>
-      <c r="S14" s="120"/>
-      <c r="T14" s="120"/>
-      <c r="U14" s="120"/>
-      <c r="V14" s="120"/>
-      <c r="W14" s="120"/>
-      <c r="X14" s="120"/>
-      <c r="Y14" s="120"/>
-      <c r="Z14" s="120"/>
-      <c r="AA14" s="120"/>
-      <c r="AB14" s="120"/>
-      <c r="AC14" s="120"/>
-      <c r="AD14" s="120"/>
-      <c r="AE14" s="121"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="123"/>
+      <c r="L14" s="123"/>
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="123"/>
+      <c r="R14" s="123"/>
+      <c r="S14" s="123"/>
+      <c r="T14" s="123"/>
+      <c r="U14" s="123"/>
+      <c r="V14" s="123"/>
+      <c r="W14" s="123"/>
+      <c r="X14" s="123"/>
+      <c r="Y14" s="123"/>
+      <c r="Z14" s="123"/>
+      <c r="AA14" s="123"/>
+      <c r="AB14" s="123"/>
+      <c r="AC14" s="123"/>
+      <c r="AD14" s="123"/>
+      <c r="AE14" s="124"/>
     </row>
     <row r="15" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J15" s="119"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="120"/>
-      <c r="P15" s="120"/>
-      <c r="Q15" s="120"/>
-      <c r="R15" s="120"/>
-      <c r="S15" s="120"/>
-      <c r="T15" s="120"/>
-      <c r="U15" s="120"/>
-      <c r="V15" s="120"/>
-      <c r="W15" s="120"/>
-      <c r="X15" s="120"/>
-      <c r="Y15" s="120"/>
-      <c r="Z15" s="120"/>
-      <c r="AA15" s="120"/>
-      <c r="AB15" s="120"/>
-      <c r="AC15" s="120"/>
-      <c r="AD15" s="120"/>
-      <c r="AE15" s="121"/>
+      <c r="J15" s="122"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="123"/>
+      <c r="M15" s="123"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="123"/>
+      <c r="S15" s="123"/>
+      <c r="T15" s="123"/>
+      <c r="U15" s="123"/>
+      <c r="V15" s="123"/>
+      <c r="W15" s="123"/>
+      <c r="X15" s="123"/>
+      <c r="Y15" s="123"/>
+      <c r="Z15" s="123"/>
+      <c r="AA15" s="123"/>
+      <c r="AB15" s="123"/>
+      <c r="AC15" s="123"/>
+      <c r="AD15" s="123"/>
+      <c r="AE15" s="124"/>
     </row>
     <row r="16" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J16" s="119"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="120"/>
-      <c r="P16" s="120"/>
-      <c r="Q16" s="120"/>
-      <c r="R16" s="120"/>
-      <c r="S16" s="120"/>
-      <c r="T16" s="120"/>
-      <c r="U16" s="120"/>
-      <c r="V16" s="120"/>
-      <c r="W16" s="120"/>
-      <c r="X16" s="120"/>
-      <c r="Y16" s="120"/>
-      <c r="Z16" s="120"/>
-      <c r="AA16" s="120"/>
-      <c r="AB16" s="120"/>
-      <c r="AC16" s="120"/>
-      <c r="AD16" s="120"/>
-      <c r="AE16" s="121"/>
+      <c r="J16" s="122"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
+      <c r="M16" s="123"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="123"/>
+      <c r="P16" s="123"/>
+      <c r="Q16" s="123"/>
+      <c r="R16" s="123"/>
+      <c r="S16" s="123"/>
+      <c r="T16" s="123"/>
+      <c r="U16" s="123"/>
+      <c r="V16" s="123"/>
+      <c r="W16" s="123"/>
+      <c r="X16" s="123"/>
+      <c r="Y16" s="123"/>
+      <c r="Z16" s="123"/>
+      <c r="AA16" s="123"/>
+      <c r="AB16" s="123"/>
+      <c r="AC16" s="123"/>
+      <c r="AD16" s="123"/>
+      <c r="AE16" s="124"/>
     </row>
     <row r="17" spans="6:31" ht="14.1" customHeight="1">
-      <c r="J17" s="119"/>
-      <c r="K17" s="120"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="120"/>
-      <c r="O17" s="120"/>
-      <c r="P17" s="120"/>
-      <c r="Q17" s="120"/>
-      <c r="R17" s="120"/>
-      <c r="S17" s="120"/>
-      <c r="T17" s="120"/>
-      <c r="U17" s="120"/>
-      <c r="V17" s="120"/>
-      <c r="W17" s="120"/>
-      <c r="X17" s="120"/>
-      <c r="Y17" s="120"/>
-      <c r="Z17" s="120"/>
-      <c r="AA17" s="120"/>
-      <c r="AB17" s="120"/>
-      <c r="AC17" s="120"/>
-      <c r="AD17" s="120"/>
-      <c r="AE17" s="121"/>
+      <c r="J17" s="122"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="123"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="123"/>
+      <c r="R17" s="123"/>
+      <c r="S17" s="123"/>
+      <c r="T17" s="123"/>
+      <c r="U17" s="123"/>
+      <c r="V17" s="123"/>
+      <c r="W17" s="123"/>
+      <c r="X17" s="123"/>
+      <c r="Y17" s="123"/>
+      <c r="Z17" s="123"/>
+      <c r="AA17" s="123"/>
+      <c r="AB17" s="123"/>
+      <c r="AC17" s="123"/>
+      <c r="AD17" s="123"/>
+      <c r="AE17" s="124"/>
     </row>
     <row r="18" spans="6:31" ht="14.1" customHeight="1">
-      <c r="J18" s="119"/>
-      <c r="K18" s="120"/>
-      <c r="L18" s="120"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="120"/>
-      <c r="O18" s="120"/>
-      <c r="P18" s="120"/>
-      <c r="Q18" s="120"/>
-      <c r="R18" s="120"/>
-      <c r="S18" s="120"/>
-      <c r="T18" s="120"/>
-      <c r="U18" s="120"/>
-      <c r="V18" s="120"/>
-      <c r="W18" s="120"/>
-      <c r="X18" s="120"/>
-      <c r="Y18" s="120"/>
-      <c r="Z18" s="120"/>
-      <c r="AA18" s="120"/>
-      <c r="AB18" s="120"/>
-      <c r="AC18" s="120"/>
-      <c r="AD18" s="120"/>
-      <c r="AE18" s="121"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="123"/>
+      <c r="R18" s="123"/>
+      <c r="S18" s="123"/>
+      <c r="T18" s="123"/>
+      <c r="U18" s="123"/>
+      <c r="V18" s="123"/>
+      <c r="W18" s="123"/>
+      <c r="X18" s="123"/>
+      <c r="Y18" s="123"/>
+      <c r="Z18" s="123"/>
+      <c r="AA18" s="123"/>
+      <c r="AB18" s="123"/>
+      <c r="AC18" s="123"/>
+      <c r="AD18" s="123"/>
+      <c r="AE18" s="124"/>
     </row>
     <row r="19" spans="6:31" ht="14.1" customHeight="1" thickBot="1">
-      <c r="J19" s="122"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="123"/>
-      <c r="M19" s="123"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="123"/>
-      <c r="P19" s="123"/>
-      <c r="Q19" s="123"/>
-      <c r="R19" s="123"/>
-      <c r="S19" s="123"/>
-      <c r="T19" s="123"/>
-      <c r="U19" s="123"/>
-      <c r="V19" s="123"/>
-      <c r="W19" s="123"/>
-      <c r="X19" s="123"/>
-      <c r="Y19" s="123"/>
-      <c r="Z19" s="123"/>
-      <c r="AA19" s="123"/>
-      <c r="AB19" s="123"/>
-      <c r="AC19" s="123"/>
-      <c r="AD19" s="123"/>
-      <c r="AE19" s="124"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="126"/>
+      <c r="S19" s="126"/>
+      <c r="T19" s="126"/>
+      <c r="U19" s="126"/>
+      <c r="V19" s="126"/>
+      <c r="W19" s="126"/>
+      <c r="X19" s="126"/>
+      <c r="Y19" s="126"/>
+      <c r="Z19" s="126"/>
+      <c r="AA19" s="126"/>
+      <c r="AB19" s="126"/>
+      <c r="AC19" s="126"/>
+      <c r="AD19" s="126"/>
+      <c r="AE19" s="127"/>
     </row>
     <row r="20" spans="6:31" ht="14.1" customHeight="1" thickTop="1"/>
     <row r="21" spans="6:31" ht="14.1" customHeight="1">
@@ -2567,14 +2589,14 @@
       </c>
       <c r="S23" s="9"/>
       <c r="T23" s="9"/>
-      <c r="U23" s="125">
+      <c r="U23" s="128">
         <f>MAX(更新履歴!I6:N27)</f>
         <v>46086</v>
       </c>
-      <c r="V23" s="125"/>
-      <c r="W23" s="125"/>
-      <c r="X23" s="125"/>
-      <c r="Y23" s="125"/>
+      <c r="V23" s="128"/>
+      <c r="W23" s="128"/>
+      <c r="X23" s="128"/>
+      <c r="Y23" s="128"/>
       <c r="Z23" s="11"/>
       <c r="AA23" s="4"/>
     </row>
@@ -2598,77 +2620,77 @@
     <row r="25" spans="6:31" ht="14.1" customHeight="1">
       <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="126" t="s">
+      <c r="O25" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="127"/>
-      <c r="R25" s="128"/>
-      <c r="S25" s="126" t="s">
+      <c r="P25" s="130"/>
+      <c r="Q25" s="130"/>
+      <c r="R25" s="131"/>
+      <c r="S25" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="127"/>
-      <c r="U25" s="127"/>
-      <c r="V25" s="128"/>
-      <c r="W25" s="126" t="s">
+      <c r="T25" s="130"/>
+      <c r="U25" s="130"/>
+      <c r="V25" s="131"/>
+      <c r="W25" s="129" t="s">
         <v>10</v>
       </c>
-      <c r="X25" s="127"/>
-      <c r="Y25" s="127"/>
-      <c r="Z25" s="128"/>
+      <c r="X25" s="130"/>
+      <c r="Y25" s="130"/>
+      <c r="Z25" s="131"/>
       <c r="AA25" s="4"/>
     </row>
     <row r="26" spans="6:31" ht="14.1" customHeight="1">
       <c r="M26" s="8"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="89" t="s">
+      <c r="O26" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="P26" s="90"/>
-      <c r="Q26" s="90"/>
-      <c r="R26" s="91"/>
-      <c r="S26" s="98"/>
-      <c r="T26" s="99"/>
-      <c r="U26" s="99"/>
-      <c r="V26" s="100"/>
-      <c r="W26" s="107"/>
-      <c r="X26" s="108"/>
-      <c r="Y26" s="108"/>
-      <c r="Z26" s="109"/>
+      <c r="P26" s="93"/>
+      <c r="Q26" s="93"/>
+      <c r="R26" s="94"/>
+      <c r="S26" s="101"/>
+      <c r="T26" s="102"/>
+      <c r="U26" s="102"/>
+      <c r="V26" s="103"/>
+      <c r="W26" s="110"/>
+      <c r="X26" s="111"/>
+      <c r="Y26" s="111"/>
+      <c r="Z26" s="112"/>
       <c r="AA26" s="4"/>
     </row>
     <row r="27" spans="6:31" ht="14.1" customHeight="1">
       <c r="M27" s="8"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="92"/>
-      <c r="P27" s="93"/>
-      <c r="Q27" s="93"/>
-      <c r="R27" s="94"/>
-      <c r="S27" s="101"/>
-      <c r="T27" s="102"/>
-      <c r="U27" s="102"/>
-      <c r="V27" s="103"/>
-      <c r="W27" s="110"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="111"/>
-      <c r="Z27" s="112"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="96"/>
+      <c r="Q27" s="96"/>
+      <c r="R27" s="97"/>
+      <c r="S27" s="104"/>
+      <c r="T27" s="105"/>
+      <c r="U27" s="105"/>
+      <c r="V27" s="106"/>
+      <c r="W27" s="113"/>
+      <c r="X27" s="114"/>
+      <c r="Y27" s="114"/>
+      <c r="Z27" s="115"/>
       <c r="AA27" s="4"/>
     </row>
     <row r="28" spans="6:31" ht="14.1" customHeight="1">
       <c r="M28" s="8"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="95"/>
-      <c r="P28" s="96"/>
-      <c r="Q28" s="96"/>
-      <c r="R28" s="97"/>
-      <c r="S28" s="104"/>
-      <c r="T28" s="105"/>
-      <c r="U28" s="105"/>
-      <c r="V28" s="106"/>
-      <c r="W28" s="113"/>
-      <c r="X28" s="114"/>
-      <c r="Y28" s="114"/>
-      <c r="Z28" s="115"/>
+      <c r="O28" s="98"/>
+      <c r="P28" s="99"/>
+      <c r="Q28" s="99"/>
+      <c r="R28" s="100"/>
+      <c r="S28" s="107"/>
+      <c r="T28" s="108"/>
+      <c r="U28" s="108"/>
+      <c r="V28" s="109"/>
+      <c r="W28" s="116"/>
+      <c r="X28" s="117"/>
+      <c r="Y28" s="117"/>
+      <c r="Z28" s="118"/>
       <c r="AA28" s="4"/>
     </row>
     <row r="29" spans="6:31" ht="14.1" customHeight="1">
@@ -2707,36 +2729,36 @@
     <row r="31" spans="6:31" ht="14.1" customHeight="1">
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
-      <c r="O31" s="87" t="s">
+      <c r="O31" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="P31" s="88"/>
-      <c r="Q31" s="88"/>
-      <c r="R31" s="88"/>
-      <c r="S31" s="88"/>
-      <c r="T31" s="88"/>
-      <c r="U31" s="88"/>
-      <c r="V31" s="88"/>
-      <c r="W31" s="88"/>
-      <c r="X31" s="88"/>
-      <c r="Y31" s="88"/>
-      <c r="Z31" s="88"/>
+      <c r="P31" s="91"/>
+      <c r="Q31" s="91"/>
+      <c r="R31" s="91"/>
+      <c r="S31" s="91"/>
+      <c r="T31" s="91"/>
+      <c r="U31" s="91"/>
+      <c r="V31" s="91"/>
+      <c r="W31" s="91"/>
+      <c r="X31" s="91"/>
+      <c r="Y31" s="91"/>
+      <c r="Z31" s="91"/>
     </row>
     <row r="32" spans="6:31" ht="14.1" customHeight="1">
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
-      <c r="O32" s="88"/>
-      <c r="P32" s="88"/>
-      <c r="Q32" s="88"/>
-      <c r="R32" s="88"/>
-      <c r="S32" s="88"/>
-      <c r="T32" s="88"/>
-      <c r="U32" s="88"/>
-      <c r="V32" s="88"/>
-      <c r="W32" s="88"/>
-      <c r="X32" s="88"/>
-      <c r="Y32" s="88"/>
-      <c r="Z32" s="88"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="91"/>
+      <c r="Q32" s="91"/>
+      <c r="R32" s="91"/>
+      <c r="S32" s="91"/>
+      <c r="T32" s="91"/>
+      <c r="U32" s="91"/>
+      <c r="V32" s="91"/>
+      <c r="W32" s="91"/>
+      <c r="X32" s="91"/>
+      <c r="Y32" s="91"/>
+      <c r="Z32" s="91"/>
     </row>
     <row r="33" ht="14.1" customHeight="1"/>
   </sheetData>
@@ -2758,6 +2780,1511 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DBED43-E4B6-4D24-AC88-89CDEF182391}">
+  <dimension ref="A1:AP33"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="40" width="3.33203125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="32"/>
+      <c r="AK1" s="32"/>
+      <c r="AL1" s="32"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="32"/>
+    </row>
+    <row r="2" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A2" s="32"/>
+      <c r="B2" s="89" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+    </row>
+    <row r="3" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A3" s="32"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AL3" s="32"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+    </row>
+    <row r="4" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+    </row>
+    <row r="5" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A5" s="32"/>
+      <c r="B5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="W5" s="47"/>
+      <c r="X5" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE5" s="50"/>
+      <c r="AF5" s="50"/>
+      <c r="AG5" s="50"/>
+      <c r="AH5" s="50"/>
+      <c r="AI5" s="50"/>
+      <c r="AJ5" s="50"/>
+      <c r="AK5" s="50"/>
+      <c r="AL5" s="50"/>
+      <c r="AM5" s="51"/>
+      <c r="AN5" s="32"/>
+    </row>
+    <row r="6" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A6" s="32"/>
+      <c r="B6" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="87"/>
+      <c r="W6" s="88"/>
+      <c r="X6" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="30"/>
+      <c r="AM6" s="31"/>
+      <c r="AN6" s="32"/>
+      <c r="AO6" s="27"/>
+    </row>
+    <row r="7" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A7" s="32"/>
+      <c r="B7" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="87">
+        <v>20</v>
+      </c>
+      <c r="W7" s="88"/>
+      <c r="X7" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="31"/>
+      <c r="AN7" s="32"/>
+    </row>
+    <row r="8" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A8" s="32"/>
+      <c r="B8" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="30"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="30"/>
+      <c r="AJ8" s="30"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="30"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="32"/>
+    </row>
+    <row r="9" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A9" s="32"/>
+      <c r="B9" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="31"/>
+      <c r="AN9" s="32"/>
+    </row>
+    <row r="10" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A10" s="32"/>
+      <c r="B10" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="87">
+        <v>20</v>
+      </c>
+      <c r="W10" s="88"/>
+      <c r="X10" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="30"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="30"/>
+      <c r="AJ10" s="30"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="30"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="32"/>
+    </row>
+    <row r="11" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A11" s="32"/>
+      <c r="B11" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="30"/>
+      <c r="AJ11" s="30"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="30"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="32"/>
+    </row>
+    <row r="12" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A12" s="32"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="142"/>
+      <c r="W12" s="142"/>
+      <c r="X12" s="32"/>
+      <c r="Y12" s="32"/>
+      <c r="Z12" s="32"/>
+      <c r="AA12" s="32"/>
+      <c r="AB12" s="32"/>
+      <c r="AC12" s="32"/>
+      <c r="AD12" s="68"/>
+      <c r="AE12" s="68"/>
+      <c r="AF12" s="68"/>
+      <c r="AG12" s="68"/>
+      <c r="AH12" s="68"/>
+      <c r="AI12" s="68"/>
+      <c r="AJ12" s="68"/>
+      <c r="AK12" s="68"/>
+      <c r="AL12" s="68"/>
+      <c r="AM12" s="68"/>
+      <c r="AN12" s="32"/>
+    </row>
+    <row r="13" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
+      <c r="AE13" s="32"/>
+      <c r="AF13" s="32"/>
+      <c r="AG13" s="32"/>
+      <c r="AH13" s="32"/>
+      <c r="AI13" s="32"/>
+      <c r="AJ13" s="32"/>
+      <c r="AK13" s="32"/>
+      <c r="AL13" s="32"/>
+      <c r="AM13" s="32"/>
+      <c r="AN13" s="32"/>
+    </row>
+    <row r="14" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
+      <c r="Y14" s="32"/>
+      <c r="Z14" s="32"/>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="32"/>
+      <c r="AC14" s="32"/>
+      <c r="AD14" s="32"/>
+      <c r="AE14" s="32"/>
+      <c r="AF14" s="32"/>
+      <c r="AG14" s="32"/>
+      <c r="AH14" s="32"/>
+      <c r="AI14" s="32"/>
+      <c r="AJ14" s="32"/>
+      <c r="AK14" s="32"/>
+      <c r="AL14" s="32"/>
+      <c r="AM14" s="32"/>
+      <c r="AN14" s="32"/>
+    </row>
+    <row r="15" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+      <c r="AA15" s="32"/>
+      <c r="AB15" s="32"/>
+      <c r="AC15" s="32"/>
+      <c r="AD15" s="32"/>
+      <c r="AE15" s="32"/>
+      <c r="AF15" s="32"/>
+      <c r="AG15" s="32"/>
+      <c r="AH15" s="32"/>
+      <c r="AI15" s="32"/>
+      <c r="AJ15" s="32"/>
+      <c r="AK15" s="32"/>
+      <c r="AL15" s="32"/>
+      <c r="AM15" s="32"/>
+      <c r="AN15" s="32"/>
+    </row>
+    <row r="16" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="45"/>
+      <c r="R16" s="45"/>
+      <c r="S16" s="45"/>
+      <c r="T16" s="45"/>
+      <c r="U16" s="45"/>
+      <c r="V16" s="45"/>
+      <c r="W16" s="45"/>
+      <c r="X16" s="45"/>
+      <c r="Y16" s="45"/>
+      <c r="Z16" s="45"/>
+      <c r="AA16" s="45"/>
+      <c r="AB16" s="45"/>
+      <c r="AC16" s="45"/>
+      <c r="AD16" s="45"/>
+      <c r="AE16" s="45"/>
+      <c r="AF16" s="32"/>
+      <c r="AG16" s="32"/>
+      <c r="AH16" s="32"/>
+      <c r="AI16" s="32"/>
+      <c r="AJ16" s="32"/>
+      <c r="AK16" s="32"/>
+      <c r="AL16" s="32"/>
+      <c r="AM16" s="32"/>
+      <c r="AN16" s="32"/>
+    </row>
+    <row r="17" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="142"/>
+      <c r="W17" s="142"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="32"/>
+      <c r="AC17" s="32"/>
+      <c r="AD17" s="32"/>
+      <c r="AE17" s="32"/>
+      <c r="AF17" s="32"/>
+      <c r="AG17" s="32"/>
+      <c r="AH17" s="32"/>
+      <c r="AI17" s="32"/>
+      <c r="AJ17" s="32"/>
+      <c r="AK17" s="32"/>
+      <c r="AL17" s="32"/>
+      <c r="AM17" s="32"/>
+      <c r="AN17" s="32"/>
+    </row>
+    <row r="18" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="45"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="45"/>
+      <c r="U18" s="45"/>
+      <c r="V18" s="45"/>
+      <c r="W18" s="45"/>
+      <c r="X18" s="45"/>
+      <c r="Y18" s="45"/>
+      <c r="Z18" s="45"/>
+      <c r="AA18" s="45"/>
+      <c r="AB18" s="45"/>
+      <c r="AC18" s="45"/>
+      <c r="AD18" s="45"/>
+      <c r="AE18" s="45"/>
+      <c r="AF18" s="32"/>
+      <c r="AG18" s="32"/>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="32"/>
+      <c r="AJ18" s="32"/>
+      <c r="AK18" s="32"/>
+      <c r="AL18" s="32"/>
+      <c r="AM18" s="32"/>
+      <c r="AN18" s="32"/>
+    </row>
+    <row r="19" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="32"/>
+      <c r="AF19" s="32"/>
+      <c r="AG19" s="32"/>
+      <c r="AH19" s="32"/>
+      <c r="AI19" s="32"/>
+      <c r="AJ19" s="32"/>
+      <c r="AK19" s="32"/>
+      <c r="AL19" s="32"/>
+      <c r="AM19" s="32"/>
+      <c r="AN19" s="32"/>
+    </row>
+    <row r="20" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="32"/>
+      <c r="AJ20" s="32"/>
+      <c r="AK20" s="32"/>
+      <c r="AL20" s="32"/>
+      <c r="AM20" s="32"/>
+      <c r="AN20" s="32"/>
+    </row>
+    <row r="21" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="32"/>
+      <c r="AJ21" s="32"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="32"/>
+      <c r="AM21" s="32"/>
+      <c r="AN21" s="32"/>
+    </row>
+    <row r="22" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A22" s="32"/>
+      <c r="B22" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="52"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="52"/>
+      <c r="U22" s="52"/>
+      <c r="V22" s="52"/>
+      <c r="W22" s="52"/>
+      <c r="X22" s="52"/>
+      <c r="Y22" s="52"/>
+      <c r="Z22" s="52"/>
+      <c r="AA22" s="52"/>
+      <c r="AB22" s="52"/>
+      <c r="AC22" s="52"/>
+      <c r="AD22" s="52"/>
+      <c r="AE22" s="52"/>
+      <c r="AF22" s="47"/>
+      <c r="AG22" s="47"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="47"/>
+      <c r="AJ22" s="47"/>
+      <c r="AK22" s="47"/>
+      <c r="AL22" s="47"/>
+      <c r="AM22" s="48"/>
+      <c r="AN22" s="32"/>
+    </row>
+    <row r="23" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A23" s="32"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="55"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="56"/>
+      <c r="W23" s="56"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="54"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
+      <c r="AF23" s="54"/>
+      <c r="AG23" s="54"/>
+      <c r="AH23" s="54"/>
+      <c r="AI23" s="54"/>
+      <c r="AJ23" s="54"/>
+      <c r="AK23" s="54"/>
+      <c r="AL23" s="54"/>
+      <c r="AM23" s="57"/>
+      <c r="AN23" s="32"/>
+    </row>
+    <row r="24" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A24" s="32"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AA24" s="60"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="32"/>
+      <c r="AG24" s="32"/>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="32"/>
+      <c r="AJ24" s="32"/>
+      <c r="AK24" s="32"/>
+      <c r="AL24" s="32"/>
+      <c r="AM24" s="61"/>
+      <c r="AN24" s="32"/>
+      <c r="AP24" s="38"/>
+    </row>
+    <row r="25" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A25" s="32"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="60"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="63"/>
+      <c r="V25" s="63"/>
+      <c r="W25" s="63"/>
+      <c r="X25" s="63"/>
+      <c r="Y25" s="63"/>
+      <c r="Z25" s="63"/>
+      <c r="AA25" s="60"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
+      <c r="AG25" s="32"/>
+      <c r="AH25" s="32"/>
+      <c r="AI25" s="32"/>
+      <c r="AJ25" s="32"/>
+      <c r="AK25" s="32"/>
+      <c r="AL25" s="32"/>
+      <c r="AM25" s="61"/>
+      <c r="AN25" s="32"/>
+      <c r="AP25" s="38"/>
+    </row>
+    <row r="26" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A26" s="32"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="60"/>
+      <c r="S26" s="60"/>
+      <c r="T26" s="60"/>
+      <c r="U26" s="60"/>
+      <c r="V26" s="60"/>
+      <c r="W26" s="60"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="60"/>
+      <c r="AA26" s="60"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="61"/>
+      <c r="AN26" s="32"/>
+      <c r="AP26" s="38"/>
+    </row>
+    <row r="27" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A27" s="32"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="60"/>
+      <c r="Z27" s="60"/>
+      <c r="AA27" s="60"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="61"/>
+      <c r="AN27" s="32"/>
+      <c r="AP27" s="38"/>
+    </row>
+    <row r="28" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A28" s="32"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
+      <c r="S28" s="60"/>
+      <c r="T28" s="60"/>
+      <c r="U28" s="60"/>
+      <c r="V28" s="60"/>
+      <c r="W28" s="60"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="60"/>
+      <c r="Z28" s="60"/>
+      <c r="AA28" s="60"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
+      <c r="AG28" s="32"/>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="32"/>
+      <c r="AJ28" s="32"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="32"/>
+      <c r="AM28" s="61"/>
+      <c r="AN28" s="32"/>
+      <c r="AP28" s="38"/>
+    </row>
+    <row r="29" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A29" s="32"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="60"/>
+      <c r="P29" s="60"/>
+      <c r="Q29" s="60"/>
+      <c r="R29" s="60"/>
+      <c r="S29" s="60"/>
+      <c r="T29" s="60"/>
+      <c r="U29" s="60"/>
+      <c r="V29" s="60"/>
+      <c r="W29" s="60"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="60"/>
+      <c r="Z29" s="60"/>
+      <c r="AA29" s="60"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="32"/>
+      <c r="AG29" s="32"/>
+      <c r="AH29" s="32"/>
+      <c r="AI29" s="32"/>
+      <c r="AJ29" s="32"/>
+      <c r="AK29" s="32"/>
+      <c r="AL29" s="32"/>
+      <c r="AM29" s="61"/>
+      <c r="AN29" s="32"/>
+      <c r="AP29" s="38"/>
+    </row>
+    <row r="30" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A30" s="32"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="60"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="60"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="60"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="60"/>
+      <c r="V30" s="60"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="60"/>
+      <c r="Z30" s="60"/>
+      <c r="AA30" s="60"/>
+      <c r="AB30" s="32"/>
+      <c r="AC30" s="32"/>
+      <c r="AD30" s="32"/>
+      <c r="AE30" s="32"/>
+      <c r="AF30" s="32"/>
+      <c r="AG30" s="32"/>
+      <c r="AH30" s="32"/>
+      <c r="AI30" s="32"/>
+      <c r="AJ30" s="32"/>
+      <c r="AK30" s="32"/>
+      <c r="AL30" s="32"/>
+      <c r="AM30" s="61"/>
+      <c r="AN30" s="32"/>
+      <c r="AP30" s="38"/>
+    </row>
+    <row r="31" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A31" s="32"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="65"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="65"/>
+      <c r="T31" s="65"/>
+      <c r="U31" s="65"/>
+      <c r="V31" s="65"/>
+      <c r="W31" s="65"/>
+      <c r="X31" s="65"/>
+      <c r="Y31" s="65"/>
+      <c r="Z31" s="65"/>
+      <c r="AA31" s="65"/>
+      <c r="AB31" s="65"/>
+      <c r="AC31" s="65"/>
+      <c r="AD31" s="65"/>
+      <c r="AE31" s="65"/>
+      <c r="AF31" s="65"/>
+      <c r="AG31" s="65"/>
+      <c r="AH31" s="65"/>
+      <c r="AI31" s="65"/>
+      <c r="AJ31" s="65"/>
+      <c r="AK31" s="65"/>
+      <c r="AL31" s="65"/>
+      <c r="AM31" s="67"/>
+      <c r="AN31" s="32"/>
+      <c r="AP31" s="38"/>
+    </row>
+    <row r="32" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="32"/>
+      <c r="AF32" s="32"/>
+      <c r="AG32" s="32"/>
+      <c r="AH32" s="32"/>
+      <c r="AI32" s="32"/>
+      <c r="AJ32" s="32"/>
+      <c r="AK32" s="32"/>
+      <c r="AL32" s="32"/>
+      <c r="AM32" s="32"/>
+      <c r="AN32" s="32"/>
+      <c r="AP32" s="38"/>
+    </row>
+    <row r="33" spans="1:42" ht="14.1" customHeight="1">
+      <c r="A33" s="32"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+      <c r="Z33" s="32"/>
+      <c r="AA33" s="32"/>
+      <c r="AB33" s="32"/>
+      <c r="AC33" s="32"/>
+      <c r="AD33" s="32"/>
+      <c r="AE33" s="32"/>
+      <c r="AF33" s="32"/>
+      <c r="AG33" s="32"/>
+      <c r="AH33" s="32"/>
+      <c r="AI33" s="32"/>
+      <c r="AJ33" s="32"/>
+      <c r="AK33" s="32"/>
+      <c r="AL33" s="32"/>
+      <c r="AM33" s="32"/>
+      <c r="AN33" s="32"/>
+      <c r="AP33" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B2:P3"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V7:W7"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5112C446-F973-4C26-8146-684254FAD872}">
   <dimension ref="A1:BS33"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
@@ -2809,23 +4336,23 @@
     </row>
     <row r="2" spans="1:71" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
       <c r="Q2" s="32"/>
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
@@ -2853,21 +4380,21 @@
     </row>
     <row r="3" spans="1:71" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
       <c r="S3" s="32"/>
@@ -3017,8 +4544,8 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="139"/>
-      <c r="W6" s="140"/>
+      <c r="V6" s="87"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -3070,10 +4597,10 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="139">
+      <c r="V7" s="87">
         <v>20</v>
       </c>
-      <c r="W7" s="140"/>
+      <c r="W7" s="88"/>
       <c r="X7" s="29" t="s">
         <v>25</v>
       </c>
@@ -3122,8 +4649,8 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="140"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="88"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -3174,8 +4701,8 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="140"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="88"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -3226,10 +4753,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="139">
+      <c r="V10" s="87">
         <v>20</v>
       </c>
-      <c r="W10" s="140"/>
+      <c r="W10" s="88"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -3278,8 +4805,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="140"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="88"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -4810,7 +6337,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24BB53F4-2AB1-428A-9E5C-832D2C56E7DE}">
   <dimension ref="A1:AO33"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
@@ -4821,44 +6348,44 @@
   <sheetData>
     <row r="1" spans="2:41" ht="14.1" customHeight="1"/>
     <row r="2" spans="2:41" ht="14.1" customHeight="1">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="89" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
     </row>
     <row r="3" spans="2:41" ht="14.1" customHeight="1">
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="141"/>
-      <c r="R3" s="141"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
     </row>
     <row r="4" spans="2:41" ht="14.1" customHeight="1"/>
     <row r="5" spans="2:41" ht="14.1" customHeight="1">
@@ -4940,8 +6467,8 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="139"/>
-      <c r="W6" s="140"/>
+      <c r="V6" s="87"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -4988,8 +6515,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="140"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="88"/>
       <c r="X7" s="29" t="s">
         <v>25</v>
       </c>
@@ -5038,10 +6565,10 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="139">
+      <c r="V8" s="87">
         <v>2000</v>
       </c>
-      <c r="W8" s="140"/>
+      <c r="W8" s="88"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -5089,10 +6616,10 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="139">
+      <c r="V9" s="87">
         <v>100</v>
       </c>
-      <c r="W9" s="140"/>
+      <c r="W9" s="88"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -5139,10 +6666,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="139">
+      <c r="V10" s="87">
         <v>50</v>
       </c>
-      <c r="W10" s="140"/>
+      <c r="W10" s="88"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -5191,8 +6718,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="140"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="88"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -5241,8 +6768,8 @@
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="140"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="88"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -5291,8 +6818,8 @@
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="140"/>
+      <c r="V13" s="87"/>
+      <c r="W13" s="88"/>
       <c r="X13" s="29" t="s">
         <v>25</v>
       </c>
@@ -5341,10 +6868,10 @@
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31"/>
-      <c r="V14" s="139">
+      <c r="V14" s="87">
         <v>20</v>
       </c>
-      <c r="W14" s="140"/>
+      <c r="W14" s="88"/>
       <c r="X14" s="29" t="s">
         <v>25</v>
       </c>
@@ -5391,8 +6918,8 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31"/>
-      <c r="V15" s="139"/>
-      <c r="W15" s="140"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="88"/>
       <c r="X15" s="29" t="s">
         <v>25</v>
       </c>
@@ -5954,7 +7481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE68A44-658E-428B-A19E-D952DB9C7789}">
   <dimension ref="A1:AO33"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
@@ -5965,48 +7492,48 @@
   <sheetData>
     <row r="1" spans="2:41" ht="14.1" customHeight="1"/>
     <row r="2" spans="2:41" ht="14.1" customHeight="1">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
-      <c r="S2" s="141"/>
-      <c r="T2" s="141"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
     </row>
     <row r="3" spans="2:41" ht="14.1" customHeight="1">
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="141"/>
-      <c r="R3" s="141"/>
-      <c r="S3" s="141"/>
-      <c r="T3" s="141"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
     </row>
     <row r="4" spans="2:41" ht="14.1" customHeight="1"/>
     <row r="5" spans="2:41" ht="14.1" customHeight="1">
@@ -6088,10 +7615,10 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="139">
+      <c r="V6" s="87">
         <v>100</v>
       </c>
-      <c r="W6" s="140"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="29" t="s">
         <v>143</v>
       </c>
@@ -6138,10 +7665,10 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="139">
+      <c r="V7" s="87">
         <v>100</v>
       </c>
-      <c r="W7" s="140"/>
+      <c r="W7" s="88"/>
       <c r="X7" s="29" t="s">
         <v>143</v>
       </c>
@@ -6383,8 +7910,8 @@
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="140"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="88"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -6433,8 +7960,8 @@
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="140"/>
+      <c r="V13" s="87"/>
+      <c r="W13" s="88"/>
       <c r="X13" s="29" t="s">
         <v>25</v>
       </c>
@@ -6483,10 +8010,10 @@
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31"/>
-      <c r="V14" s="139">
+      <c r="V14" s="87">
         <v>20</v>
       </c>
-      <c r="W14" s="140"/>
+      <c r="W14" s="88"/>
       <c r="X14" s="29" t="s">
         <v>25</v>
       </c>
@@ -6533,8 +8060,8 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31"/>
-      <c r="V15" s="139"/>
-      <c r="W15" s="140"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="88"/>
       <c r="X15" s="29" t="s">
         <v>25</v>
       </c>
@@ -7097,15 +8624,15 @@
   <sheetData>
     <row r="1" spans="2:39" ht="14.1" customHeight="1"/>
     <row r="2" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -7131,564 +8658,564 @@
       <c r="AE2" s="8"/>
     </row>
     <row r="3" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
     </row>
     <row r="4" spans="2:39" ht="14.1" customHeight="1"/>
     <row r="5" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132" t="s">
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="132"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="132"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="132" t="s">
+      <c r="J5" s="135"/>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135"/>
+      <c r="M5" s="135"/>
+      <c r="N5" s="135"/>
+      <c r="O5" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="132"/>
-      <c r="R5" s="132"/>
-      <c r="S5" s="132"/>
-      <c r="T5" s="132" t="s">
+      <c r="P5" s="135"/>
+      <c r="Q5" s="135"/>
+      <c r="R5" s="135"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="U5" s="132"/>
-      <c r="V5" s="132"/>
-      <c r="W5" s="132"/>
-      <c r="X5" s="132"/>
-      <c r="Y5" s="132"/>
-      <c r="Z5" s="132"/>
-      <c r="AA5" s="132"/>
-      <c r="AB5" s="132"/>
-      <c r="AC5" s="132"/>
-      <c r="AD5" s="132"/>
-      <c r="AE5" s="132"/>
-      <c r="AF5" s="132"/>
-      <c r="AG5" s="132"/>
-      <c r="AH5" s="132" t="s">
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
+      <c r="Y5" s="135"/>
+      <c r="Z5" s="135"/>
+      <c r="AA5" s="135"/>
+      <c r="AB5" s="135"/>
+      <c r="AC5" s="135"/>
+      <c r="AD5" s="135"/>
+      <c r="AE5" s="135"/>
+      <c r="AF5" s="135"/>
+      <c r="AG5" s="135"/>
+      <c r="AH5" s="135" t="s">
         <v>15</v>
       </c>
-      <c r="AI5" s="132"/>
-      <c r="AJ5" s="132"/>
-      <c r="AK5" s="132"/>
-      <c r="AL5" s="132"/>
-      <c r="AM5" s="132"/>
+      <c r="AI5" s="135"/>
+      <c r="AJ5" s="135"/>
+      <c r="AK5" s="135"/>
+      <c r="AL5" s="135"/>
+      <c r="AM5" s="135"/>
     </row>
     <row r="6" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B6" s="133">
+      <c r="B6" s="139">
         <v>1</v>
       </c>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="130">
+      <c r="C6" s="139"/>
+      <c r="D6" s="139"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="139"/>
+      <c r="I6" s="137">
         <v>45611</v>
       </c>
-      <c r="J6" s="129"/>
-      <c r="K6" s="129"/>
-      <c r="L6" s="129"/>
-      <c r="M6" s="129"/>
-      <c r="N6" s="129"/>
-      <c r="O6" s="131" t="s">
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="P6" s="131"/>
-      <c r="Q6" s="131"/>
-      <c r="R6" s="131"/>
-      <c r="S6" s="131"/>
-      <c r="T6" s="131" t="s">
+      <c r="P6" s="138"/>
+      <c r="Q6" s="138"/>
+      <c r="R6" s="138"/>
+      <c r="S6" s="138"/>
+      <c r="T6" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="U6" s="131"/>
-      <c r="V6" s="131"/>
-      <c r="W6" s="131"/>
-      <c r="X6" s="131"/>
-      <c r="Y6" s="131"/>
-      <c r="Z6" s="131"/>
-      <c r="AA6" s="131"/>
-      <c r="AB6" s="131"/>
-      <c r="AC6" s="131"/>
-      <c r="AD6" s="131"/>
-      <c r="AE6" s="131"/>
-      <c r="AF6" s="131"/>
-      <c r="AG6" s="131"/>
-      <c r="AH6" s="131" t="s">
+      <c r="U6" s="138"/>
+      <c r="V6" s="138"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="138"/>
+      <c r="Y6" s="138"/>
+      <c r="Z6" s="138"/>
+      <c r="AA6" s="138"/>
+      <c r="AB6" s="138"/>
+      <c r="AC6" s="138"/>
+      <c r="AD6" s="138"/>
+      <c r="AE6" s="138"/>
+      <c r="AF6" s="138"/>
+      <c r="AG6" s="138"/>
+      <c r="AH6" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="AI6" s="131"/>
-      <c r="AJ6" s="131"/>
-      <c r="AK6" s="131"/>
-      <c r="AL6" s="131"/>
-      <c r="AM6" s="131"/>
+      <c r="AI6" s="138"/>
+      <c r="AJ6" s="138"/>
+      <c r="AK6" s="138"/>
+      <c r="AL6" s="138"/>
+      <c r="AM6" s="138"/>
     </row>
     <row r="7" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B7" s="129">
+      <c r="B7" s="136">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="130">
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="137">
         <v>46086</v>
       </c>
-      <c r="J7" s="129"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="129"/>
-      <c r="O7" s="131" t="s">
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="131"/>
-      <c r="T7" s="131" t="s">
-        <v>175</v>
-      </c>
-      <c r="U7" s="131"/>
-      <c r="V7" s="131"/>
-      <c r="W7" s="131"/>
-      <c r="X7" s="131"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="131"/>
-      <c r="AB7" s="131"/>
-      <c r="AC7" s="131"/>
-      <c r="AD7" s="131"/>
-      <c r="AE7" s="131"/>
-      <c r="AF7" s="131"/>
-      <c r="AG7" s="131"/>
-      <c r="AH7" s="131" t="s">
-        <v>174</v>
-      </c>
-      <c r="AI7" s="131"/>
-      <c r="AJ7" s="131"/>
-      <c r="AK7" s="131"/>
-      <c r="AL7" s="131"/>
-      <c r="AM7" s="131"/>
+      <c r="P7" s="138"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="138"/>
+      <c r="S7" s="138"/>
+      <c r="T7" s="138" t="s">
+        <v>173</v>
+      </c>
+      <c r="U7" s="138"/>
+      <c r="V7" s="138"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="138"/>
+      <c r="Y7" s="138"/>
+      <c r="Z7" s="138"/>
+      <c r="AA7" s="138"/>
+      <c r="AB7" s="138"/>
+      <c r="AC7" s="138"/>
+      <c r="AD7" s="138"/>
+      <c r="AE7" s="138"/>
+      <c r="AF7" s="138"/>
+      <c r="AG7" s="138"/>
+      <c r="AH7" s="138" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI7" s="138"/>
+      <c r="AJ7" s="138"/>
+      <c r="AK7" s="138"/>
+      <c r="AL7" s="138"/>
+      <c r="AM7" s="138"/>
     </row>
     <row r="8" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B8" s="129"/>
-      <c r="C8" s="129"/>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="129"/>
-      <c r="H8" s="129"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="129"/>
-      <c r="K8" s="129"/>
-      <c r="L8" s="129"/>
-      <c r="M8" s="129"/>
-      <c r="N8" s="129"/>
-      <c r="O8" s="131"/>
-      <c r="P8" s="131"/>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="131"/>
-      <c r="S8" s="131"/>
-      <c r="T8" s="131"/>
-      <c r="U8" s="131"/>
-      <c r="V8" s="131"/>
-      <c r="W8" s="131"/>
-      <c r="X8" s="131"/>
-      <c r="Y8" s="131"/>
-      <c r="Z8" s="131"/>
-      <c r="AA8" s="131"/>
-      <c r="AB8" s="131"/>
-      <c r="AC8" s="131"/>
-      <c r="AD8" s="131"/>
-      <c r="AE8" s="131"/>
-      <c r="AF8" s="131"/>
-      <c r="AG8" s="131"/>
-      <c r="AH8" s="131"/>
-      <c r="AI8" s="131"/>
-      <c r="AJ8" s="131"/>
-      <c r="AK8" s="131"/>
-      <c r="AL8" s="131"/>
-      <c r="AM8" s="131"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="136"/>
+      <c r="H8" s="136"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="136"/>
+      <c r="K8" s="136"/>
+      <c r="L8" s="136"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="136"/>
+      <c r="O8" s="138"/>
+      <c r="P8" s="138"/>
+      <c r="Q8" s="138"/>
+      <c r="R8" s="138"/>
+      <c r="S8" s="138"/>
+      <c r="T8" s="138"/>
+      <c r="U8" s="138"/>
+      <c r="V8" s="138"/>
+      <c r="W8" s="138"/>
+      <c r="X8" s="138"/>
+      <c r="Y8" s="138"/>
+      <c r="Z8" s="138"/>
+      <c r="AA8" s="138"/>
+      <c r="AB8" s="138"/>
+      <c r="AC8" s="138"/>
+      <c r="AD8" s="138"/>
+      <c r="AE8" s="138"/>
+      <c r="AF8" s="138"/>
+      <c r="AG8" s="138"/>
+      <c r="AH8" s="138"/>
+      <c r="AI8" s="138"/>
+      <c r="AJ8" s="138"/>
+      <c r="AK8" s="138"/>
+      <c r="AL8" s="138"/>
+      <c r="AM8" s="138"/>
     </row>
     <row r="9" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B9" s="129"/>
-      <c r="C9" s="129"/>
-      <c r="D9" s="129"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="129"/>
-      <c r="K9" s="129"/>
-      <c r="L9" s="129"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="129"/>
-      <c r="O9" s="131"/>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="131"/>
-      <c r="S9" s="131"/>
-      <c r="T9" s="131"/>
-      <c r="U9" s="131"/>
-      <c r="V9" s="131"/>
-      <c r="W9" s="131"/>
-      <c r="X9" s="131"/>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="131"/>
-      <c r="AA9" s="131"/>
-      <c r="AB9" s="131"/>
-      <c r="AC9" s="131"/>
-      <c r="AD9" s="131"/>
-      <c r="AE9" s="131"/>
-      <c r="AF9" s="131"/>
-      <c r="AG9" s="131"/>
-      <c r="AH9" s="131"/>
-      <c r="AI9" s="131"/>
-      <c r="AJ9" s="131"/>
-      <c r="AK9" s="131"/>
-      <c r="AL9" s="131"/>
-      <c r="AM9" s="131"/>
+      <c r="B9" s="136"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="136"/>
+      <c r="H9" s="136"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="136"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+      <c r="N9" s="136"/>
+      <c r="O9" s="138"/>
+      <c r="P9" s="138"/>
+      <c r="Q9" s="138"/>
+      <c r="R9" s="138"/>
+      <c r="S9" s="138"/>
+      <c r="T9" s="138"/>
+      <c r="U9" s="138"/>
+      <c r="V9" s="138"/>
+      <c r="W9" s="138"/>
+      <c r="X9" s="138"/>
+      <c r="Y9" s="138"/>
+      <c r="Z9" s="138"/>
+      <c r="AA9" s="138"/>
+      <c r="AB9" s="138"/>
+      <c r="AC9" s="138"/>
+      <c r="AD9" s="138"/>
+      <c r="AE9" s="138"/>
+      <c r="AF9" s="138"/>
+      <c r="AG9" s="138"/>
+      <c r="AH9" s="138"/>
+      <c r="AI9" s="138"/>
+      <c r="AJ9" s="138"/>
+      <c r="AK9" s="138"/>
+      <c r="AL9" s="138"/>
+      <c r="AM9" s="138"/>
     </row>
     <row r="10" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="129"/>
-      <c r="K10" s="129"/>
-      <c r="L10" s="129"/>
-      <c r="M10" s="129"/>
-      <c r="N10" s="129"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="131"/>
-      <c r="T10" s="131"/>
-      <c r="U10" s="131"/>
-      <c r="V10" s="131"/>
-      <c r="W10" s="131"/>
-      <c r="X10" s="131"/>
-      <c r="Y10" s="131"/>
-      <c r="Z10" s="131"/>
-      <c r="AA10" s="131"/>
-      <c r="AB10" s="131"/>
-      <c r="AC10" s="131"/>
-      <c r="AD10" s="131"/>
-      <c r="AE10" s="131"/>
-      <c r="AF10" s="131"/>
-      <c r="AG10" s="131"/>
-      <c r="AH10" s="131"/>
-      <c r="AI10" s="131"/>
-      <c r="AJ10" s="131"/>
-      <c r="AK10" s="131"/>
-      <c r="AL10" s="131"/>
-      <c r="AM10" s="131"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="136"/>
+      <c r="E10" s="136"/>
+      <c r="F10" s="136"/>
+      <c r="G10" s="136"/>
+      <c r="H10" s="136"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="136"/>
+      <c r="K10" s="136"/>
+      <c r="L10" s="136"/>
+      <c r="M10" s="136"/>
+      <c r="N10" s="136"/>
+      <c r="O10" s="138"/>
+      <c r="P10" s="138"/>
+      <c r="Q10" s="138"/>
+      <c r="R10" s="138"/>
+      <c r="S10" s="138"/>
+      <c r="T10" s="138"/>
+      <c r="U10" s="138"/>
+      <c r="V10" s="138"/>
+      <c r="W10" s="138"/>
+      <c r="X10" s="138"/>
+      <c r="Y10" s="138"/>
+      <c r="Z10" s="138"/>
+      <c r="AA10" s="138"/>
+      <c r="AB10" s="138"/>
+      <c r="AC10" s="138"/>
+      <c r="AD10" s="138"/>
+      <c r="AE10" s="138"/>
+      <c r="AF10" s="138"/>
+      <c r="AG10" s="138"/>
+      <c r="AH10" s="138"/>
+      <c r="AI10" s="138"/>
+      <c r="AJ10" s="138"/>
+      <c r="AK10" s="138"/>
+      <c r="AL10" s="138"/>
+      <c r="AM10" s="138"/>
     </row>
     <row r="11" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B11" s="129"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="129"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="129"/>
-      <c r="N11" s="129"/>
-      <c r="O11" s="131"/>
-      <c r="P11" s="131"/>
-      <c r="Q11" s="131"/>
-      <c r="R11" s="131"/>
-      <c r="S11" s="131"/>
-      <c r="T11" s="131"/>
-      <c r="U11" s="131"/>
-      <c r="V11" s="131"/>
-      <c r="W11" s="131"/>
-      <c r="X11" s="131"/>
-      <c r="Y11" s="131"/>
-      <c r="Z11" s="131"/>
-      <c r="AA11" s="131"/>
-      <c r="AB11" s="131"/>
-      <c r="AC11" s="131"/>
-      <c r="AD11" s="131"/>
-      <c r="AE11" s="131"/>
-      <c r="AF11" s="131"/>
-      <c r="AG11" s="131"/>
-      <c r="AH11" s="131"/>
-      <c r="AI11" s="131"/>
-      <c r="AJ11" s="131"/>
-      <c r="AK11" s="131"/>
-      <c r="AL11" s="131"/>
-      <c r="AM11" s="131"/>
+      <c r="B11" s="136"/>
+      <c r="C11" s="136"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="136"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="136"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
+      <c r="N11" s="136"/>
+      <c r="O11" s="138"/>
+      <c r="P11" s="138"/>
+      <c r="Q11" s="138"/>
+      <c r="R11" s="138"/>
+      <c r="S11" s="138"/>
+      <c r="T11" s="138"/>
+      <c r="U11" s="138"/>
+      <c r="V11" s="138"/>
+      <c r="W11" s="138"/>
+      <c r="X11" s="138"/>
+      <c r="Y11" s="138"/>
+      <c r="Z11" s="138"/>
+      <c r="AA11" s="138"/>
+      <c r="AB11" s="138"/>
+      <c r="AC11" s="138"/>
+      <c r="AD11" s="138"/>
+      <c r="AE11" s="138"/>
+      <c r="AF11" s="138"/>
+      <c r="AG11" s="138"/>
+      <c r="AH11" s="138"/>
+      <c r="AI11" s="138"/>
+      <c r="AJ11" s="138"/>
+      <c r="AK11" s="138"/>
+      <c r="AL11" s="138"/>
+      <c r="AM11" s="138"/>
     </row>
     <row r="12" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
-      <c r="M12" s="129"/>
-      <c r="N12" s="129"/>
-      <c r="O12" s="129"/>
-      <c r="P12" s="129"/>
-      <c r="Q12" s="129"/>
-      <c r="R12" s="129"/>
-      <c r="S12" s="129"/>
-      <c r="T12" s="129"/>
-      <c r="U12" s="129"/>
-      <c r="V12" s="129"/>
-      <c r="W12" s="129"/>
-      <c r="X12" s="129"/>
-      <c r="Y12" s="129"/>
-      <c r="Z12" s="129"/>
-      <c r="AA12" s="129"/>
-      <c r="AB12" s="129"/>
-      <c r="AC12" s="129"/>
-      <c r="AD12" s="129"/>
-      <c r="AE12" s="129"/>
-      <c r="AF12" s="129"/>
-      <c r="AG12" s="129"/>
-      <c r="AH12" s="129"/>
-      <c r="AI12" s="129"/>
-      <c r="AJ12" s="129"/>
-      <c r="AK12" s="129"/>
-      <c r="AL12" s="129"/>
-      <c r="AM12" s="129"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="136"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="136"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="136"/>
+      <c r="P12" s="136"/>
+      <c r="Q12" s="136"/>
+      <c r="R12" s="136"/>
+      <c r="S12" s="136"/>
+      <c r="T12" s="136"/>
+      <c r="U12" s="136"/>
+      <c r="V12" s="136"/>
+      <c r="W12" s="136"/>
+      <c r="X12" s="136"/>
+      <c r="Y12" s="136"/>
+      <c r="Z12" s="136"/>
+      <c r="AA12" s="136"/>
+      <c r="AB12" s="136"/>
+      <c r="AC12" s="136"/>
+      <c r="AD12" s="136"/>
+      <c r="AE12" s="136"/>
+      <c r="AF12" s="136"/>
+      <c r="AG12" s="136"/>
+      <c r="AH12" s="136"/>
+      <c r="AI12" s="136"/>
+      <c r="AJ12" s="136"/>
+      <c r="AK12" s="136"/>
+      <c r="AL12" s="136"/>
+      <c r="AM12" s="136"/>
     </row>
     <row r="13" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B13" s="129"/>
-      <c r="C13" s="129"/>
-      <c r="D13" s="129"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="129"/>
-      <c r="L13" s="129"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="129"/>
-      <c r="O13" s="129"/>
-      <c r="P13" s="129"/>
-      <c r="Q13" s="129"/>
-      <c r="R13" s="129"/>
-      <c r="S13" s="129"/>
-      <c r="T13" s="129"/>
-      <c r="U13" s="129"/>
-      <c r="V13" s="129"/>
-      <c r="W13" s="129"/>
-      <c r="X13" s="129"/>
-      <c r="Y13" s="129"/>
-      <c r="Z13" s="129"/>
-      <c r="AA13" s="129"/>
-      <c r="AB13" s="129"/>
-      <c r="AC13" s="129"/>
-      <c r="AD13" s="129"/>
-      <c r="AE13" s="129"/>
-      <c r="AF13" s="129"/>
-      <c r="AG13" s="129"/>
-      <c r="AH13" s="129"/>
-      <c r="AI13" s="129"/>
-      <c r="AJ13" s="129"/>
-      <c r="AK13" s="129"/>
-      <c r="AL13" s="129"/>
-      <c r="AM13" s="129"/>
+      <c r="B13" s="136"/>
+      <c r="C13" s="136"/>
+      <c r="D13" s="136"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="136"/>
+      <c r="H13" s="136"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="136"/>
+      <c r="K13" s="136"/>
+      <c r="L13" s="136"/>
+      <c r="M13" s="136"/>
+      <c r="N13" s="136"/>
+      <c r="O13" s="136"/>
+      <c r="P13" s="136"/>
+      <c r="Q13" s="136"/>
+      <c r="R13" s="136"/>
+      <c r="S13" s="136"/>
+      <c r="T13" s="136"/>
+      <c r="U13" s="136"/>
+      <c r="V13" s="136"/>
+      <c r="W13" s="136"/>
+      <c r="X13" s="136"/>
+      <c r="Y13" s="136"/>
+      <c r="Z13" s="136"/>
+      <c r="AA13" s="136"/>
+      <c r="AB13" s="136"/>
+      <c r="AC13" s="136"/>
+      <c r="AD13" s="136"/>
+      <c r="AE13" s="136"/>
+      <c r="AF13" s="136"/>
+      <c r="AG13" s="136"/>
+      <c r="AH13" s="136"/>
+      <c r="AI13" s="136"/>
+      <c r="AJ13" s="136"/>
+      <c r="AK13" s="136"/>
+      <c r="AL13" s="136"/>
+      <c r="AM13" s="136"/>
     </row>
     <row r="14" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="129"/>
-      <c r="K14" s="129"/>
-      <c r="L14" s="129"/>
-      <c r="M14" s="129"/>
-      <c r="N14" s="129"/>
-      <c r="O14" s="129"/>
-      <c r="P14" s="129"/>
-      <c r="Q14" s="129"/>
-      <c r="R14" s="129"/>
-      <c r="S14" s="129"/>
-      <c r="T14" s="129"/>
-      <c r="U14" s="129"/>
-      <c r="V14" s="129"/>
-      <c r="W14" s="129"/>
-      <c r="X14" s="129"/>
-      <c r="Y14" s="129"/>
-      <c r="Z14" s="129"/>
-      <c r="AA14" s="129"/>
-      <c r="AB14" s="129"/>
-      <c r="AC14" s="129"/>
-      <c r="AD14" s="129"/>
-      <c r="AE14" s="129"/>
-      <c r="AF14" s="129"/>
-      <c r="AG14" s="129"/>
-      <c r="AH14" s="129"/>
-      <c r="AI14" s="129"/>
-      <c r="AJ14" s="129"/>
-      <c r="AK14" s="129"/>
-      <c r="AL14" s="129"/>
-      <c r="AM14" s="129"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="136"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
+      <c r="R14" s="136"/>
+      <c r="S14" s="136"/>
+      <c r="T14" s="136"/>
+      <c r="U14" s="136"/>
+      <c r="V14" s="136"/>
+      <c r="W14" s="136"/>
+      <c r="X14" s="136"/>
+      <c r="Y14" s="136"/>
+      <c r="Z14" s="136"/>
+      <c r="AA14" s="136"/>
+      <c r="AB14" s="136"/>
+      <c r="AC14" s="136"/>
+      <c r="AD14" s="136"/>
+      <c r="AE14" s="136"/>
+      <c r="AF14" s="136"/>
+      <c r="AG14" s="136"/>
+      <c r="AH14" s="136"/>
+      <c r="AI14" s="136"/>
+      <c r="AJ14" s="136"/>
+      <c r="AK14" s="136"/>
+      <c r="AL14" s="136"/>
+      <c r="AM14" s="136"/>
     </row>
     <row r="15" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="129"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="129"/>
-      <c r="O15" s="129"/>
-      <c r="P15" s="129"/>
-      <c r="Q15" s="129"/>
-      <c r="R15" s="129"/>
-      <c r="S15" s="129"/>
-      <c r="T15" s="129"/>
-      <c r="U15" s="129"/>
-      <c r="V15" s="129"/>
-      <c r="W15" s="129"/>
-      <c r="X15" s="129"/>
-      <c r="Y15" s="129"/>
-      <c r="Z15" s="129"/>
-      <c r="AA15" s="129"/>
-      <c r="AB15" s="129"/>
-      <c r="AC15" s="129"/>
-      <c r="AD15" s="129"/>
-      <c r="AE15" s="129"/>
-      <c r="AF15" s="129"/>
-      <c r="AG15" s="129"/>
-      <c r="AH15" s="129"/>
-      <c r="AI15" s="129"/>
-      <c r="AJ15" s="129"/>
-      <c r="AK15" s="129"/>
-      <c r="AL15" s="129"/>
-      <c r="AM15" s="129"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="137"/>
+      <c r="J15" s="136"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="136"/>
+      <c r="M15" s="136"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="136"/>
+      <c r="P15" s="136"/>
+      <c r="Q15" s="136"/>
+      <c r="R15" s="136"/>
+      <c r="S15" s="136"/>
+      <c r="T15" s="136"/>
+      <c r="U15" s="136"/>
+      <c r="V15" s="136"/>
+      <c r="W15" s="136"/>
+      <c r="X15" s="136"/>
+      <c r="Y15" s="136"/>
+      <c r="Z15" s="136"/>
+      <c r="AA15" s="136"/>
+      <c r="AB15" s="136"/>
+      <c r="AC15" s="136"/>
+      <c r="AD15" s="136"/>
+      <c r="AE15" s="136"/>
+      <c r="AF15" s="136"/>
+      <c r="AG15" s="136"/>
+      <c r="AH15" s="136"/>
+      <c r="AI15" s="136"/>
+      <c r="AJ15" s="136"/>
+      <c r="AK15" s="136"/>
+      <c r="AL15" s="136"/>
+      <c r="AM15" s="136"/>
     </row>
     <row r="16" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="129"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
-      <c r="M16" s="129"/>
-      <c r="N16" s="129"/>
-      <c r="O16" s="129"/>
-      <c r="P16" s="129"/>
-      <c r="Q16" s="129"/>
-      <c r="R16" s="129"/>
-      <c r="S16" s="129"/>
-      <c r="T16" s="129"/>
-      <c r="U16" s="129"/>
-      <c r="V16" s="129"/>
-      <c r="W16" s="129"/>
-      <c r="X16" s="129"/>
-      <c r="Y16" s="129"/>
-      <c r="Z16" s="129"/>
-      <c r="AA16" s="129"/>
-      <c r="AB16" s="129"/>
-      <c r="AC16" s="129"/>
-      <c r="AD16" s="129"/>
-      <c r="AE16" s="129"/>
-      <c r="AF16" s="129"/>
-      <c r="AG16" s="129"/>
-      <c r="AH16" s="129"/>
-      <c r="AI16" s="129"/>
-      <c r="AJ16" s="129"/>
-      <c r="AK16" s="129"/>
-      <c r="AL16" s="129"/>
-      <c r="AM16" s="129"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="136"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="136"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="136"/>
+      <c r="O16" s="136"/>
+      <c r="P16" s="136"/>
+      <c r="Q16" s="136"/>
+      <c r="R16" s="136"/>
+      <c r="S16" s="136"/>
+      <c r="T16" s="136"/>
+      <c r="U16" s="136"/>
+      <c r="V16" s="136"/>
+      <c r="W16" s="136"/>
+      <c r="X16" s="136"/>
+      <c r="Y16" s="136"/>
+      <c r="Z16" s="136"/>
+      <c r="AA16" s="136"/>
+      <c r="AB16" s="136"/>
+      <c r="AC16" s="136"/>
+      <c r="AD16" s="136"/>
+      <c r="AE16" s="136"/>
+      <c r="AF16" s="136"/>
+      <c r="AG16" s="136"/>
+      <c r="AH16" s="136"/>
+      <c r="AI16" s="136"/>
+      <c r="AJ16" s="136"/>
+      <c r="AK16" s="136"/>
+      <c r="AL16" s="136"/>
+      <c r="AM16" s="136"/>
     </row>
     <row r="17" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B17" s="129"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="129"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="129"/>
-      <c r="M17" s="129"/>
-      <c r="N17" s="129"/>
-      <c r="O17" s="129"/>
-      <c r="P17" s="129"/>
-      <c r="Q17" s="129"/>
-      <c r="R17" s="129"/>
-      <c r="S17" s="129"/>
-      <c r="T17" s="129"/>
-      <c r="U17" s="129"/>
-      <c r="V17" s="129"/>
-      <c r="W17" s="129"/>
-      <c r="X17" s="129"/>
-      <c r="Y17" s="129"/>
-      <c r="Z17" s="129"/>
-      <c r="AA17" s="129"/>
-      <c r="AB17" s="129"/>
-      <c r="AC17" s="129"/>
-      <c r="AD17" s="129"/>
-      <c r="AE17" s="129"/>
-      <c r="AF17" s="129"/>
-      <c r="AG17" s="129"/>
-      <c r="AH17" s="129"/>
-      <c r="AI17" s="129"/>
-      <c r="AJ17" s="129"/>
-      <c r="AK17" s="129"/>
-      <c r="AL17" s="129"/>
-      <c r="AM17" s="129"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="137"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="136"/>
+      <c r="P17" s="136"/>
+      <c r="Q17" s="136"/>
+      <c r="R17" s="136"/>
+      <c r="S17" s="136"/>
+      <c r="T17" s="136"/>
+      <c r="U17" s="136"/>
+      <c r="V17" s="136"/>
+      <c r="W17" s="136"/>
+      <c r="X17" s="136"/>
+      <c r="Y17" s="136"/>
+      <c r="Z17" s="136"/>
+      <c r="AA17" s="136"/>
+      <c r="AB17" s="136"/>
+      <c r="AC17" s="136"/>
+      <c r="AD17" s="136"/>
+      <c r="AE17" s="136"/>
+      <c r="AF17" s="136"/>
+      <c r="AG17" s="136"/>
+      <c r="AH17" s="136"/>
+      <c r="AI17" s="136"/>
+      <c r="AJ17" s="136"/>
+      <c r="AK17" s="136"/>
+      <c r="AL17" s="136"/>
+      <c r="AM17" s="136"/>
     </row>
     <row r="18" spans="2:39" ht="14.1" customHeight="1"/>
     <row r="19" spans="2:39" ht="14.1" customHeight="1">
@@ -7797,10 +9324,10 @@
     <row r="25" spans="2:39" ht="14.1" customHeight="1">
       <c r="B25" s="25"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="136"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="136"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
@@ -7829,10 +9356,10 @@
     <row r="26" spans="2:39" ht="14.1" customHeight="1">
       <c r="B26" s="25"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="136"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="136"/>
-      <c r="G26" s="136"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
@@ -7861,10 +9388,10 @@
     <row r="27" spans="2:39" ht="14.1" customHeight="1">
       <c r="B27" s="25"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="136"/>
-      <c r="E27" s="136"/>
-      <c r="F27" s="136"/>
-      <c r="G27" s="136"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
@@ -7893,10 +9420,10 @@
     <row r="28" spans="2:39" ht="14.1" customHeight="1">
       <c r="B28" s="25"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="136"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="136"/>
-      <c r="G28" s="136"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
@@ -7925,10 +9452,10 @@
     <row r="29" spans="2:39" ht="14.1" customHeight="1">
       <c r="B29" s="25"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="136"/>
-      <c r="E29" s="136"/>
-      <c r="F29" s="136"/>
-      <c r="G29" s="136"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
@@ -7958,33 +9485,41 @@
     <row r="31" spans="2:39" ht="14.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="T5:AG5"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I7:N7"/>
-    <mergeCell ref="O7:S7"/>
-    <mergeCell ref="T7:AG7"/>
-    <mergeCell ref="AH7:AM7"/>
-    <mergeCell ref="AH5:AM5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:N6"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="T6:AG6"/>
-    <mergeCell ref="AH6:AM6"/>
-    <mergeCell ref="AH9:AM9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="AH8:AM8"/>
-    <mergeCell ref="O8:S8"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:S17"/>
+    <mergeCell ref="T17:AG17"/>
+    <mergeCell ref="AH17:AM17"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:S16"/>
+    <mergeCell ref="T16:AG16"/>
+    <mergeCell ref="AH16:AM16"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:AG15"/>
+    <mergeCell ref="AH15:AM15"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:AG14"/>
+    <mergeCell ref="AH14:AM14"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:AG13"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T12:AG12"/>
+    <mergeCell ref="AH12:AM12"/>
+    <mergeCell ref="AH11:AM11"/>
+    <mergeCell ref="I10:N10"/>
+    <mergeCell ref="T10:AG10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="O10:S10"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B9:H9"/>
@@ -7994,41 +9529,33 @@
     <mergeCell ref="I11:N11"/>
     <mergeCell ref="O11:S11"/>
     <mergeCell ref="T11:AG11"/>
-    <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="T10:AG10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T12:AG12"/>
-    <mergeCell ref="AH12:AM12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:AG13"/>
-    <mergeCell ref="AH13:AM13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:AG14"/>
-    <mergeCell ref="AH14:AM14"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:AG15"/>
-    <mergeCell ref="AH15:AM15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="T16:AG16"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:S17"/>
-    <mergeCell ref="T17:AG17"/>
-    <mergeCell ref="AH17:AM17"/>
+    <mergeCell ref="AH9:AM9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="AH8:AM8"/>
+    <mergeCell ref="O8:S8"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="AH5:AM5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="T6:AG6"/>
+    <mergeCell ref="AH6:AM6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I7:N7"/>
+    <mergeCell ref="O7:S7"/>
+    <mergeCell ref="T7:AG7"/>
+    <mergeCell ref="AH7:AM7"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="T5:AG5"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8088,15 +9615,15 @@
     </row>
     <row r="2" spans="1:40" ht="14.1" customHeight="1">
       <c r="A2" s="8"/>
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="133" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -8132,13 +9659,13 @@
     </row>
     <row r="3" spans="1:40" ht="14.1" customHeight="1">
       <c r="A3" s="8"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -9466,15 +10993,15 @@
     </row>
     <row r="2" spans="1:40" ht="14.1" customHeight="1">
       <c r="A2" s="8"/>
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -9510,13 +11037,13 @@
     </row>
     <row r="3" spans="1:40" ht="14.1" customHeight="1">
       <c r="A3" s="8"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -9644,10 +11171,10 @@
     </row>
     <row r="6" spans="1:40" ht="14.1" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" s="137">
+      <c r="B6" s="140">
         <v>1</v>
       </c>
-      <c r="C6" s="138"/>
+      <c r="C6" s="141"/>
       <c r="D6" s="29" t="s">
         <v>56</v>
       </c>
@@ -9694,10 +11221,10 @@
     </row>
     <row r="7" spans="1:40" ht="14.1" customHeight="1">
       <c r="A7" s="8"/>
-      <c r="B7" s="137">
+      <c r="B7" s="140">
         <v>2</v>
       </c>
-      <c r="C7" s="138"/>
+      <c r="C7" s="141"/>
       <c r="D7" s="29" t="s">
         <v>57</v>
       </c>
@@ -9744,10 +11271,10 @@
     </row>
     <row r="8" spans="1:40" ht="14.1" customHeight="1">
       <c r="A8" s="8"/>
-      <c r="B8" s="137">
+      <c r="B8" s="140">
         <v>3</v>
       </c>
-      <c r="C8" s="138"/>
+      <c r="C8" s="141"/>
       <c r="D8" s="29" t="s">
         <v>49</v>
       </c>
@@ -9794,10 +11321,10 @@
     </row>
     <row r="9" spans="1:40" ht="14.1" customHeight="1">
       <c r="A9" s="8"/>
-      <c r="B9" s="137">
+      <c r="B9" s="140">
         <v>4</v>
       </c>
-      <c r="C9" s="138"/>
+      <c r="C9" s="141"/>
       <c r="D9" s="29" t="s">
         <v>94</v>
       </c>
@@ -9844,10 +11371,10 @@
     </row>
     <row r="10" spans="1:40" ht="14.1" customHeight="1">
       <c r="A10" s="8"/>
-      <c r="B10" s="137">
+      <c r="B10" s="140">
         <v>5</v>
       </c>
-      <c r="C10" s="138"/>
+      <c r="C10" s="141"/>
       <c r="D10" s="29" t="s">
         <v>50</v>
       </c>
@@ -9894,10 +11421,10 @@
     </row>
     <row r="11" spans="1:40" ht="14.1" customHeight="1">
       <c r="A11" s="8"/>
-      <c r="B11" s="137">
+      <c r="B11" s="140">
         <v>6</v>
       </c>
-      <c r="C11" s="138"/>
+      <c r="C11" s="141"/>
       <c r="D11" s="29" t="s">
         <v>51</v>
       </c>
@@ -9944,10 +11471,10 @@
     </row>
     <row r="12" spans="1:40" s="70" customFormat="1" ht="14.1" customHeight="1">
       <c r="A12" s="32"/>
-      <c r="B12" s="137">
+      <c r="B12" s="140">
         <v>7</v>
       </c>
-      <c r="C12" s="138"/>
+      <c r="C12" s="141"/>
       <c r="D12" s="29" t="s">
         <v>105</v>
       </c>
@@ -9994,10 +11521,10 @@
     </row>
     <row r="13" spans="1:40" ht="14.1" customHeight="1">
       <c r="A13" s="8"/>
-      <c r="B13" s="137">
+      <c r="B13" s="140">
         <v>8</v>
       </c>
-      <c r="C13" s="138"/>
+      <c r="C13" s="141"/>
       <c r="D13" s="29" t="s">
         <v>140</v>
       </c>
@@ -10911,21 +12438,21 @@
     </row>
     <row r="2" spans="1:41" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
       <c r="O2" s="32"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -10955,19 +12482,19 @@
     </row>
     <row r="3" spans="1:41" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
       <c r="O3" s="32"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -11119,8 +12646,8 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="139"/>
-      <c r="W6" s="140"/>
+      <c r="V6" s="87"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -11172,8 +12699,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="140"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="88"/>
       <c r="X7" s="29" t="s">
         <v>24</v>
       </c>
@@ -11225,8 +12752,8 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="140"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="88"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -11276,10 +12803,10 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="139">
+      <c r="V9" s="87">
         <v>100</v>
       </c>
-      <c r="W9" s="140"/>
+      <c r="W9" s="88"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -11331,10 +12858,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="139">
+      <c r="V10" s="87">
         <v>100</v>
       </c>
-      <c r="W10" s="140"/>
+      <c r="W10" s="88"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -11384,10 +12911,10 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="139">
+      <c r="V11" s="87">
         <v>8</v>
       </c>
-      <c r="W11" s="140"/>
+      <c r="W11" s="88"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -11412,7 +12939,7 @@
     <row r="12" spans="1:41" ht="14.1" customHeight="1">
       <c r="A12" s="32"/>
       <c r="B12" s="29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
@@ -11422,7 +12949,7 @@
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="29" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
@@ -11431,14 +12958,14 @@
       <c r="O12" s="30"/>
       <c r="P12" s="30"/>
       <c r="Q12" s="29" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R12" s="30"/>
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="140"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="88"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -11463,7 +12990,7 @@
     <row r="13" spans="1:41" ht="14.1" customHeight="1">
       <c r="A13" s="32"/>
       <c r="B13" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
@@ -11473,7 +13000,7 @@
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
       <c r="J13" s="29" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -11482,14 +13009,14 @@
       <c r="O13" s="30"/>
       <c r="P13" s="30"/>
       <c r="Q13" s="29" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R13" s="30"/>
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="140"/>
+      <c r="V13" s="87"/>
+      <c r="W13" s="88"/>
       <c r="X13" s="29" t="s">
         <v>25</v>
       </c>
@@ -11539,8 +13066,8 @@
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31"/>
-      <c r="V14" s="139"/>
-      <c r="W14" s="140"/>
+      <c r="V14" s="87"/>
+      <c r="W14" s="88"/>
       <c r="X14" s="29" t="s">
         <v>25</v>
       </c>
@@ -11592,8 +13119,8 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31"/>
-      <c r="V15" s="139"/>
-      <c r="W15" s="140"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="88"/>
       <c r="X15" s="29" t="s">
         <v>25</v>
       </c>
@@ -11645,8 +13172,8 @@
       <c r="S16" s="30"/>
       <c r="T16" s="30"/>
       <c r="U16" s="31"/>
-      <c r="V16" s="139"/>
-      <c r="W16" s="140"/>
+      <c r="V16" s="87"/>
+      <c r="W16" s="88"/>
       <c r="X16" s="29" t="s">
         <v>25</v>
       </c>
@@ -11751,8 +13278,8 @@
       <c r="S18" s="30"/>
       <c r="T18" s="30"/>
       <c r="U18" s="31"/>
-      <c r="V18" s="139"/>
-      <c r="W18" s="140"/>
+      <c r="V18" s="87"/>
+      <c r="W18" s="88"/>
       <c r="X18" s="29" t="s">
         <v>25</v>
       </c>
@@ -12469,8 +13996,8 @@
     <mergeCell ref="V11:W11"/>
     <mergeCell ref="V7:W7"/>
     <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V13:W13"/>
     <mergeCell ref="V12:W12"/>
-    <mergeCell ref="V13:W13"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12530,23 +14057,23 @@
     </row>
     <row r="2" spans="1:41" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
       <c r="Q2" s="32"/>
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
@@ -12574,21 +14101,21 @@
     </row>
     <row r="3" spans="1:41" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
       <c r="S3" s="32"/>
@@ -12738,8 +14265,8 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="139"/>
-      <c r="W6" s="140"/>
+      <c r="V6" s="87"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="29" t="s">
         <v>76</v>
       </c>
@@ -12791,8 +14318,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="140"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="88"/>
       <c r="X7" s="29" t="s">
         <v>167</v>
       </c>
@@ -12844,10 +14371,10 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="139">
+      <c r="V8" s="87">
         <v>20</v>
       </c>
-      <c r="W8" s="140"/>
+      <c r="W8" s="88"/>
       <c r="X8" s="29" t="s">
         <v>76</v>
       </c>
@@ -12898,8 +14425,8 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="140"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="88"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -12950,8 +14477,8 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="139"/>
-      <c r="W10" s="140"/>
+      <c r="V10" s="87"/>
+      <c r="W10" s="88"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -13002,10 +14529,10 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="139">
+      <c r="V11" s="87">
         <v>20</v>
       </c>
-      <c r="W11" s="140"/>
+      <c r="W11" s="88"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -13054,8 +14581,8 @@
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="140"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="88"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -14032,23 +15559,23 @@
     </row>
     <row r="2" spans="1:41" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
       <c r="Q2" s="32"/>
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
@@ -14076,21 +15603,21 @@
     </row>
     <row r="3" spans="1:41" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
       <c r="S3" s="32"/>
@@ -14240,10 +15767,10 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="139">
+      <c r="V6" s="87">
         <v>20</v>
       </c>
-      <c r="W6" s="140"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -14292,8 +15819,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="140"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="88"/>
       <c r="X7" s="29" t="s">
         <v>78</v>
       </c>
@@ -14345,10 +15872,10 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="139">
+      <c r="V8" s="87">
         <v>100</v>
       </c>
-      <c r="W8" s="140"/>
+      <c r="W8" s="88"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -14398,10 +15925,10 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="139">
+      <c r="V9" s="87">
         <v>100</v>
       </c>
-      <c r="W9" s="140"/>
+      <c r="W9" s="88"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -14451,10 +15978,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="139">
+      <c r="V10" s="87">
         <v>100</v>
       </c>
-      <c r="W10" s="140"/>
+      <c r="W10" s="88"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -14506,8 +16033,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="140"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="88"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -14559,8 +16086,8 @@
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="140"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="88"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -14612,8 +16139,8 @@
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="140"/>
+      <c r="V13" s="87"/>
+      <c r="W13" s="88"/>
       <c r="X13" s="29" t="s">
         <v>25</v>
       </c>
@@ -14664,8 +16191,8 @@
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31"/>
-      <c r="V14" s="139"/>
-      <c r="W14" s="140"/>
+      <c r="V14" s="87"/>
+      <c r="W14" s="88"/>
       <c r="X14" s="29" t="s">
         <v>25</v>
       </c>
@@ -14716,10 +16243,10 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31"/>
-      <c r="V15" s="139">
+      <c r="V15" s="87">
         <v>20</v>
       </c>
-      <c r="W15" s="140"/>
+      <c r="W15" s="88"/>
       <c r="X15" s="29" t="s">
         <v>25</v>
       </c>
@@ -14768,8 +16295,8 @@
       <c r="S16" s="30"/>
       <c r="T16" s="30"/>
       <c r="U16" s="31"/>
-      <c r="V16" s="139"/>
-      <c r="W16" s="140"/>
+      <c r="V16" s="87"/>
+      <c r="W16" s="88"/>
       <c r="X16" s="29" t="s">
         <v>25</v>
       </c>
@@ -15497,6 +17024,1248 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5DE7B0-A097-47C4-994E-9AD67B30BEB7}">
+  <dimension ref="A1:AO28"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="40" width="3.33203125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="32"/>
+      <c r="AK1" s="32"/>
+      <c r="AL1" s="32"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="32"/>
+    </row>
+    <row r="2" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A2" s="32"/>
+      <c r="B2" s="89" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+    </row>
+    <row r="3" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A3" s="32"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="89"/>
+      <c r="X3" s="89"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AL3" s="32"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+    </row>
+    <row r="4" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+    </row>
+    <row r="5" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A5" s="32"/>
+      <c r="B5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="W5" s="47"/>
+      <c r="X5" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE5" s="50"/>
+      <c r="AF5" s="50"/>
+      <c r="AG5" s="50"/>
+      <c r="AH5" s="50"/>
+      <c r="AI5" s="50"/>
+      <c r="AJ5" s="50"/>
+      <c r="AK5" s="50"/>
+      <c r="AL5" s="50"/>
+      <c r="AM5" s="51"/>
+      <c r="AN5" s="32"/>
+    </row>
+    <row r="6" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A6" s="32"/>
+      <c r="B6" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="87">
+        <v>20</v>
+      </c>
+      <c r="W6" s="88"/>
+      <c r="X6" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="30"/>
+      <c r="AM6" s="31"/>
+      <c r="AN6" s="32"/>
+    </row>
+    <row r="7" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A7" s="32"/>
+      <c r="B7" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="87">
+        <v>100</v>
+      </c>
+      <c r="W7" s="88"/>
+      <c r="X7" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="31"/>
+      <c r="AN7" s="32"/>
+      <c r="AO7" s="27"/>
+    </row>
+    <row r="8" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A8" s="32"/>
+      <c r="B8" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="30"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="30"/>
+      <c r="AJ8" s="30"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="30"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="32"/>
+    </row>
+    <row r="9" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A9" s="32"/>
+      <c r="B9" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="31"/>
+      <c r="AN9" s="32"/>
+    </row>
+    <row r="10" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A10" s="32"/>
+      <c r="B10" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="87">
+        <v>20</v>
+      </c>
+      <c r="W10" s="88"/>
+      <c r="X10" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="30"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="30"/>
+      <c r="AJ10" s="30"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="30"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="32"/>
+    </row>
+    <row r="11" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A11" s="32"/>
+      <c r="B11" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="30"/>
+      <c r="AJ11" s="30"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="30"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="32"/>
+    </row>
+    <row r="12" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A12" s="32"/>
+      <c r="AN12" s="32"/>
+    </row>
+    <row r="13" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="59"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="142"/>
+      <c r="W13" s="142"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
+      <c r="AE13" s="32"/>
+      <c r="AF13" s="32"/>
+      <c r="AG13" s="32"/>
+      <c r="AH13" s="32"/>
+      <c r="AI13" s="32"/>
+      <c r="AJ13" s="32"/>
+      <c r="AK13" s="32"/>
+      <c r="AL13" s="32"/>
+      <c r="AM13" s="32"/>
+      <c r="AN13" s="32"/>
+    </row>
+    <row r="14" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="45"/>
+      <c r="T14" s="45"/>
+      <c r="U14" s="45"/>
+      <c r="V14" s="45"/>
+      <c r="W14" s="45"/>
+      <c r="X14" s="45"/>
+      <c r="Y14" s="45"/>
+      <c r="Z14" s="45"/>
+      <c r="AA14" s="45"/>
+      <c r="AB14" s="45"/>
+      <c r="AC14" s="45"/>
+      <c r="AD14" s="45"/>
+      <c r="AE14" s="45"/>
+      <c r="AF14" s="32"/>
+      <c r="AG14" s="32"/>
+      <c r="AH14" s="32"/>
+      <c r="AI14" s="32"/>
+      <c r="AJ14" s="32"/>
+      <c r="AK14" s="32"/>
+      <c r="AL14" s="32"/>
+      <c r="AM14" s="32"/>
+      <c r="AN14" s="32"/>
+    </row>
+    <row r="15" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+      <c r="AA15" s="32"/>
+      <c r="AB15" s="32"/>
+      <c r="AC15" s="32"/>
+      <c r="AD15" s="32"/>
+      <c r="AE15" s="32"/>
+      <c r="AF15" s="32"/>
+      <c r="AG15" s="32"/>
+      <c r="AH15" s="32"/>
+      <c r="AI15" s="32"/>
+      <c r="AJ15" s="32"/>
+      <c r="AK15" s="32"/>
+      <c r="AL15" s="32"/>
+      <c r="AM15" s="32"/>
+      <c r="AN15" s="32"/>
+    </row>
+    <row r="16" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="32"/>
+      <c r="AD16" s="32"/>
+      <c r="AE16" s="32"/>
+      <c r="AF16" s="32"/>
+      <c r="AG16" s="32"/>
+      <c r="AH16" s="32"/>
+      <c r="AI16" s="32"/>
+      <c r="AJ16" s="32"/>
+      <c r="AK16" s="32"/>
+      <c r="AL16" s="32"/>
+      <c r="AM16" s="32"/>
+      <c r="AN16" s="32"/>
+    </row>
+    <row r="17" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A17" s="32"/>
+      <c r="B17" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="52"/>
+      <c r="R17" s="52"/>
+      <c r="S17" s="52"/>
+      <c r="T17" s="52"/>
+      <c r="U17" s="52"/>
+      <c r="V17" s="52"/>
+      <c r="W17" s="52"/>
+      <c r="X17" s="52"/>
+      <c r="Y17" s="52"/>
+      <c r="Z17" s="52"/>
+      <c r="AA17" s="52"/>
+      <c r="AB17" s="52"/>
+      <c r="AC17" s="52"/>
+      <c r="AD17" s="52"/>
+      <c r="AE17" s="52"/>
+      <c r="AF17" s="47"/>
+      <c r="AG17" s="47"/>
+      <c r="AH17" s="47"/>
+      <c r="AI17" s="47"/>
+      <c r="AJ17" s="47"/>
+      <c r="AK17" s="47"/>
+      <c r="AL17" s="47"/>
+      <c r="AM17" s="48"/>
+      <c r="AN17" s="32"/>
+    </row>
+    <row r="18" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A18" s="32"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="55"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+      <c r="V18" s="56"/>
+      <c r="W18" s="56"/>
+      <c r="X18" s="54"/>
+      <c r="Y18" s="54"/>
+      <c r="Z18" s="54"/>
+      <c r="AA18" s="54"/>
+      <c r="AB18" s="54"/>
+      <c r="AC18" s="54"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="54"/>
+      <c r="AF18" s="54"/>
+      <c r="AG18" s="54"/>
+      <c r="AH18" s="54"/>
+      <c r="AI18" s="54"/>
+      <c r="AJ18" s="54"/>
+      <c r="AK18" s="54"/>
+      <c r="AL18" s="54"/>
+      <c r="AM18" s="57"/>
+      <c r="AN18" s="32"/>
+    </row>
+    <row r="19" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A19" s="32"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="X19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="60"/>
+      <c r="AA19" s="60"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="32"/>
+      <c r="AF19" s="32"/>
+      <c r="AG19" s="32"/>
+      <c r="AH19" s="32"/>
+      <c r="AI19" s="32"/>
+      <c r="AJ19" s="32"/>
+      <c r="AK19" s="32"/>
+      <c r="AL19" s="32"/>
+      <c r="AM19" s="61"/>
+      <c r="AN19" s="32"/>
+    </row>
+    <row r="20" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A20" s="32"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="60"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="63"/>
+      <c r="V20" s="63"/>
+      <c r="W20" s="63"/>
+      <c r="X20" s="63"/>
+      <c r="Y20" s="63"/>
+      <c r="Z20" s="63"/>
+      <c r="AA20" s="60"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="32"/>
+      <c r="AJ20" s="32"/>
+      <c r="AK20" s="32"/>
+      <c r="AL20" s="32"/>
+      <c r="AM20" s="61"/>
+      <c r="AN20" s="32"/>
+    </row>
+    <row r="21" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A21" s="32"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="60"/>
+      <c r="Q21" s="60"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="60"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="60"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="60"/>
+      <c r="AA21" s="60"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="32"/>
+      <c r="AJ21" s="32"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="32"/>
+      <c r="AM21" s="61"/>
+      <c r="AN21" s="32"/>
+    </row>
+    <row r="22" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A22" s="32"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="60"/>
+      <c r="Z22" s="60"/>
+      <c r="AA22" s="60"/>
+      <c r="AB22" s="32"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
+      <c r="AG22" s="32"/>
+      <c r="AH22" s="32"/>
+      <c r="AI22" s="32"/>
+      <c r="AJ22" s="32"/>
+      <c r="AK22" s="32"/>
+      <c r="AL22" s="32"/>
+      <c r="AM22" s="61"/>
+      <c r="AN22" s="32"/>
+    </row>
+    <row r="23" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A23" s="32"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="60"/>
+      <c r="X23" s="60"/>
+      <c r="Y23" s="60"/>
+      <c r="Z23" s="60"/>
+      <c r="AA23" s="60"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
+      <c r="AG23" s="32"/>
+      <c r="AH23" s="32"/>
+      <c r="AI23" s="32"/>
+      <c r="AJ23" s="32"/>
+      <c r="AK23" s="32"/>
+      <c r="AL23" s="32"/>
+      <c r="AM23" s="61"/>
+      <c r="AN23" s="32"/>
+    </row>
+    <row r="24" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A24" s="32"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AA24" s="60"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="32"/>
+      <c r="AG24" s="32"/>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="32"/>
+      <c r="AJ24" s="32"/>
+      <c r="AK24" s="32"/>
+      <c r="AL24" s="32"/>
+      <c r="AM24" s="61"/>
+      <c r="AN24" s="32"/>
+    </row>
+    <row r="25" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A25" s="32"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="60"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="60"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="60"/>
+      <c r="V25" s="60"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="60"/>
+      <c r="Z25" s="60"/>
+      <c r="AA25" s="60"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
+      <c r="AG25" s="32"/>
+      <c r="AH25" s="32"/>
+      <c r="AI25" s="32"/>
+      <c r="AJ25" s="32"/>
+      <c r="AK25" s="32"/>
+      <c r="AL25" s="32"/>
+      <c r="AM25" s="61"/>
+      <c r="AN25" s="32"/>
+    </row>
+    <row r="26" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A26" s="32"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="66"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="65"/>
+      <c r="R26" s="65"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="65"/>
+      <c r="U26" s="65"/>
+      <c r="V26" s="65"/>
+      <c r="W26" s="65"/>
+      <c r="X26" s="65"/>
+      <c r="Y26" s="65"/>
+      <c r="Z26" s="65"/>
+      <c r="AA26" s="65"/>
+      <c r="AB26" s="65"/>
+      <c r="AC26" s="65"/>
+      <c r="AD26" s="65"/>
+      <c r="AE26" s="65"/>
+      <c r="AF26" s="65"/>
+      <c r="AG26" s="65"/>
+      <c r="AH26" s="65"/>
+      <c r="AI26" s="65"/>
+      <c r="AJ26" s="65"/>
+      <c r="AK26" s="65"/>
+      <c r="AL26" s="65"/>
+      <c r="AM26" s="67"/>
+      <c r="AN26" s="32"/>
+    </row>
+    <row r="27" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A27" s="32"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="32"/>
+      <c r="AN27" s="32"/>
+    </row>
+    <row r="28" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A28" s="32"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
+      <c r="AG28" s="32"/>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="32"/>
+      <c r="AJ28" s="32"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="32"/>
+      <c r="AM28" s="32"/>
+      <c r="AN28" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="B2:X3"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5FCE4-25D4-4DF4-B755-48F88E4D77C4}">
   <dimension ref="A1:AO33"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
@@ -15548,29 +18317,29 @@
     </row>
     <row r="2" spans="1:41" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
-      <c r="S2" s="141"/>
-      <c r="T2" s="141"/>
-      <c r="U2" s="141"/>
-      <c r="V2" s="141"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
       <c r="W2" s="32"/>
       <c r="X2" s="32"/>
       <c r="Y2" s="32"/>
@@ -15592,27 +18361,27 @@
     </row>
     <row r="3" spans="1:41" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="141"/>
-      <c r="R3" s="141"/>
-      <c r="S3" s="141"/>
-      <c r="T3" s="141"/>
-      <c r="U3" s="141"/>
-      <c r="V3" s="141"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
       <c r="W3" s="32"/>
       <c r="X3" s="32"/>
       <c r="Y3" s="32"/>
@@ -15756,10 +18525,10 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="139">
+      <c r="V6" s="87">
         <v>20</v>
       </c>
-      <c r="W6" s="140"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="29" t="s">
         <v>76</v>
       </c>
@@ -15811,8 +18580,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="140"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="88"/>
       <c r="X7" s="29" t="s">
         <v>76</v>
       </c>
@@ -15863,8 +18632,8 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="140"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="88"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -15915,8 +18684,8 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="140"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="88"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -15967,10 +18736,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="139">
+      <c r="V10" s="87">
         <v>20</v>
       </c>
-      <c r="W10" s="140"/>
+      <c r="W10" s="88"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -16019,8 +18788,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="140"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="88"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -16946,1509 +19715,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DBED43-E4B6-4D24-AC88-89CDEF182391}">
-  <dimension ref="A1:AP33"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
-  <cols>
-    <col min="1" max="40" width="3.33203125" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A1" s="32"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-    </row>
-    <row r="2" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A2" s="32"/>
-      <c r="B2" s="141" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-    </row>
-    <row r="3" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A3" s="32"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-    </row>
-    <row r="4" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="32"/>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="32"/>
-      <c r="AM4" s="32"/>
-      <c r="AN4" s="32"/>
-    </row>
-    <row r="5" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A5" s="32"/>
-      <c r="B5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="W5" s="47"/>
-      <c r="X5" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE5" s="50"/>
-      <c r="AF5" s="50"/>
-      <c r="AG5" s="50"/>
-      <c r="AH5" s="50"/>
-      <c r="AI5" s="50"/>
-      <c r="AJ5" s="50"/>
-      <c r="AK5" s="50"/>
-      <c r="AL5" s="50"/>
-      <c r="AM5" s="51"/>
-      <c r="AN5" s="32"/>
-    </row>
-    <row r="6" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="139"/>
-      <c r="W6" s="140"/>
-      <c r="X6" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="31"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="27"/>
-    </row>
-    <row r="7" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="139">
-        <v>20</v>
-      </c>
-      <c r="W7" s="140"/>
-      <c r="X7" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="30"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="32"/>
-    </row>
-    <row r="8" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="140"/>
-      <c r="X8" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="30"/>
-      <c r="AD8" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AH8" s="30"/>
-      <c r="AI8" s="30"/>
-      <c r="AJ8" s="30"/>
-      <c r="AK8" s="30"/>
-      <c r="AL8" s="30"/>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="32"/>
-    </row>
-    <row r="9" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A9" s="32"/>
-      <c r="B9" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="140"/>
-      <c r="X9" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="30"/>
-      <c r="AD9" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="30"/>
-      <c r="AH9" s="30"/>
-      <c r="AI9" s="30"/>
-      <c r="AJ9" s="30"/>
-      <c r="AK9" s="30"/>
-      <c r="AL9" s="30"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="32"/>
-    </row>
-    <row r="10" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A10" s="32"/>
-      <c r="B10" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="139">
-        <v>20</v>
-      </c>
-      <c r="W10" s="140"/>
-      <c r="X10" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="29"/>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="30"/>
-      <c r="AK10" s="30"/>
-      <c r="AL10" s="30"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="32"/>
-    </row>
-    <row r="11" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A11" s="32"/>
-      <c r="B11" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="140"/>
-      <c r="X11" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="30"/>
-      <c r="AK11" s="30"/>
-      <c r="AL11" s="30"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="32"/>
-    </row>
-    <row r="12" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
-      <c r="O12" s="32"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="32"/>
-      <c r="S12" s="32"/>
-      <c r="T12" s="32"/>
-      <c r="U12" s="32"/>
-      <c r="V12" s="142"/>
-      <c r="W12" s="142"/>
-      <c r="X12" s="32"/>
-      <c r="Y12" s="32"/>
-      <c r="Z12" s="32"/>
-      <c r="AA12" s="32"/>
-      <c r="AB12" s="32"/>
-      <c r="AC12" s="32"/>
-      <c r="AD12" s="68"/>
-      <c r="AE12" s="68"/>
-      <c r="AF12" s="68"/>
-      <c r="AG12" s="68"/>
-      <c r="AH12" s="68"/>
-      <c r="AI12" s="68"/>
-      <c r="AJ12" s="68"/>
-      <c r="AK12" s="68"/>
-      <c r="AL12" s="68"/>
-      <c r="AM12" s="68"/>
-      <c r="AN12" s="32"/>
-    </row>
-    <row r="13" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="32"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="32"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="32"/>
-      <c r="AE13" s="32"/>
-      <c r="AF13" s="32"/>
-      <c r="AG13" s="32"/>
-      <c r="AH13" s="32"/>
-      <c r="AI13" s="32"/>
-      <c r="AJ13" s="32"/>
-      <c r="AK13" s="32"/>
-      <c r="AL13" s="32"/>
-      <c r="AM13" s="32"/>
-      <c r="AN13" s="32"/>
-    </row>
-    <row r="14" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="32"/>
-      <c r="U14" s="32"/>
-      <c r="V14" s="32"/>
-      <c r="W14" s="32"/>
-      <c r="X14" s="32"/>
-      <c r="Y14" s="32"/>
-      <c r="Z14" s="32"/>
-      <c r="AA14" s="32"/>
-      <c r="AB14" s="32"/>
-      <c r="AC14" s="32"/>
-      <c r="AD14" s="32"/>
-      <c r="AE14" s="32"/>
-      <c r="AF14" s="32"/>
-      <c r="AG14" s="32"/>
-      <c r="AH14" s="32"/>
-      <c r="AI14" s="32"/>
-      <c r="AJ14" s="32"/>
-      <c r="AK14" s="32"/>
-      <c r="AL14" s="32"/>
-      <c r="AM14" s="32"/>
-      <c r="AN14" s="32"/>
-    </row>
-    <row r="15" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="32"/>
-      <c r="AA15" s="32"/>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="32"/>
-      <c r="AD15" s="32"/>
-      <c r="AE15" s="32"/>
-      <c r="AF15" s="32"/>
-      <c r="AG15" s="32"/>
-      <c r="AH15" s="32"/>
-      <c r="AI15" s="32"/>
-      <c r="AJ15" s="32"/>
-      <c r="AK15" s="32"/>
-      <c r="AL15" s="32"/>
-      <c r="AM15" s="32"/>
-      <c r="AN15" s="32"/>
-    </row>
-    <row r="16" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
-      <c r="U16" s="45"/>
-      <c r="V16" s="45"/>
-      <c r="W16" s="45"/>
-      <c r="X16" s="45"/>
-      <c r="Y16" s="45"/>
-      <c r="Z16" s="45"/>
-      <c r="AA16" s="45"/>
-      <c r="AB16" s="45"/>
-      <c r="AC16" s="45"/>
-      <c r="AD16" s="45"/>
-      <c r="AE16" s="45"/>
-      <c r="AF16" s="32"/>
-      <c r="AG16" s="32"/>
-      <c r="AH16" s="32"/>
-      <c r="AI16" s="32"/>
-      <c r="AJ16" s="32"/>
-      <c r="AK16" s="32"/>
-      <c r="AL16" s="32"/>
-      <c r="AM16" s="32"/>
-      <c r="AN16" s="32"/>
-    </row>
-    <row r="17" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="59"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="142"/>
-      <c r="W17" s="142"/>
-      <c r="X17" s="32"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-      <c r="AA17" s="32"/>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="32"/>
-      <c r="AE17" s="32"/>
-      <c r="AF17" s="32"/>
-      <c r="AG17" s="32"/>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="32"/>
-      <c r="AJ17" s="32"/>
-      <c r="AK17" s="32"/>
-      <c r="AL17" s="32"/>
-      <c r="AM17" s="32"/>
-      <c r="AN17" s="32"/>
-    </row>
-    <row r="18" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-      <c r="U18" s="45"/>
-      <c r="V18" s="45"/>
-      <c r="W18" s="45"/>
-      <c r="X18" s="45"/>
-      <c r="Y18" s="45"/>
-      <c r="Z18" s="45"/>
-      <c r="AA18" s="45"/>
-      <c r="AB18" s="45"/>
-      <c r="AC18" s="45"/>
-      <c r="AD18" s="45"/>
-      <c r="AE18" s="45"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="32"/>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="32"/>
-      <c r="AJ18" s="32"/>
-      <c r="AK18" s="32"/>
-      <c r="AL18" s="32"/>
-      <c r="AM18" s="32"/>
-      <c r="AN18" s="32"/>
-    </row>
-    <row r="19" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A19" s="32"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="32"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="32"/>
-      <c r="U19" s="32"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="32"/>
-      <c r="AA19" s="32"/>
-      <c r="AB19" s="32"/>
-      <c r="AC19" s="32"/>
-      <c r="AD19" s="32"/>
-      <c r="AE19" s="32"/>
-      <c r="AF19" s="32"/>
-      <c r="AG19" s="32"/>
-      <c r="AH19" s="32"/>
-      <c r="AI19" s="32"/>
-      <c r="AJ19" s="32"/>
-      <c r="AK19" s="32"/>
-      <c r="AL19" s="32"/>
-      <c r="AM19" s="32"/>
-      <c r="AN19" s="32"/>
-    </row>
-    <row r="20" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="32"/>
-      <c r="U20" s="32"/>
-      <c r="V20" s="32"/>
-      <c r="W20" s="32"/>
-      <c r="X20" s="32"/>
-      <c r="Y20" s="32"/>
-      <c r="Z20" s="32"/>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="32"/>
-      <c r="AC20" s="32"/>
-      <c r="AD20" s="32"/>
-      <c r="AE20" s="32"/>
-      <c r="AF20" s="32"/>
-      <c r="AG20" s="32"/>
-      <c r="AH20" s="32"/>
-      <c r="AI20" s="32"/>
-      <c r="AJ20" s="32"/>
-      <c r="AK20" s="32"/>
-      <c r="AL20" s="32"/>
-      <c r="AM20" s="32"/>
-      <c r="AN20" s="32"/>
-    </row>
-    <row r="21" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="32"/>
-      <c r="T21" s="32"/>
-      <c r="U21" s="32"/>
-      <c r="V21" s="32"/>
-      <c r="W21" s="32"/>
-      <c r="X21" s="32"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="32"/>
-      <c r="AE21" s="32"/>
-      <c r="AF21" s="32"/>
-      <c r="AG21" s="32"/>
-      <c r="AH21" s="32"/>
-      <c r="AI21" s="32"/>
-      <c r="AJ21" s="32"/>
-      <c r="AK21" s="32"/>
-      <c r="AL21" s="32"/>
-      <c r="AM21" s="32"/>
-      <c r="AN21" s="32"/>
-    </row>
-    <row r="22" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A22" s="32"/>
-      <c r="B22" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="52"/>
-      <c r="R22" s="52"/>
-      <c r="S22" s="52"/>
-      <c r="T22" s="52"/>
-      <c r="U22" s="52"/>
-      <c r="V22" s="52"/>
-      <c r="W22" s="52"/>
-      <c r="X22" s="52"/>
-      <c r="Y22" s="52"/>
-      <c r="Z22" s="52"/>
-      <c r="AA22" s="52"/>
-      <c r="AB22" s="52"/>
-      <c r="AC22" s="52"/>
-      <c r="AD22" s="52"/>
-      <c r="AE22" s="52"/>
-      <c r="AF22" s="47"/>
-      <c r="AG22" s="47"/>
-      <c r="AH22" s="47"/>
-      <c r="AI22" s="47"/>
-      <c r="AJ22" s="47"/>
-      <c r="AK22" s="47"/>
-      <c r="AL22" s="47"/>
-      <c r="AM22" s="48"/>
-      <c r="AN22" s="32"/>
-    </row>
-    <row r="23" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A23" s="32"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="54"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="56"/>
-      <c r="W23" s="56"/>
-      <c r="X23" s="54"/>
-      <c r="Y23" s="54"/>
-      <c r="Z23" s="54"/>
-      <c r="AA23" s="54"/>
-      <c r="AB23" s="54"/>
-      <c r="AC23" s="54"/>
-      <c r="AD23" s="54"/>
-      <c r="AE23" s="54"/>
-      <c r="AF23" s="54"/>
-      <c r="AG23" s="54"/>
-      <c r="AH23" s="54"/>
-      <c r="AI23" s="54"/>
-      <c r="AJ23" s="54"/>
-      <c r="AK23" s="54"/>
-      <c r="AL23" s="54"/>
-      <c r="AM23" s="57"/>
-      <c r="AN23" s="32"/>
-    </row>
-    <row r="24" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A24" s="32"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="60"/>
-      <c r="M24" s="60"/>
-      <c r="N24" s="60"/>
-      <c r="O24" s="60"/>
-      <c r="P24" s="60"/>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="60"/>
-      <c r="S24" s="60"/>
-      <c r="T24" s="60"/>
-      <c r="U24" s="60"/>
-      <c r="V24" s="60"/>
-      <c r="W24" s="60"/>
-      <c r="X24" s="60"/>
-      <c r="Y24" s="60"/>
-      <c r="Z24" s="60"/>
-      <c r="AA24" s="60"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="32"/>
-      <c r="AD24" s="32"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="32"/>
-      <c r="AG24" s="32"/>
-      <c r="AH24" s="32"/>
-      <c r="AI24" s="32"/>
-      <c r="AJ24" s="32"/>
-      <c r="AK24" s="32"/>
-      <c r="AL24" s="32"/>
-      <c r="AM24" s="61"/>
-      <c r="AN24" s="32"/>
-      <c r="AP24" s="38"/>
-    </row>
-    <row r="25" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A25" s="32"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="62"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="60"/>
-      <c r="U25" s="63"/>
-      <c r="V25" s="63"/>
-      <c r="W25" s="63"/>
-      <c r="X25" s="63"/>
-      <c r="Y25" s="63"/>
-      <c r="Z25" s="63"/>
-      <c r="AA25" s="60"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="32"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="32"/>
-      <c r="AG25" s="32"/>
-      <c r="AH25" s="32"/>
-      <c r="AI25" s="32"/>
-      <c r="AJ25" s="32"/>
-      <c r="AK25" s="32"/>
-      <c r="AL25" s="32"/>
-      <c r="AM25" s="61"/>
-      <c r="AN25" s="32"/>
-      <c r="AP25" s="38"/>
-    </row>
-    <row r="26" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A26" s="32"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="60"/>
-      <c r="O26" s="60"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="60"/>
-      <c r="T26" s="60"/>
-      <c r="U26" s="60"/>
-      <c r="V26" s="60"/>
-      <c r="W26" s="60"/>
-      <c r="X26" s="60"/>
-      <c r="Y26" s="60"/>
-      <c r="Z26" s="60"/>
-      <c r="AA26" s="60"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="32"/>
-      <c r="AG26" s="32"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="32"/>
-      <c r="AJ26" s="32"/>
-      <c r="AK26" s="32"/>
-      <c r="AL26" s="32"/>
-      <c r="AM26" s="61"/>
-      <c r="AN26" s="32"/>
-      <c r="AP26" s="38"/>
-    </row>
-    <row r="27" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A27" s="32"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="60"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="60"/>
-      <c r="Y27" s="60"/>
-      <c r="Z27" s="60"/>
-      <c r="AA27" s="60"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="32"/>
-      <c r="AG27" s="32"/>
-      <c r="AH27" s="32"/>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="61"/>
-      <c r="AN27" s="32"/>
-      <c r="AP27" s="38"/>
-    </row>
-    <row r="28" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A28" s="32"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="60"/>
-      <c r="O28" s="60"/>
-      <c r="P28" s="60"/>
-      <c r="Q28" s="60"/>
-      <c r="R28" s="60"/>
-      <c r="S28" s="60"/>
-      <c r="T28" s="60"/>
-      <c r="U28" s="60"/>
-      <c r="V28" s="60"/>
-      <c r="W28" s="60"/>
-      <c r="X28" s="60"/>
-      <c r="Y28" s="60"/>
-      <c r="Z28" s="60"/>
-      <c r="AA28" s="60"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="32"/>
-      <c r="AG28" s="32"/>
-      <c r="AH28" s="32"/>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="61"/>
-      <c r="AN28" s="32"/>
-      <c r="AP28" s="38"/>
-    </row>
-    <row r="29" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A29" s="32"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="60"/>
-      <c r="O29" s="60"/>
-      <c r="P29" s="60"/>
-      <c r="Q29" s="60"/>
-      <c r="R29" s="60"/>
-      <c r="S29" s="60"/>
-      <c r="T29" s="60"/>
-      <c r="U29" s="60"/>
-      <c r="V29" s="60"/>
-      <c r="W29" s="60"/>
-      <c r="X29" s="60"/>
-      <c r="Y29" s="60"/>
-      <c r="Z29" s="60"/>
-      <c r="AA29" s="60"/>
-      <c r="AB29" s="32"/>
-      <c r="AC29" s="32"/>
-      <c r="AD29" s="32"/>
-      <c r="AE29" s="32"/>
-      <c r="AF29" s="32"/>
-      <c r="AG29" s="32"/>
-      <c r="AH29" s="32"/>
-      <c r="AI29" s="32"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
-      <c r="AL29" s="32"/>
-      <c r="AM29" s="61"/>
-      <c r="AN29" s="32"/>
-      <c r="AP29" s="38"/>
-    </row>
-    <row r="30" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A30" s="32"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="60"/>
-      <c r="O30" s="60"/>
-      <c r="P30" s="60"/>
-      <c r="Q30" s="60"/>
-      <c r="R30" s="60"/>
-      <c r="S30" s="60"/>
-      <c r="T30" s="60"/>
-      <c r="U30" s="60"/>
-      <c r="V30" s="60"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="60"/>
-      <c r="Y30" s="60"/>
-      <c r="Z30" s="60"/>
-      <c r="AA30" s="60"/>
-      <c r="AB30" s="32"/>
-      <c r="AC30" s="32"/>
-      <c r="AD30" s="32"/>
-      <c r="AE30" s="32"/>
-      <c r="AF30" s="32"/>
-      <c r="AG30" s="32"/>
-      <c r="AH30" s="32"/>
-      <c r="AI30" s="32"/>
-      <c r="AJ30" s="32"/>
-      <c r="AK30" s="32"/>
-      <c r="AL30" s="32"/>
-      <c r="AM30" s="61"/>
-      <c r="AN30" s="32"/>
-      <c r="AP30" s="38"/>
-    </row>
-    <row r="31" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A31" s="32"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
-      <c r="N31" s="65"/>
-      <c r="O31" s="66"/>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="65"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
-      <c r="Z31" s="65"/>
-      <c r="AA31" s="65"/>
-      <c r="AB31" s="65"/>
-      <c r="AC31" s="65"/>
-      <c r="AD31" s="65"/>
-      <c r="AE31" s="65"/>
-      <c r="AF31" s="65"/>
-      <c r="AG31" s="65"/>
-      <c r="AH31" s="65"/>
-      <c r="AI31" s="65"/>
-      <c r="AJ31" s="65"/>
-      <c r="AK31" s="65"/>
-      <c r="AL31" s="65"/>
-      <c r="AM31" s="67"/>
-      <c r="AN31" s="32"/>
-      <c r="AP31" s="38"/>
-    </row>
-    <row r="32" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
-      <c r="P32" s="32"/>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="32"/>
-      <c r="T32" s="32"/>
-      <c r="U32" s="32"/>
-      <c r="V32" s="32"/>
-      <c r="W32" s="32"/>
-      <c r="X32" s="32"/>
-      <c r="Y32" s="32"/>
-      <c r="Z32" s="32"/>
-      <c r="AA32" s="32"/>
-      <c r="AB32" s="32"/>
-      <c r="AC32" s="32"/>
-      <c r="AD32" s="32"/>
-      <c r="AE32" s="32"/>
-      <c r="AF32" s="32"/>
-      <c r="AG32" s="32"/>
-      <c r="AH32" s="32"/>
-      <c r="AI32" s="32"/>
-      <c r="AJ32" s="32"/>
-      <c r="AK32" s="32"/>
-      <c r="AL32" s="32"/>
-      <c r="AM32" s="32"/>
-      <c r="AN32" s="32"/>
-      <c r="AP32" s="38"/>
-    </row>
-    <row r="33" spans="1:42" ht="14.1" customHeight="1">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="32"/>
-      <c r="T33" s="32"/>
-      <c r="U33" s="32"/>
-      <c r="V33" s="32"/>
-      <c r="W33" s="32"/>
-      <c r="X33" s="32"/>
-      <c r="Y33" s="32"/>
-      <c r="Z33" s="32"/>
-      <c r="AA33" s="32"/>
-      <c r="AB33" s="32"/>
-      <c r="AC33" s="32"/>
-      <c r="AD33" s="32"/>
-      <c r="AE33" s="32"/>
-      <c r="AF33" s="32"/>
-      <c r="AG33" s="32"/>
-      <c r="AH33" s="32"/>
-      <c r="AI33" s="32"/>
-      <c r="AJ33" s="32"/>
-      <c r="AK33" s="32"/>
-      <c r="AL33" s="32"/>
-      <c r="AM33" s="32"/>
-      <c r="AN33" s="32"/>
-      <c r="AP33" s="38"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B2:P3"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V7:W7"/>
-  </mergeCells>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-</worksheet>
 </file>
--- a/機能設計書/DB設計書.xlsx
+++ b/機能設計書/DB設計書.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FileManagementSystem_Doc\機能設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C269131E-2CDD-47EF-B5F4-DEED4D41CE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0377743B-3697-4A2C-A509-1B49343A8666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="10" r:id="rId1"/>
     <sheet name="更新履歴" sheetId="13" r:id="rId2"/>
     <sheet name="DB規約" sheetId="23" r:id="rId3"/>
     <sheet name="DB一覧" sheetId="11" r:id="rId4"/>
-    <sheet name="ファイル管理" sheetId="14" r:id="rId5"/>
-    <sheet name="会議参加者" sheetId="20" r:id="rId6"/>
+    <sheet name="会議参加者" sheetId="20" r:id="rId5"/>
+    <sheet name="ファイル管理" sheetId="14" r:id="rId6"/>
     <sheet name="ユーザーマスタ" sheetId="15" r:id="rId7"/>
     <sheet name="外部ユーザーマスタ" sheetId="25" r:id="rId8"/>
     <sheet name="所属管理マスタ" sheetId="21" r:id="rId9"/>
@@ -28,13 +28,13 @@
     <sheet name="排他ロック" sheetId="24" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">DB一覧!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">DB一覧!$A$1:$AN$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">DB規約!$A$1:$AN$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">ファイル管理!$A$1:$AN$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">ファイル管理!$A$1:$AN$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">ユーザーマスタ!$A$1:$AN$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">ログ!$A$1:$AN$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">会議参加者!$A$1:$AN$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">外部ユーザーマスタ!$A$1:$AN$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">会議参加者!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">外部ユーザーマスタ!$A$1:$AN$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">更新履歴!$A$1:$AN$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">所属マスタ!$A$1:$AN$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">所属管理マスタ!$A$1:$AN$33</definedName>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="182">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -1090,10 +1090,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>time</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>藤田</t>
     <rPh sb="0" eb="2">
       <t>フジタ</t>
@@ -1121,16 +1117,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>外部ユーザーのため所属マスタにおけるIDは「10:組織に属さない」となる</t>
-    <rPh sb="0" eb="2">
-      <t>ガイブ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ショゾク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>時間自</t>
     <rPh sb="0" eb="2">
       <t>ジカン</t>
@@ -1147,6 +1133,48 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>イタル</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フォーマットはhhmm</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>m_external_user</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外部ユーザーマスタ</t>
+    <rPh sb="0" eb="2">
+      <t>ガイブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外部ユーザーのユーザー情報</t>
+    <rPh sb="0" eb="2">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外部ユーザーマスタの追加</t>
+    <rPh sb="0" eb="2">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>藤原</t>
+    <rPh sb="0" eb="2">
+      <t>フジワラ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1636,7 +1664,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1872,15 +1900,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2007,18 +2026,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2028,14 +2035,35 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2045,6 +2073,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2287,271 +2318,271 @@
     <row r="7" spans="2:31" ht="14.1" customHeight="1"/>
     <row r="8" spans="2:31" ht="14.1" customHeight="1" thickBot="1"/>
     <row r="9" spans="2:31" ht="14.1" customHeight="1" thickTop="1">
-      <c r="J9" s="119" t="s">
+      <c r="J9" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="120"/>
-      <c r="O9" s="120"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="120"/>
-      <c r="R9" s="120"/>
-      <c r="S9" s="120"/>
-      <c r="T9" s="120"/>
-      <c r="U9" s="120"/>
-      <c r="V9" s="120"/>
-      <c r="W9" s="120"/>
-      <c r="X9" s="120"/>
-      <c r="Y9" s="120"/>
-      <c r="Z9" s="120"/>
-      <c r="AA9" s="120"/>
-      <c r="AB9" s="120"/>
-      <c r="AC9" s="120"/>
-      <c r="AD9" s="120"/>
-      <c r="AE9" s="121"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="117"/>
+      <c r="R9" s="117"/>
+      <c r="S9" s="117"/>
+      <c r="T9" s="117"/>
+      <c r="U9" s="117"/>
+      <c r="V9" s="117"/>
+      <c r="W9" s="117"/>
+      <c r="X9" s="117"/>
+      <c r="Y9" s="117"/>
+      <c r="Z9" s="117"/>
+      <c r="AA9" s="117"/>
+      <c r="AB9" s="117"/>
+      <c r="AC9" s="117"/>
+      <c r="AD9" s="117"/>
+      <c r="AE9" s="118"/>
     </row>
     <row r="10" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J10" s="122"/>
-      <c r="K10" s="123"/>
-      <c r="L10" s="123"/>
-      <c r="M10" s="123"/>
-      <c r="N10" s="123"/>
-      <c r="O10" s="123"/>
-      <c r="P10" s="123"/>
-      <c r="Q10" s="123"/>
-      <c r="R10" s="123"/>
-      <c r="S10" s="123"/>
-      <c r="T10" s="123"/>
-      <c r="U10" s="123"/>
-      <c r="V10" s="123"/>
-      <c r="W10" s="123"/>
-      <c r="X10" s="123"/>
-      <c r="Y10" s="123"/>
-      <c r="Z10" s="123"/>
-      <c r="AA10" s="123"/>
-      <c r="AB10" s="123"/>
-      <c r="AC10" s="123"/>
-      <c r="AD10" s="123"/>
-      <c r="AE10" s="124"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="120"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="120"/>
+      <c r="O10" s="120"/>
+      <c r="P10" s="120"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="120"/>
+      <c r="S10" s="120"/>
+      <c r="T10" s="120"/>
+      <c r="U10" s="120"/>
+      <c r="V10" s="120"/>
+      <c r="W10" s="120"/>
+      <c r="X10" s="120"/>
+      <c r="Y10" s="120"/>
+      <c r="Z10" s="120"/>
+      <c r="AA10" s="120"/>
+      <c r="AB10" s="120"/>
+      <c r="AC10" s="120"/>
+      <c r="AD10" s="120"/>
+      <c r="AE10" s="121"/>
     </row>
     <row r="11" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J11" s="122"/>
-      <c r="K11" s="123"/>
-      <c r="L11" s="123"/>
-      <c r="M11" s="123"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="123"/>
-      <c r="R11" s="123"/>
-      <c r="S11" s="123"/>
-      <c r="T11" s="123"/>
-      <c r="U11" s="123"/>
-      <c r="V11" s="123"/>
-      <c r="W11" s="123"/>
-      <c r="X11" s="123"/>
-      <c r="Y11" s="123"/>
-      <c r="Z11" s="123"/>
-      <c r="AA11" s="123"/>
-      <c r="AB11" s="123"/>
-      <c r="AC11" s="123"/>
-      <c r="AD11" s="123"/>
-      <c r="AE11" s="124"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="120"/>
+      <c r="L11" s="120"/>
+      <c r="M11" s="120"/>
+      <c r="N11" s="120"/>
+      <c r="O11" s="120"/>
+      <c r="P11" s="120"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="120"/>
+      <c r="S11" s="120"/>
+      <c r="T11" s="120"/>
+      <c r="U11" s="120"/>
+      <c r="V11" s="120"/>
+      <c r="W11" s="120"/>
+      <c r="X11" s="120"/>
+      <c r="Y11" s="120"/>
+      <c r="Z11" s="120"/>
+      <c r="AA11" s="120"/>
+      <c r="AB11" s="120"/>
+      <c r="AC11" s="120"/>
+      <c r="AD11" s="120"/>
+      <c r="AE11" s="121"/>
     </row>
     <row r="12" spans="2:31" ht="14.1" customHeight="1">
       <c r="B12" s="3"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="123"/>
-      <c r="M12" s="123"/>
-      <c r="N12" s="123"/>
-      <c r="O12" s="123"/>
-      <c r="P12" s="123"/>
-      <c r="Q12" s="123"/>
-      <c r="R12" s="123"/>
-      <c r="S12" s="123"/>
-      <c r="T12" s="123"/>
-      <c r="U12" s="123"/>
-      <c r="V12" s="123"/>
-      <c r="W12" s="123"/>
-      <c r="X12" s="123"/>
-      <c r="Y12" s="123"/>
-      <c r="Z12" s="123"/>
-      <c r="AA12" s="123"/>
-      <c r="AB12" s="123"/>
-      <c r="AC12" s="123"/>
-      <c r="AD12" s="123"/>
-      <c r="AE12" s="124"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="120"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="120"/>
+      <c r="P12" s="120"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="120"/>
+      <c r="S12" s="120"/>
+      <c r="T12" s="120"/>
+      <c r="U12" s="120"/>
+      <c r="V12" s="120"/>
+      <c r="W12" s="120"/>
+      <c r="X12" s="120"/>
+      <c r="Y12" s="120"/>
+      <c r="Z12" s="120"/>
+      <c r="AA12" s="120"/>
+      <c r="AB12" s="120"/>
+      <c r="AC12" s="120"/>
+      <c r="AD12" s="120"/>
+      <c r="AE12" s="121"/>
     </row>
     <row r="13" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J13" s="122"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="123"/>
-      <c r="M13" s="123"/>
-      <c r="N13" s="123"/>
-      <c r="O13" s="123"/>
-      <c r="P13" s="123"/>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="123"/>
-      <c r="S13" s="123"/>
-      <c r="T13" s="123"/>
-      <c r="U13" s="123"/>
-      <c r="V13" s="123"/>
-      <c r="W13" s="123"/>
-      <c r="X13" s="123"/>
-      <c r="Y13" s="123"/>
-      <c r="Z13" s="123"/>
-      <c r="AA13" s="123"/>
-      <c r="AB13" s="123"/>
-      <c r="AC13" s="123"/>
-      <c r="AD13" s="123"/>
-      <c r="AE13" s="124"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="120"/>
+      <c r="Q13" s="120"/>
+      <c r="R13" s="120"/>
+      <c r="S13" s="120"/>
+      <c r="T13" s="120"/>
+      <c r="U13" s="120"/>
+      <c r="V13" s="120"/>
+      <c r="W13" s="120"/>
+      <c r="X13" s="120"/>
+      <c r="Y13" s="120"/>
+      <c r="Z13" s="120"/>
+      <c r="AA13" s="120"/>
+      <c r="AB13" s="120"/>
+      <c r="AC13" s="120"/>
+      <c r="AD13" s="120"/>
+      <c r="AE13" s="121"/>
     </row>
     <row r="14" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J14" s="122"/>
-      <c r="K14" s="123"/>
-      <c r="L14" s="123"/>
-      <c r="M14" s="123"/>
-      <c r="N14" s="123"/>
-      <c r="O14" s="123"/>
-      <c r="P14" s="123"/>
-      <c r="Q14" s="123"/>
-      <c r="R14" s="123"/>
-      <c r="S14" s="123"/>
-      <c r="T14" s="123"/>
-      <c r="U14" s="123"/>
-      <c r="V14" s="123"/>
-      <c r="W14" s="123"/>
-      <c r="X14" s="123"/>
-      <c r="Y14" s="123"/>
-      <c r="Z14" s="123"/>
-      <c r="AA14" s="123"/>
-      <c r="AB14" s="123"/>
-      <c r="AC14" s="123"/>
-      <c r="AD14" s="123"/>
-      <c r="AE14" s="124"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="120"/>
+      <c r="P14" s="120"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="120"/>
+      <c r="S14" s="120"/>
+      <c r="T14" s="120"/>
+      <c r="U14" s="120"/>
+      <c r="V14" s="120"/>
+      <c r="W14" s="120"/>
+      <c r="X14" s="120"/>
+      <c r="Y14" s="120"/>
+      <c r="Z14" s="120"/>
+      <c r="AA14" s="120"/>
+      <c r="AB14" s="120"/>
+      <c r="AC14" s="120"/>
+      <c r="AD14" s="120"/>
+      <c r="AE14" s="121"/>
     </row>
     <row r="15" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J15" s="122"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="123"/>
-      <c r="M15" s="123"/>
-      <c r="N15" s="123"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="123"/>
-      <c r="Q15" s="123"/>
-      <c r="R15" s="123"/>
-      <c r="S15" s="123"/>
-      <c r="T15" s="123"/>
-      <c r="U15" s="123"/>
-      <c r="V15" s="123"/>
-      <c r="W15" s="123"/>
-      <c r="X15" s="123"/>
-      <c r="Y15" s="123"/>
-      <c r="Z15" s="123"/>
-      <c r="AA15" s="123"/>
-      <c r="AB15" s="123"/>
-      <c r="AC15" s="123"/>
-      <c r="AD15" s="123"/>
-      <c r="AE15" s="124"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="120"/>
+      <c r="L15" s="120"/>
+      <c r="M15" s="120"/>
+      <c r="N15" s="120"/>
+      <c r="O15" s="120"/>
+      <c r="P15" s="120"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="120"/>
+      <c r="S15" s="120"/>
+      <c r="T15" s="120"/>
+      <c r="U15" s="120"/>
+      <c r="V15" s="120"/>
+      <c r="W15" s="120"/>
+      <c r="X15" s="120"/>
+      <c r="Y15" s="120"/>
+      <c r="Z15" s="120"/>
+      <c r="AA15" s="120"/>
+      <c r="AB15" s="120"/>
+      <c r="AC15" s="120"/>
+      <c r="AD15" s="120"/>
+      <c r="AE15" s="121"/>
     </row>
     <row r="16" spans="2:31" ht="14.1" customHeight="1">
-      <c r="J16" s="122"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="123"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="123"/>
-      <c r="P16" s="123"/>
-      <c r="Q16" s="123"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="123"/>
-      <c r="T16" s="123"/>
-      <c r="U16" s="123"/>
-      <c r="V16" s="123"/>
-      <c r="W16" s="123"/>
-      <c r="X16" s="123"/>
-      <c r="Y16" s="123"/>
-      <c r="Z16" s="123"/>
-      <c r="AA16" s="123"/>
-      <c r="AB16" s="123"/>
-      <c r="AC16" s="123"/>
-      <c r="AD16" s="123"/>
-      <c r="AE16" s="124"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="120"/>
+      <c r="S16" s="120"/>
+      <c r="T16" s="120"/>
+      <c r="U16" s="120"/>
+      <c r="V16" s="120"/>
+      <c r="W16" s="120"/>
+      <c r="X16" s="120"/>
+      <c r="Y16" s="120"/>
+      <c r="Z16" s="120"/>
+      <c r="AA16" s="120"/>
+      <c r="AB16" s="120"/>
+      <c r="AC16" s="120"/>
+      <c r="AD16" s="120"/>
+      <c r="AE16" s="121"/>
     </row>
     <row r="17" spans="6:31" ht="14.1" customHeight="1">
-      <c r="J17" s="122"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="123"/>
-      <c r="N17" s="123"/>
-      <c r="O17" s="123"/>
-      <c r="P17" s="123"/>
-      <c r="Q17" s="123"/>
-      <c r="R17" s="123"/>
-      <c r="S17" s="123"/>
-      <c r="T17" s="123"/>
-      <c r="U17" s="123"/>
-      <c r="V17" s="123"/>
-      <c r="W17" s="123"/>
-      <c r="X17" s="123"/>
-      <c r="Y17" s="123"/>
-      <c r="Z17" s="123"/>
-      <c r="AA17" s="123"/>
-      <c r="AB17" s="123"/>
-      <c r="AC17" s="123"/>
-      <c r="AD17" s="123"/>
-      <c r="AE17" s="124"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="120"/>
+      <c r="P17" s="120"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="120"/>
+      <c r="S17" s="120"/>
+      <c r="T17" s="120"/>
+      <c r="U17" s="120"/>
+      <c r="V17" s="120"/>
+      <c r="W17" s="120"/>
+      <c r="X17" s="120"/>
+      <c r="Y17" s="120"/>
+      <c r="Z17" s="120"/>
+      <c r="AA17" s="120"/>
+      <c r="AB17" s="120"/>
+      <c r="AC17" s="120"/>
+      <c r="AD17" s="120"/>
+      <c r="AE17" s="121"/>
     </row>
     <row r="18" spans="6:31" ht="14.1" customHeight="1">
-      <c r="J18" s="122"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="123"/>
-      <c r="M18" s="123"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="123"/>
-      <c r="Q18" s="123"/>
-      <c r="R18" s="123"/>
-      <c r="S18" s="123"/>
-      <c r="T18" s="123"/>
-      <c r="U18" s="123"/>
-      <c r="V18" s="123"/>
-      <c r="W18" s="123"/>
-      <c r="X18" s="123"/>
-      <c r="Y18" s="123"/>
-      <c r="Z18" s="123"/>
-      <c r="AA18" s="123"/>
-      <c r="AB18" s="123"/>
-      <c r="AC18" s="123"/>
-      <c r="AD18" s="123"/>
-      <c r="AE18" s="124"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
+      <c r="P18" s="120"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="120"/>
+      <c r="S18" s="120"/>
+      <c r="T18" s="120"/>
+      <c r="U18" s="120"/>
+      <c r="V18" s="120"/>
+      <c r="W18" s="120"/>
+      <c r="X18" s="120"/>
+      <c r="Y18" s="120"/>
+      <c r="Z18" s="120"/>
+      <c r="AA18" s="120"/>
+      <c r="AB18" s="120"/>
+      <c r="AC18" s="120"/>
+      <c r="AD18" s="120"/>
+      <c r="AE18" s="121"/>
     </row>
     <row r="19" spans="6:31" ht="14.1" customHeight="1" thickBot="1">
-      <c r="J19" s="125"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="126"/>
-      <c r="O19" s="126"/>
-      <c r="P19" s="126"/>
-      <c r="Q19" s="126"/>
-      <c r="R19" s="126"/>
-      <c r="S19" s="126"/>
-      <c r="T19" s="126"/>
-      <c r="U19" s="126"/>
-      <c r="V19" s="126"/>
-      <c r="W19" s="126"/>
-      <c r="X19" s="126"/>
-      <c r="Y19" s="126"/>
-      <c r="Z19" s="126"/>
-      <c r="AA19" s="126"/>
-      <c r="AB19" s="126"/>
-      <c r="AC19" s="126"/>
-      <c r="AD19" s="126"/>
-      <c r="AE19" s="127"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="123"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="123"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="123"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="123"/>
+      <c r="R19" s="123"/>
+      <c r="S19" s="123"/>
+      <c r="T19" s="123"/>
+      <c r="U19" s="123"/>
+      <c r="V19" s="123"/>
+      <c r="W19" s="123"/>
+      <c r="X19" s="123"/>
+      <c r="Y19" s="123"/>
+      <c r="Z19" s="123"/>
+      <c r="AA19" s="123"/>
+      <c r="AB19" s="123"/>
+      <c r="AC19" s="123"/>
+      <c r="AD19" s="123"/>
+      <c r="AE19" s="124"/>
     </row>
     <row r="20" spans="6:31" ht="14.1" customHeight="1" thickTop="1"/>
     <row r="21" spans="6:31" ht="14.1" customHeight="1">
@@ -2585,18 +2616,18 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="10" t="str">
         <f>"第"&amp;TEXT(MAX(更新履歴!B4:B22),"#0.0")&amp;"版"</f>
-        <v>第1.1版</v>
+        <v>第1.2版</v>
       </c>
       <c r="S23" s="9"/>
       <c r="T23" s="9"/>
-      <c r="U23" s="128">
+      <c r="U23" s="125">
         <f>MAX(更新履歴!I6:N27)</f>
-        <v>46086</v>
-      </c>
-      <c r="V23" s="128"/>
-      <c r="W23" s="128"/>
-      <c r="X23" s="128"/>
-      <c r="Y23" s="128"/>
+        <v>46087</v>
+      </c>
+      <c r="V23" s="125"/>
+      <c r="W23" s="125"/>
+      <c r="X23" s="125"/>
+      <c r="Y23" s="125"/>
       <c r="Z23" s="11"/>
       <c r="AA23" s="4"/>
     </row>
@@ -2620,77 +2651,77 @@
     <row r="25" spans="6:31" ht="14.1" customHeight="1">
       <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="129" t="s">
+      <c r="O25" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="P25" s="130"/>
-      <c r="Q25" s="130"/>
-      <c r="R25" s="131"/>
-      <c r="S25" s="129" t="s">
+      <c r="P25" s="127"/>
+      <c r="Q25" s="127"/>
+      <c r="R25" s="128"/>
+      <c r="S25" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="130"/>
-      <c r="U25" s="130"/>
-      <c r="V25" s="131"/>
-      <c r="W25" s="129" t="s">
+      <c r="T25" s="127"/>
+      <c r="U25" s="127"/>
+      <c r="V25" s="128"/>
+      <c r="W25" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="X25" s="130"/>
-      <c r="Y25" s="130"/>
-      <c r="Z25" s="131"/>
+      <c r="X25" s="127"/>
+      <c r="Y25" s="127"/>
+      <c r="Z25" s="128"/>
       <c r="AA25" s="4"/>
     </row>
     <row r="26" spans="6:31" ht="14.1" customHeight="1">
       <c r="M26" s="8"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="92" t="s">
+      <c r="O26" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="P26" s="93"/>
-      <c r="Q26" s="93"/>
-      <c r="R26" s="94"/>
-      <c r="S26" s="101"/>
-      <c r="T26" s="102"/>
-      <c r="U26" s="102"/>
-      <c r="V26" s="103"/>
-      <c r="W26" s="110"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="111"/>
-      <c r="Z26" s="112"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="90"/>
+      <c r="R26" s="91"/>
+      <c r="S26" s="98"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="100"/>
+      <c r="W26" s="107"/>
+      <c r="X26" s="108"/>
+      <c r="Y26" s="108"/>
+      <c r="Z26" s="109"/>
       <c r="AA26" s="4"/>
     </row>
     <row r="27" spans="6:31" ht="14.1" customHeight="1">
       <c r="M27" s="8"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="95"/>
-      <c r="P27" s="96"/>
-      <c r="Q27" s="96"/>
-      <c r="R27" s="97"/>
-      <c r="S27" s="104"/>
-      <c r="T27" s="105"/>
-      <c r="U27" s="105"/>
-      <c r="V27" s="106"/>
-      <c r="W27" s="113"/>
-      <c r="X27" s="114"/>
-      <c r="Y27" s="114"/>
-      <c r="Z27" s="115"/>
+      <c r="O27" s="92"/>
+      <c r="P27" s="93"/>
+      <c r="Q27" s="93"/>
+      <c r="R27" s="94"/>
+      <c r="S27" s="101"/>
+      <c r="T27" s="102"/>
+      <c r="U27" s="102"/>
+      <c r="V27" s="103"/>
+      <c r="W27" s="110"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="111"/>
+      <c r="Z27" s="112"/>
       <c r="AA27" s="4"/>
     </row>
     <row r="28" spans="6:31" ht="14.1" customHeight="1">
       <c r="M28" s="8"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="98"/>
-      <c r="P28" s="99"/>
-      <c r="Q28" s="99"/>
-      <c r="R28" s="100"/>
-      <c r="S28" s="107"/>
-      <c r="T28" s="108"/>
-      <c r="U28" s="108"/>
-      <c r="V28" s="109"/>
-      <c r="W28" s="116"/>
-      <c r="X28" s="117"/>
-      <c r="Y28" s="117"/>
-      <c r="Z28" s="118"/>
+      <c r="O28" s="95"/>
+      <c r="P28" s="96"/>
+      <c r="Q28" s="96"/>
+      <c r="R28" s="97"/>
+      <c r="S28" s="104"/>
+      <c r="T28" s="105"/>
+      <c r="U28" s="105"/>
+      <c r="V28" s="106"/>
+      <c r="W28" s="113"/>
+      <c r="X28" s="114"/>
+      <c r="Y28" s="114"/>
+      <c r="Z28" s="115"/>
       <c r="AA28" s="4"/>
     </row>
     <row r="29" spans="6:31" ht="14.1" customHeight="1">
@@ -2729,36 +2760,36 @@
     <row r="31" spans="6:31" ht="14.1" customHeight="1">
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
-      <c r="O31" s="90" t="s">
+      <c r="O31" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="P31" s="91"/>
-      <c r="Q31" s="91"/>
-      <c r="R31" s="91"/>
-      <c r="S31" s="91"/>
-      <c r="T31" s="91"/>
-      <c r="U31" s="91"/>
-      <c r="V31" s="91"/>
-      <c r="W31" s="91"/>
-      <c r="X31" s="91"/>
-      <c r="Y31" s="91"/>
-      <c r="Z31" s="91"/>
+      <c r="P31" s="88"/>
+      <c r="Q31" s="88"/>
+      <c r="R31" s="88"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+      <c r="Y31" s="88"/>
+      <c r="Z31" s="88"/>
     </row>
     <row r="32" spans="6:31" ht="14.1" customHeight="1">
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
-      <c r="O32" s="91"/>
-      <c r="P32" s="91"/>
-      <c r="Q32" s="91"/>
-      <c r="R32" s="91"/>
-      <c r="S32" s="91"/>
-      <c r="T32" s="91"/>
-      <c r="U32" s="91"/>
-      <c r="V32" s="91"/>
-      <c r="W32" s="91"/>
-      <c r="X32" s="91"/>
-      <c r="Y32" s="91"/>
-      <c r="Z32" s="91"/>
+      <c r="O32" s="88"/>
+      <c r="P32" s="88"/>
+      <c r="Q32" s="88"/>
+      <c r="R32" s="88"/>
+      <c r="S32" s="88"/>
+      <c r="T32" s="88"/>
+      <c r="U32" s="88"/>
+      <c r="V32" s="88"/>
+      <c r="W32" s="88"/>
+      <c r="X32" s="88"/>
+      <c r="Y32" s="88"/>
+      <c r="Z32" s="88"/>
     </row>
     <row r="33" ht="14.1" customHeight="1"/>
   </sheetData>
@@ -2831,23 +2862,23 @@
     </row>
     <row r="2" spans="1:41" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
       <c r="Q2" s="32"/>
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
@@ -2875,21 +2906,21 @@
     </row>
     <row r="3" spans="1:41" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
       <c r="S3" s="32"/>
@@ -3039,8 +3070,8 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="87"/>
-      <c r="W6" s="88"/>
+      <c r="V6" s="139"/>
+      <c r="W6" s="140"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -3092,10 +3123,10 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="87">
+      <c r="V7" s="139">
         <v>20</v>
       </c>
-      <c r="W7" s="88"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="29" t="s">
         <v>25</v>
       </c>
@@ -3144,8 +3175,8 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="88"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="140"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -3196,8 +3227,8 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="88"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="140"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -3248,10 +3279,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="87">
+      <c r="V10" s="139">
         <v>20</v>
       </c>
-      <c r="W10" s="88"/>
+      <c r="W10" s="140"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3331,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="88"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="140"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -4336,23 +4367,23 @@
     </row>
     <row r="2" spans="1:71" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
       <c r="Q2" s="32"/>
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
@@ -4380,21 +4411,21 @@
     </row>
     <row r="3" spans="1:71" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
       <c r="S3" s="32"/>
@@ -4544,8 +4575,8 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="87"/>
-      <c r="W6" s="88"/>
+      <c r="V6" s="139"/>
+      <c r="W6" s="140"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -4597,10 +4628,10 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="87">
+      <c r="V7" s="139">
         <v>20</v>
       </c>
-      <c r="W7" s="88"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="29" t="s">
         <v>25</v>
       </c>
@@ -4649,8 +4680,8 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="88"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="140"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -4701,8 +4732,8 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="88"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="140"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -4753,10 +4784,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="87">
+      <c r="V10" s="139">
         <v>20</v>
       </c>
-      <c r="W10" s="88"/>
+      <c r="W10" s="140"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -4805,8 +4836,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="88"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="140"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -6348,44 +6379,44 @@
   <sheetData>
     <row r="1" spans="2:41" ht="14.1" customHeight="1"/>
     <row r="2" spans="2:41" ht="14.1" customHeight="1">
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="141" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="141"/>
     </row>
     <row r="3" spans="2:41" ht="14.1" customHeight="1">
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="89"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="141"/>
     </row>
     <row r="4" spans="2:41" ht="14.1" customHeight="1"/>
     <row r="5" spans="2:41" ht="14.1" customHeight="1">
@@ -6467,8 +6498,8 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="87"/>
-      <c r="W6" s="88"/>
+      <c r="V6" s="139"/>
+      <c r="W6" s="140"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -6515,8 +6546,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="88"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="29" t="s">
         <v>25</v>
       </c>
@@ -6565,10 +6596,10 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="87">
+      <c r="V8" s="139">
         <v>2000</v>
       </c>
-      <c r="W8" s="88"/>
+      <c r="W8" s="140"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -6616,10 +6647,10 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="87">
+      <c r="V9" s="139">
         <v>100</v>
       </c>
-      <c r="W9" s="88"/>
+      <c r="W9" s="140"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -6666,10 +6697,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="87">
+      <c r="V10" s="139">
         <v>50</v>
       </c>
-      <c r="W10" s="88"/>
+      <c r="W10" s="140"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -6718,8 +6749,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="88"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="140"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -6768,8 +6799,8 @@
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="88"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="140"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -6818,8 +6849,8 @@
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="88"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="140"/>
       <c r="X13" s="29" t="s">
         <v>25</v>
       </c>
@@ -6868,10 +6899,10 @@
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31"/>
-      <c r="V14" s="87">
+      <c r="V14" s="139">
         <v>20</v>
       </c>
-      <c r="W14" s="88"/>
+      <c r="W14" s="140"/>
       <c r="X14" s="29" t="s">
         <v>25</v>
       </c>
@@ -6918,8 +6949,8 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="88"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="140"/>
       <c r="X15" s="29" t="s">
         <v>25</v>
       </c>
@@ -7492,48 +7523,48 @@
   <sheetData>
     <row r="1" spans="2:41" ht="14.1" customHeight="1"/>
     <row r="2" spans="2:41" ht="14.1" customHeight="1">
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="141"/>
+      <c r="S2" s="141"/>
+      <c r="T2" s="141"/>
     </row>
     <row r="3" spans="2:41" ht="14.1" customHeight="1">
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="89"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="141"/>
+      <c r="S3" s="141"/>
+      <c r="T3" s="141"/>
     </row>
     <row r="4" spans="2:41" ht="14.1" customHeight="1"/>
     <row r="5" spans="2:41" ht="14.1" customHeight="1">
@@ -7615,10 +7646,10 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="87">
+      <c r="V6" s="139">
         <v>100</v>
       </c>
-      <c r="W6" s="88"/>
+      <c r="W6" s="140"/>
       <c r="X6" s="29" t="s">
         <v>143</v>
       </c>
@@ -7665,10 +7696,10 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="87">
+      <c r="V7" s="139">
         <v>100</v>
       </c>
-      <c r="W7" s="88"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="29" t="s">
         <v>143</v>
       </c>
@@ -7910,8 +7941,8 @@
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="88"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="140"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -7960,8 +7991,8 @@
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="88"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="140"/>
       <c r="X13" s="29" t="s">
         <v>25</v>
       </c>
@@ -8010,10 +8041,10 @@
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31"/>
-      <c r="V14" s="87">
+      <c r="V14" s="139">
         <v>20</v>
       </c>
-      <c r="W14" s="88"/>
+      <c r="W14" s="140"/>
       <c r="X14" s="29" t="s">
         <v>25</v>
       </c>
@@ -8060,8 +8091,8 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="88"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="140"/>
       <c r="X15" s="29" t="s">
         <v>25</v>
       </c>
@@ -8624,15 +8655,15 @@
   <sheetData>
     <row r="1" spans="2:39" ht="14.1" customHeight="1"/>
     <row r="2" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -8658,564 +8689,574 @@
       <c r="AE2" s="8"/>
     </row>
     <row r="3" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
     </row>
     <row r="4" spans="2:39" ht="14.1" customHeight="1"/>
     <row r="5" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B5" s="135" t="s">
+      <c r="B5" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135" t="s">
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
-      <c r="M5" s="135"/>
-      <c r="N5" s="135"/>
-      <c r="O5" s="135" t="s">
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="132"/>
+      <c r="O5" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="P5" s="135"/>
-      <c r="Q5" s="135"/>
-      <c r="R5" s="135"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135" t="s">
+      <c r="P5" s="132"/>
+      <c r="Q5" s="132"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="132"/>
+      <c r="T5" s="132" t="s">
         <v>14</v>
       </c>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
-      <c r="Y5" s="135"/>
-      <c r="Z5" s="135"/>
-      <c r="AA5" s="135"/>
-      <c r="AB5" s="135"/>
-      <c r="AC5" s="135"/>
-      <c r="AD5" s="135"/>
-      <c r="AE5" s="135"/>
-      <c r="AF5" s="135"/>
-      <c r="AG5" s="135"/>
-      <c r="AH5" s="135" t="s">
+      <c r="U5" s="132"/>
+      <c r="V5" s="132"/>
+      <c r="W5" s="132"/>
+      <c r="X5" s="132"/>
+      <c r="Y5" s="132"/>
+      <c r="Z5" s="132"/>
+      <c r="AA5" s="132"/>
+      <c r="AB5" s="132"/>
+      <c r="AC5" s="132"/>
+      <c r="AD5" s="132"/>
+      <c r="AE5" s="132"/>
+      <c r="AF5" s="132"/>
+      <c r="AG5" s="132"/>
+      <c r="AH5" s="132" t="s">
         <v>15</v>
       </c>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="135"/>
-      <c r="AL5" s="135"/>
-      <c r="AM5" s="135"/>
+      <c r="AI5" s="132"/>
+      <c r="AJ5" s="132"/>
+      <c r="AK5" s="132"/>
+      <c r="AL5" s="132"/>
+      <c r="AM5" s="132"/>
     </row>
     <row r="6" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B6" s="139">
+      <c r="B6" s="133">
         <v>1</v>
       </c>
-      <c r="C6" s="139"/>
-      <c r="D6" s="139"/>
-      <c r="E6" s="139"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="139"/>
-      <c r="I6" s="137">
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="130">
         <v>45611</v>
       </c>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="138" t="s">
+      <c r="J6" s="129"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="129"/>
+      <c r="M6" s="129"/>
+      <c r="N6" s="129"/>
+      <c r="O6" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="138"/>
-      <c r="R6" s="138"/>
-      <c r="S6" s="138"/>
-      <c r="T6" s="138" t="s">
+      <c r="P6" s="131"/>
+      <c r="Q6" s="131"/>
+      <c r="R6" s="131"/>
+      <c r="S6" s="131"/>
+      <c r="T6" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="U6" s="138"/>
-      <c r="V6" s="138"/>
-      <c r="W6" s="138"/>
-      <c r="X6" s="138"/>
-      <c r="Y6" s="138"/>
-      <c r="Z6" s="138"/>
-      <c r="AA6" s="138"/>
-      <c r="AB6" s="138"/>
-      <c r="AC6" s="138"/>
-      <c r="AD6" s="138"/>
-      <c r="AE6" s="138"/>
-      <c r="AF6" s="138"/>
-      <c r="AG6" s="138"/>
-      <c r="AH6" s="138" t="s">
+      <c r="U6" s="131"/>
+      <c r="V6" s="131"/>
+      <c r="W6" s="131"/>
+      <c r="X6" s="131"/>
+      <c r="Y6" s="131"/>
+      <c r="Z6" s="131"/>
+      <c r="AA6" s="131"/>
+      <c r="AB6" s="131"/>
+      <c r="AC6" s="131"/>
+      <c r="AD6" s="131"/>
+      <c r="AE6" s="131"/>
+      <c r="AF6" s="131"/>
+      <c r="AG6" s="131"/>
+      <c r="AH6" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="AI6" s="138"/>
-      <c r="AJ6" s="138"/>
-      <c r="AK6" s="138"/>
-      <c r="AL6" s="138"/>
-      <c r="AM6" s="138"/>
+      <c r="AI6" s="131"/>
+      <c r="AJ6" s="131"/>
+      <c r="AK6" s="131"/>
+      <c r="AL6" s="131"/>
+      <c r="AM6" s="131"/>
     </row>
     <row r="7" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B7" s="136">
+      <c r="B7" s="129">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="137">
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="130">
         <v>46086</v>
       </c>
-      <c r="J7" s="136"/>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="138" t="s">
+      <c r="J7" s="129"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="P7" s="138"/>
-      <c r="Q7" s="138"/>
-      <c r="R7" s="138"/>
-      <c r="S7" s="138"/>
-      <c r="T7" s="138" t="s">
-        <v>173</v>
-      </c>
-      <c r="U7" s="138"/>
-      <c r="V7" s="138"/>
-      <c r="W7" s="138"/>
-      <c r="X7" s="138"/>
-      <c r="Y7" s="138"/>
-      <c r="Z7" s="138"/>
-      <c r="AA7" s="138"/>
-      <c r="AB7" s="138"/>
-      <c r="AC7" s="138"/>
-      <c r="AD7" s="138"/>
-      <c r="AE7" s="138"/>
-      <c r="AF7" s="138"/>
-      <c r="AG7" s="138"/>
-      <c r="AH7" s="138" t="s">
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="131"/>
+      <c r="T7" s="131" t="s">
         <v>172</v>
       </c>
-      <c r="AI7" s="138"/>
-      <c r="AJ7" s="138"/>
-      <c r="AK7" s="138"/>
-      <c r="AL7" s="138"/>
-      <c r="AM7" s="138"/>
-    </row>
-    <row r="8" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="136"/>
-      <c r="K8" s="136"/>
-      <c r="L8" s="136"/>
-      <c r="M8" s="136"/>
-      <c r="N8" s="136"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="138"/>
-      <c r="R8" s="138"/>
-      <c r="S8" s="138"/>
-      <c r="T8" s="138"/>
-      <c r="U8" s="138"/>
-      <c r="V8" s="138"/>
-      <c r="W8" s="138"/>
-      <c r="X8" s="138"/>
-      <c r="Y8" s="138"/>
-      <c r="Z8" s="138"/>
-      <c r="AA8" s="138"/>
-      <c r="AB8" s="138"/>
-      <c r="AC8" s="138"/>
-      <c r="AD8" s="138"/>
-      <c r="AE8" s="138"/>
-      <c r="AF8" s="138"/>
-      <c r="AG8" s="138"/>
-      <c r="AH8" s="138"/>
-      <c r="AI8" s="138"/>
-      <c r="AJ8" s="138"/>
-      <c r="AK8" s="138"/>
-      <c r="AL8" s="138"/>
-      <c r="AM8" s="138"/>
+      <c r="U7" s="131"/>
+      <c r="V7" s="131"/>
+      <c r="W7" s="131"/>
+      <c r="X7" s="131"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="131"/>
+      <c r="AB7" s="131"/>
+      <c r="AC7" s="131"/>
+      <c r="AD7" s="131"/>
+      <c r="AE7" s="131"/>
+      <c r="AF7" s="131"/>
+      <c r="AG7" s="131"/>
+      <c r="AH7" s="131" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI7" s="131"/>
+      <c r="AJ7" s="131"/>
+      <c r="AK7" s="131"/>
+      <c r="AL7" s="131"/>
+      <c r="AM7" s="131"/>
+    </row>
+    <row r="8" spans="2:39" ht="30.6" customHeight="1">
+      <c r="B8" s="129">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="129"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+      <c r="G8" s="129"/>
+      <c r="H8" s="129"/>
+      <c r="I8" s="130">
+        <v>46087</v>
+      </c>
+      <c r="J8" s="129"/>
+      <c r="K8" s="129"/>
+      <c r="L8" s="129"/>
+      <c r="M8" s="129"/>
+      <c r="N8" s="129"/>
+      <c r="O8" s="145" t="s">
+        <v>178</v>
+      </c>
+      <c r="P8" s="145"/>
+      <c r="Q8" s="145"/>
+      <c r="R8" s="145"/>
+      <c r="S8" s="145"/>
+      <c r="T8" s="131" t="s">
+        <v>180</v>
+      </c>
+      <c r="U8" s="131"/>
+      <c r="V8" s="131"/>
+      <c r="W8" s="131"/>
+      <c r="X8" s="131"/>
+      <c r="Y8" s="131"/>
+      <c r="Z8" s="131"/>
+      <c r="AA8" s="131"/>
+      <c r="AB8" s="131"/>
+      <c r="AC8" s="131"/>
+      <c r="AD8" s="131"/>
+      <c r="AE8" s="131"/>
+      <c r="AF8" s="131"/>
+      <c r="AG8" s="131"/>
+      <c r="AH8" s="131" t="s">
+        <v>181</v>
+      </c>
+      <c r="AI8" s="131"/>
+      <c r="AJ8" s="131"/>
+      <c r="AK8" s="131"/>
+      <c r="AL8" s="131"/>
+      <c r="AM8" s="131"/>
     </row>
     <row r="9" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B9" s="136"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="136"/>
-      <c r="L9" s="136"/>
-      <c r="M9" s="136"/>
-      <c r="N9" s="136"/>
-      <c r="O9" s="138"/>
-      <c r="P9" s="138"/>
-      <c r="Q9" s="138"/>
-      <c r="R9" s="138"/>
-      <c r="S9" s="138"/>
-      <c r="T9" s="138"/>
-      <c r="U9" s="138"/>
-      <c r="V9" s="138"/>
-      <c r="W9" s="138"/>
-      <c r="X9" s="138"/>
-      <c r="Y9" s="138"/>
-      <c r="Z9" s="138"/>
-      <c r="AA9" s="138"/>
-      <c r="AB9" s="138"/>
-      <c r="AC9" s="138"/>
-      <c r="AD9" s="138"/>
-      <c r="AE9" s="138"/>
-      <c r="AF9" s="138"/>
-      <c r="AG9" s="138"/>
-      <c r="AH9" s="138"/>
-      <c r="AI9" s="138"/>
-      <c r="AJ9" s="138"/>
-      <c r="AK9" s="138"/>
-      <c r="AL9" s="138"/>
-      <c r="AM9" s="138"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="129"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="129"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="129"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="131"/>
+      <c r="S9" s="131"/>
+      <c r="T9" s="131"/>
+      <c r="U9" s="131"/>
+      <c r="V9" s="131"/>
+      <c r="W9" s="131"/>
+      <c r="X9" s="131"/>
+      <c r="Y9" s="131"/>
+      <c r="Z9" s="131"/>
+      <c r="AA9" s="131"/>
+      <c r="AB9" s="131"/>
+      <c r="AC9" s="131"/>
+      <c r="AD9" s="131"/>
+      <c r="AE9" s="131"/>
+      <c r="AF9" s="131"/>
+      <c r="AG9" s="131"/>
+      <c r="AH9" s="131"/>
+      <c r="AI9" s="131"/>
+      <c r="AJ9" s="131"/>
+      <c r="AK9" s="131"/>
+      <c r="AL9" s="131"/>
+      <c r="AM9" s="131"/>
     </row>
     <row r="10" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B10" s="136"/>
-      <c r="C10" s="136"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="136"/>
-      <c r="K10" s="136"/>
-      <c r="L10" s="136"/>
-      <c r="M10" s="136"/>
-      <c r="N10" s="136"/>
-      <c r="O10" s="138"/>
-      <c r="P10" s="138"/>
-      <c r="Q10" s="138"/>
-      <c r="R10" s="138"/>
-      <c r="S10" s="138"/>
-      <c r="T10" s="138"/>
-      <c r="U10" s="138"/>
-      <c r="V10" s="138"/>
-      <c r="W10" s="138"/>
-      <c r="X10" s="138"/>
-      <c r="Y10" s="138"/>
-      <c r="Z10" s="138"/>
-      <c r="AA10" s="138"/>
-      <c r="AB10" s="138"/>
-      <c r="AC10" s="138"/>
-      <c r="AD10" s="138"/>
-      <c r="AE10" s="138"/>
-      <c r="AF10" s="138"/>
-      <c r="AG10" s="138"/>
-      <c r="AH10" s="138"/>
-      <c r="AI10" s="138"/>
-      <c r="AJ10" s="138"/>
-      <c r="AK10" s="138"/>
-      <c r="AL10" s="138"/>
-      <c r="AM10" s="138"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="129"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="131"/>
+      <c r="T10" s="131"/>
+      <c r="U10" s="131"/>
+      <c r="V10" s="131"/>
+      <c r="W10" s="131"/>
+      <c r="X10" s="131"/>
+      <c r="Y10" s="131"/>
+      <c r="Z10" s="131"/>
+      <c r="AA10" s="131"/>
+      <c r="AB10" s="131"/>
+      <c r="AC10" s="131"/>
+      <c r="AD10" s="131"/>
+      <c r="AE10" s="131"/>
+      <c r="AF10" s="131"/>
+      <c r="AG10" s="131"/>
+      <c r="AH10" s="131"/>
+      <c r="AI10" s="131"/>
+      <c r="AJ10" s="131"/>
+      <c r="AK10" s="131"/>
+      <c r="AL10" s="131"/>
+      <c r="AM10" s="131"/>
     </row>
     <row r="11" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-      <c r="N11" s="136"/>
-      <c r="O11" s="138"/>
-      <c r="P11" s="138"/>
-      <c r="Q11" s="138"/>
-      <c r="R11" s="138"/>
-      <c r="S11" s="138"/>
-      <c r="T11" s="138"/>
-      <c r="U11" s="138"/>
-      <c r="V11" s="138"/>
-      <c r="W11" s="138"/>
-      <c r="X11" s="138"/>
-      <c r="Y11" s="138"/>
-      <c r="Z11" s="138"/>
-      <c r="AA11" s="138"/>
-      <c r="AB11" s="138"/>
-      <c r="AC11" s="138"/>
-      <c r="AD11" s="138"/>
-      <c r="AE11" s="138"/>
-      <c r="AF11" s="138"/>
-      <c r="AG11" s="138"/>
-      <c r="AH11" s="138"/>
-      <c r="AI11" s="138"/>
-      <c r="AJ11" s="138"/>
-      <c r="AK11" s="138"/>
-      <c r="AL11" s="138"/>
-      <c r="AM11" s="138"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="129"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="129"/>
+      <c r="N11" s="129"/>
+      <c r="O11" s="131"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
+      <c r="R11" s="131"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="131"/>
+      <c r="U11" s="131"/>
+      <c r="V11" s="131"/>
+      <c r="W11" s="131"/>
+      <c r="X11" s="131"/>
+      <c r="Y11" s="131"/>
+      <c r="Z11" s="131"/>
+      <c r="AA11" s="131"/>
+      <c r="AB11" s="131"/>
+      <c r="AC11" s="131"/>
+      <c r="AD11" s="131"/>
+      <c r="AE11" s="131"/>
+      <c r="AF11" s="131"/>
+      <c r="AG11" s="131"/>
+      <c r="AH11" s="131"/>
+      <c r="AI11" s="131"/>
+      <c r="AJ11" s="131"/>
+      <c r="AK11" s="131"/>
+      <c r="AL11" s="131"/>
+      <c r="AM11" s="131"/>
     </row>
     <row r="12" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B12" s="136"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="137"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="136"/>
-      <c r="L12" s="136"/>
-      <c r="M12" s="136"/>
-      <c r="N12" s="136"/>
-      <c r="O12" s="136"/>
-      <c r="P12" s="136"/>
-      <c r="Q12" s="136"/>
-      <c r="R12" s="136"/>
-      <c r="S12" s="136"/>
-      <c r="T12" s="136"/>
-      <c r="U12" s="136"/>
-      <c r="V12" s="136"/>
-      <c r="W12" s="136"/>
-      <c r="X12" s="136"/>
-      <c r="Y12" s="136"/>
-      <c r="Z12" s="136"/>
-      <c r="AA12" s="136"/>
-      <c r="AB12" s="136"/>
-      <c r="AC12" s="136"/>
-      <c r="AD12" s="136"/>
-      <c r="AE12" s="136"/>
-      <c r="AF12" s="136"/>
-      <c r="AG12" s="136"/>
-      <c r="AH12" s="136"/>
-      <c r="AI12" s="136"/>
-      <c r="AJ12" s="136"/>
-      <c r="AK12" s="136"/>
-      <c r="AL12" s="136"/>
-      <c r="AM12" s="136"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+      <c r="M12" s="129"/>
+      <c r="N12" s="129"/>
+      <c r="O12" s="129"/>
+      <c r="P12" s="129"/>
+      <c r="Q12" s="129"/>
+      <c r="R12" s="129"/>
+      <c r="S12" s="129"/>
+      <c r="T12" s="129"/>
+      <c r="U12" s="129"/>
+      <c r="V12" s="129"/>
+      <c r="W12" s="129"/>
+      <c r="X12" s="129"/>
+      <c r="Y12" s="129"/>
+      <c r="Z12" s="129"/>
+      <c r="AA12" s="129"/>
+      <c r="AB12" s="129"/>
+      <c r="AC12" s="129"/>
+      <c r="AD12" s="129"/>
+      <c r="AE12" s="129"/>
+      <c r="AF12" s="129"/>
+      <c r="AG12" s="129"/>
+      <c r="AH12" s="129"/>
+      <c r="AI12" s="129"/>
+      <c r="AJ12" s="129"/>
+      <c r="AK12" s="129"/>
+      <c r="AL12" s="129"/>
+      <c r="AM12" s="129"/>
     </row>
     <row r="13" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B13" s="136"/>
-      <c r="C13" s="136"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="136"/>
-      <c r="G13" s="136"/>
-      <c r="H13" s="136"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="136"/>
-      <c r="K13" s="136"/>
-      <c r="L13" s="136"/>
-      <c r="M13" s="136"/>
-      <c r="N13" s="136"/>
-      <c r="O13" s="136"/>
-      <c r="P13" s="136"/>
-      <c r="Q13" s="136"/>
-      <c r="R13" s="136"/>
-      <c r="S13" s="136"/>
-      <c r="T13" s="136"/>
-      <c r="U13" s="136"/>
-      <c r="V13" s="136"/>
-      <c r="W13" s="136"/>
-      <c r="X13" s="136"/>
-      <c r="Y13" s="136"/>
-      <c r="Z13" s="136"/>
-      <c r="AA13" s="136"/>
-      <c r="AB13" s="136"/>
-      <c r="AC13" s="136"/>
-      <c r="AD13" s="136"/>
-      <c r="AE13" s="136"/>
-      <c r="AF13" s="136"/>
-      <c r="AG13" s="136"/>
-      <c r="AH13" s="136"/>
-      <c r="AI13" s="136"/>
-      <c r="AJ13" s="136"/>
-      <c r="AK13" s="136"/>
-      <c r="AL13" s="136"/>
-      <c r="AM13" s="136"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="129"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="129"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="129"/>
+      <c r="O13" s="129"/>
+      <c r="P13" s="129"/>
+      <c r="Q13" s="129"/>
+      <c r="R13" s="129"/>
+      <c r="S13" s="129"/>
+      <c r="T13" s="129"/>
+      <c r="U13" s="129"/>
+      <c r="V13" s="129"/>
+      <c r="W13" s="129"/>
+      <c r="X13" s="129"/>
+      <c r="Y13" s="129"/>
+      <c r="Z13" s="129"/>
+      <c r="AA13" s="129"/>
+      <c r="AB13" s="129"/>
+      <c r="AC13" s="129"/>
+      <c r="AD13" s="129"/>
+      <c r="AE13" s="129"/>
+      <c r="AF13" s="129"/>
+      <c r="AG13" s="129"/>
+      <c r="AH13" s="129"/>
+      <c r="AI13" s="129"/>
+      <c r="AJ13" s="129"/>
+      <c r="AK13" s="129"/>
+      <c r="AL13" s="129"/>
+      <c r="AM13" s="129"/>
     </row>
     <row r="14" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="136"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="136"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="136"/>
-      <c r="Q14" s="136"/>
-      <c r="R14" s="136"/>
-      <c r="S14" s="136"/>
-      <c r="T14" s="136"/>
-      <c r="U14" s="136"/>
-      <c r="V14" s="136"/>
-      <c r="W14" s="136"/>
-      <c r="X14" s="136"/>
-      <c r="Y14" s="136"/>
-      <c r="Z14" s="136"/>
-      <c r="AA14" s="136"/>
-      <c r="AB14" s="136"/>
-      <c r="AC14" s="136"/>
-      <c r="AD14" s="136"/>
-      <c r="AE14" s="136"/>
-      <c r="AF14" s="136"/>
-      <c r="AG14" s="136"/>
-      <c r="AH14" s="136"/>
-      <c r="AI14" s="136"/>
-      <c r="AJ14" s="136"/>
-      <c r="AK14" s="136"/>
-      <c r="AL14" s="136"/>
-      <c r="AM14" s="136"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="129"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="129"/>
+      <c r="T14" s="129"/>
+      <c r="U14" s="129"/>
+      <c r="V14" s="129"/>
+      <c r="W14" s="129"/>
+      <c r="X14" s="129"/>
+      <c r="Y14" s="129"/>
+      <c r="Z14" s="129"/>
+      <c r="AA14" s="129"/>
+      <c r="AB14" s="129"/>
+      <c r="AC14" s="129"/>
+      <c r="AD14" s="129"/>
+      <c r="AE14" s="129"/>
+      <c r="AF14" s="129"/>
+      <c r="AG14" s="129"/>
+      <c r="AH14" s="129"/>
+      <c r="AI14" s="129"/>
+      <c r="AJ14" s="129"/>
+      <c r="AK14" s="129"/>
+      <c r="AL14" s="129"/>
+      <c r="AM14" s="129"/>
     </row>
     <row r="15" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B15" s="136"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="136"/>
-      <c r="L15" s="136"/>
-      <c r="M15" s="136"/>
-      <c r="N15" s="136"/>
-      <c r="O15" s="136"/>
-      <c r="P15" s="136"/>
-      <c r="Q15" s="136"/>
-      <c r="R15" s="136"/>
-      <c r="S15" s="136"/>
-      <c r="T15" s="136"/>
-      <c r="U15" s="136"/>
-      <c r="V15" s="136"/>
-      <c r="W15" s="136"/>
-      <c r="X15" s="136"/>
-      <c r="Y15" s="136"/>
-      <c r="Z15" s="136"/>
-      <c r="AA15" s="136"/>
-      <c r="AB15" s="136"/>
-      <c r="AC15" s="136"/>
-      <c r="AD15" s="136"/>
-      <c r="AE15" s="136"/>
-      <c r="AF15" s="136"/>
-      <c r="AG15" s="136"/>
-      <c r="AH15" s="136"/>
-      <c r="AI15" s="136"/>
-      <c r="AJ15" s="136"/>
-      <c r="AK15" s="136"/>
-      <c r="AL15" s="136"/>
-      <c r="AM15" s="136"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="129"/>
+      <c r="K15" s="129"/>
+      <c r="L15" s="129"/>
+      <c r="M15" s="129"/>
+      <c r="N15" s="129"/>
+      <c r="O15" s="129"/>
+      <c r="P15" s="129"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="129"/>
+      <c r="S15" s="129"/>
+      <c r="T15" s="129"/>
+      <c r="U15" s="129"/>
+      <c r="V15" s="129"/>
+      <c r="W15" s="129"/>
+      <c r="X15" s="129"/>
+      <c r="Y15" s="129"/>
+      <c r="Z15" s="129"/>
+      <c r="AA15" s="129"/>
+      <c r="AB15" s="129"/>
+      <c r="AC15" s="129"/>
+      <c r="AD15" s="129"/>
+      <c r="AE15" s="129"/>
+      <c r="AF15" s="129"/>
+      <c r="AG15" s="129"/>
+      <c r="AH15" s="129"/>
+      <c r="AI15" s="129"/>
+      <c r="AJ15" s="129"/>
+      <c r="AK15" s="129"/>
+      <c r="AL15" s="129"/>
+      <c r="AM15" s="129"/>
     </row>
     <row r="16" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B16" s="136"/>
-      <c r="C16" s="136"/>
-      <c r="D16" s="136"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="137"/>
-      <c r="J16" s="136"/>
-      <c r="K16" s="136"/>
-      <c r="L16" s="136"/>
-      <c r="M16" s="136"/>
-      <c r="N16" s="136"/>
-      <c r="O16" s="136"/>
-      <c r="P16" s="136"/>
-      <c r="Q16" s="136"/>
-      <c r="R16" s="136"/>
-      <c r="S16" s="136"/>
-      <c r="T16" s="136"/>
-      <c r="U16" s="136"/>
-      <c r="V16" s="136"/>
-      <c r="W16" s="136"/>
-      <c r="X16" s="136"/>
-      <c r="Y16" s="136"/>
-      <c r="Z16" s="136"/>
-      <c r="AA16" s="136"/>
-      <c r="AB16" s="136"/>
-      <c r="AC16" s="136"/>
-      <c r="AD16" s="136"/>
-      <c r="AE16" s="136"/>
-      <c r="AF16" s="136"/>
-      <c r="AG16" s="136"/>
-      <c r="AH16" s="136"/>
-      <c r="AI16" s="136"/>
-      <c r="AJ16" s="136"/>
-      <c r="AK16" s="136"/>
-      <c r="AL16" s="136"/>
-      <c r="AM16" s="136"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="129"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="129"/>
+      <c r="M16" s="129"/>
+      <c r="N16" s="129"/>
+      <c r="O16" s="129"/>
+      <c r="P16" s="129"/>
+      <c r="Q16" s="129"/>
+      <c r="R16" s="129"/>
+      <c r="S16" s="129"/>
+      <c r="T16" s="129"/>
+      <c r="U16" s="129"/>
+      <c r="V16" s="129"/>
+      <c r="W16" s="129"/>
+      <c r="X16" s="129"/>
+      <c r="Y16" s="129"/>
+      <c r="Z16" s="129"/>
+      <c r="AA16" s="129"/>
+      <c r="AB16" s="129"/>
+      <c r="AC16" s="129"/>
+      <c r="AD16" s="129"/>
+      <c r="AE16" s="129"/>
+      <c r="AF16" s="129"/>
+      <c r="AG16" s="129"/>
+      <c r="AH16" s="129"/>
+      <c r="AI16" s="129"/>
+      <c r="AJ16" s="129"/>
+      <c r="AK16" s="129"/>
+      <c r="AL16" s="129"/>
+      <c r="AM16" s="129"/>
     </row>
     <row r="17" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="137"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="136"/>
-      <c r="P17" s="136"/>
-      <c r="Q17" s="136"/>
-      <c r="R17" s="136"/>
-      <c r="S17" s="136"/>
-      <c r="T17" s="136"/>
-      <c r="U17" s="136"/>
-      <c r="V17" s="136"/>
-      <c r="W17" s="136"/>
-      <c r="X17" s="136"/>
-      <c r="Y17" s="136"/>
-      <c r="Z17" s="136"/>
-      <c r="AA17" s="136"/>
-      <c r="AB17" s="136"/>
-      <c r="AC17" s="136"/>
-      <c r="AD17" s="136"/>
-      <c r="AE17" s="136"/>
-      <c r="AF17" s="136"/>
-      <c r="AG17" s="136"/>
-      <c r="AH17" s="136"/>
-      <c r="AI17" s="136"/>
-      <c r="AJ17" s="136"/>
-      <c r="AK17" s="136"/>
-      <c r="AL17" s="136"/>
-      <c r="AM17" s="136"/>
+      <c r="B17" s="129"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="129"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="129"/>
+      <c r="N17" s="129"/>
+      <c r="O17" s="129"/>
+      <c r="P17" s="129"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="129"/>
+      <c r="S17" s="129"/>
+      <c r="T17" s="129"/>
+      <c r="U17" s="129"/>
+      <c r="V17" s="129"/>
+      <c r="W17" s="129"/>
+      <c r="X17" s="129"/>
+      <c r="Y17" s="129"/>
+      <c r="Z17" s="129"/>
+      <c r="AA17" s="129"/>
+      <c r="AB17" s="129"/>
+      <c r="AC17" s="129"/>
+      <c r="AD17" s="129"/>
+      <c r="AE17" s="129"/>
+      <c r="AF17" s="129"/>
+      <c r="AG17" s="129"/>
+      <c r="AH17" s="129"/>
+      <c r="AI17" s="129"/>
+      <c r="AJ17" s="129"/>
+      <c r="AK17" s="129"/>
+      <c r="AL17" s="129"/>
+      <c r="AM17" s="129"/>
     </row>
     <row r="18" spans="2:39" ht="14.1" customHeight="1"/>
     <row r="19" spans="2:39" ht="14.1" customHeight="1">
@@ -9324,10 +9365,10 @@
     <row r="25" spans="2:39" ht="14.1" customHeight="1">
       <c r="B25" s="25"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="132"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
+      <c r="D25" s="136"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="136"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
@@ -9356,10 +9397,10 @@
     <row r="26" spans="2:39" ht="14.1" customHeight="1">
       <c r="B26" s="25"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="136"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
@@ -9388,10 +9429,10 @@
     <row r="27" spans="2:39" ht="14.1" customHeight="1">
       <c r="B27" s="25"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="132"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="136"/>
+      <c r="G27" s="136"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
@@ -9420,10 +9461,10 @@
     <row r="28" spans="2:39" ht="14.1" customHeight="1">
       <c r="B28" s="25"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="132"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
@@ -9452,10 +9493,10 @@
     <row r="29" spans="2:39" ht="14.1" customHeight="1">
       <c r="B29" s="25"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
+      <c r="D29" s="136"/>
+      <c r="E29" s="136"/>
+      <c r="F29" s="136"/>
+      <c r="G29" s="136"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
@@ -9485,41 +9526,33 @@
     <row r="31" spans="2:39" ht="14.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:S17"/>
-    <mergeCell ref="T17:AG17"/>
-    <mergeCell ref="AH17:AM17"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="T16:AG16"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:AG15"/>
-    <mergeCell ref="AH15:AM15"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:AG14"/>
-    <mergeCell ref="AH14:AM14"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:AG13"/>
-    <mergeCell ref="AH13:AM13"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T12:AG12"/>
-    <mergeCell ref="AH12:AM12"/>
-    <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="T10:AG10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="T5:AG5"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I7:N7"/>
+    <mergeCell ref="O7:S7"/>
+    <mergeCell ref="T7:AG7"/>
+    <mergeCell ref="AH7:AM7"/>
+    <mergeCell ref="AH5:AM5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="T6:AG6"/>
+    <mergeCell ref="AH6:AM6"/>
+    <mergeCell ref="AH9:AM9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="AH8:AM8"/>
+    <mergeCell ref="O8:S8"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I8:N8"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B9:H9"/>
@@ -9529,33 +9562,41 @@
     <mergeCell ref="I11:N11"/>
     <mergeCell ref="O11:S11"/>
     <mergeCell ref="T11:AG11"/>
-    <mergeCell ref="AH9:AM9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="AH8:AM8"/>
-    <mergeCell ref="O8:S8"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="AH5:AM5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:N6"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="T6:AG6"/>
-    <mergeCell ref="AH6:AM6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I7:N7"/>
-    <mergeCell ref="O7:S7"/>
-    <mergeCell ref="T7:AG7"/>
-    <mergeCell ref="AH7:AM7"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="T5:AG5"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="AH11:AM11"/>
+    <mergeCell ref="I10:N10"/>
+    <mergeCell ref="T10:AG10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T12:AG12"/>
+    <mergeCell ref="AH12:AM12"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:AG13"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:AG14"/>
+    <mergeCell ref="AH14:AM14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:AG15"/>
+    <mergeCell ref="AH15:AM15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:S16"/>
+    <mergeCell ref="T16:AG16"/>
+    <mergeCell ref="AH16:AM16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:S17"/>
+    <mergeCell ref="T17:AG17"/>
+    <mergeCell ref="AH17:AM17"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9615,15 +9656,15 @@
     </row>
     <row r="2" spans="1:40" ht="14.1" customHeight="1">
       <c r="A2" s="8"/>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -9659,13 +9700,13 @@
     </row>
     <row r="3" spans="1:40" ht="14.1" customHeight="1">
       <c r="A3" s="8"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -10943,7 +10984,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC528174-C05D-471D-9402-F877ACB55557}">
-  <dimension ref="A1:AN32"/>
+  <dimension ref="A1:AN33"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="40" width="3.33203125" style="1" customWidth="1"/>
@@ -10993,15 +11034,15 @@
     </row>
     <row r="2" spans="1:40" ht="14.1" customHeight="1">
       <c r="A2" s="8"/>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -11037,13 +11078,13 @@
     </row>
     <row r="3" spans="1:40" ht="14.1" customHeight="1">
       <c r="A3" s="8"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -11171,10 +11212,10 @@
     </row>
     <row r="6" spans="1:40" ht="14.1" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" s="140">
+      <c r="B6" s="137">
         <v>1</v>
       </c>
-      <c r="C6" s="141"/>
+      <c r="C6" s="138"/>
       <c r="D6" s="29" t="s">
         <v>56</v>
       </c>
@@ -11221,10 +11262,10 @@
     </row>
     <row r="7" spans="1:40" ht="14.1" customHeight="1">
       <c r="A7" s="8"/>
-      <c r="B7" s="140">
+      <c r="B7" s="137">
         <v>2</v>
       </c>
-      <c r="C7" s="141"/>
+      <c r="C7" s="138"/>
       <c r="D7" s="29" t="s">
         <v>57</v>
       </c>
@@ -11271,10 +11312,10 @@
     </row>
     <row r="8" spans="1:40" ht="14.1" customHeight="1">
       <c r="A8" s="8"/>
-      <c r="B8" s="140">
+      <c r="B8" s="137">
         <v>3</v>
       </c>
-      <c r="C8" s="141"/>
+      <c r="C8" s="138"/>
       <c r="D8" s="29" t="s">
         <v>49</v>
       </c>
@@ -11321,12 +11362,12 @@
     </row>
     <row r="9" spans="1:40" ht="14.1" customHeight="1">
       <c r="A9" s="8"/>
-      <c r="B9" s="140">
-        <v>4</v>
-      </c>
-      <c r="C9" s="141"/>
+      <c r="B9" s="137">
+        <v>3</v>
+      </c>
+      <c r="C9" s="138"/>
       <c r="D9" s="29" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
@@ -11335,7 +11376,7 @@
       <c r="I9" s="82"/>
       <c r="J9" s="69"/>
       <c r="K9" s="29" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="L9" s="30"/>
       <c r="M9" s="30"/>
@@ -11344,39 +11385,39 @@
       <c r="P9" s="82"/>
       <c r="Q9" s="69"/>
       <c r="R9" s="29" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-      <c r="AD9" s="22"/>
-      <c r="AE9" s="22"/>
-      <c r="AF9" s="22"/>
-      <c r="AG9" s="22"/>
-      <c r="AH9" s="22"/>
-      <c r="AI9" s="22"/>
-      <c r="AJ9" s="22"/>
-      <c r="AK9" s="22"/>
-      <c r="AL9" s="22"/>
-      <c r="AM9" s="23"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="31"/>
       <c r="AN9" s="8"/>
     </row>
     <row r="10" spans="1:40" ht="14.1" customHeight="1">
       <c r="A10" s="8"/>
-      <c r="B10" s="140">
-        <v>5</v>
-      </c>
-      <c r="C10" s="141"/>
+      <c r="B10" s="137">
+        <v>4</v>
+      </c>
+      <c r="C10" s="138"/>
       <c r="D10" s="29" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
@@ -11385,7 +11426,7 @@
       <c r="I10" s="82"/>
       <c r="J10" s="69"/>
       <c r="K10" s="29" t="s">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
@@ -11394,39 +11435,39 @@
       <c r="P10" s="82"/>
       <c r="Q10" s="69"/>
       <c r="R10" s="29" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="30"/>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="30"/>
-      <c r="AK10" s="30"/>
-      <c r="AL10" s="30"/>
-      <c r="AM10" s="31"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="22"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
+      <c r="AE10" s="22"/>
+      <c r="AF10" s="22"/>
+      <c r="AG10" s="22"/>
+      <c r="AH10" s="22"/>
+      <c r="AI10" s="22"/>
+      <c r="AJ10" s="22"/>
+      <c r="AK10" s="22"/>
+      <c r="AL10" s="22"/>
+      <c r="AM10" s="23"/>
       <c r="AN10" s="8"/>
     </row>
     <row r="11" spans="1:40" ht="14.1" customHeight="1">
       <c r="A11" s="8"/>
-      <c r="B11" s="140">
-        <v>6</v>
-      </c>
-      <c r="C11" s="141"/>
+      <c r="B11" s="137">
+        <v>5</v>
+      </c>
+      <c r="C11" s="138"/>
       <c r="D11" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
@@ -11435,7 +11476,7 @@
       <c r="I11" s="82"/>
       <c r="J11" s="69"/>
       <c r="K11" s="29" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L11" s="30"/>
       <c r="M11" s="30"/>
@@ -11444,7 +11485,7 @@
       <c r="P11" s="82"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="29" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
@@ -11469,14 +11510,14 @@
       <c r="AM11" s="31"/>
       <c r="AN11" s="8"/>
     </row>
-    <row r="12" spans="1:40" s="70" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="140">
-        <v>7</v>
-      </c>
-      <c r="C12" s="141"/>
+    <row r="12" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="137">
+        <v>6</v>
+      </c>
+      <c r="C12" s="138"/>
       <c r="D12" s="29" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
@@ -11485,7 +11526,7 @@
       <c r="I12" s="82"/>
       <c r="J12" s="69"/>
       <c r="K12" s="29" t="s">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
@@ -11494,7 +11535,7 @@
       <c r="P12" s="82"/>
       <c r="Q12" s="69"/>
       <c r="R12" s="29" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
@@ -11517,16 +11558,16 @@
       <c r="AK12" s="30"/>
       <c r="AL12" s="30"/>
       <c r="AM12" s="31"/>
-      <c r="AN12" s="32"/>
-    </row>
-    <row r="13" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="140">
-        <v>8</v>
-      </c>
-      <c r="C13" s="141"/>
+      <c r="AN12" s="8"/>
+    </row>
+    <row r="13" spans="1:40" s="70" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A13" s="32"/>
+      <c r="B13" s="137">
+        <v>7</v>
+      </c>
+      <c r="C13" s="138"/>
       <c r="D13" s="29" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
@@ -11535,7 +11576,7 @@
       <c r="I13" s="82"/>
       <c r="J13" s="69"/>
       <c r="K13" s="29" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="L13" s="30"/>
       <c r="M13" s="30"/>
@@ -11544,7 +11585,7 @@
       <c r="P13" s="82"/>
       <c r="Q13" s="69"/>
       <c r="R13" s="29" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
@@ -11567,48 +11608,56 @@
       <c r="AK13" s="30"/>
       <c r="AL13" s="30"/>
       <c r="AM13" s="31"/>
-      <c r="AN13" s="8"/>
+      <c r="AN13" s="32"/>
     </row>
     <row r="14" spans="1:40" ht="14.1" customHeight="1">
       <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="19"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
-      <c r="AC14" s="19"/>
-      <c r="AD14" s="19"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="8"/>
-      <c r="AH14" s="8"/>
-      <c r="AI14" s="8"/>
-      <c r="AJ14" s="8"/>
-      <c r="AK14" s="8"/>
-      <c r="AL14" s="8"/>
-      <c r="AM14" s="8"/>
+      <c r="B14" s="137">
+        <v>8</v>
+      </c>
+      <c r="C14" s="138"/>
+      <c r="D14" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="69"/>
+      <c r="R14" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="30"/>
+      <c r="AD14" s="30"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="30"/>
+      <c r="AM14" s="31"/>
       <c r="AN14" s="8"/>
     </row>
     <row r="15" spans="1:40" ht="14.1" customHeight="1">
@@ -11789,28 +11838,28 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="Z19" s="8"/>
-      <c r="AA19" s="8"/>
-      <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-      <c r="AD19" s="8"/>
-      <c r="AE19" s="8"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="19"/>
+      <c r="AC19" s="19"/>
+      <c r="AD19" s="19"/>
+      <c r="AE19" s="19"/>
       <c r="AF19" s="8"/>
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
@@ -11827,8 +11876,8 @@
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -11869,28 +11918,28 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="9"/>
-      <c r="Z21" s="9"/>
-      <c r="AA21" s="9"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="8"/>
+      <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
       <c r="AC21" s="8"/>
       <c r="AD21" s="8"/>
@@ -11916,22 +11965,22 @@
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
-      <c r="R22" s="10"/>
+      <c r="R22" s="9"/>
       <c r="S22" s="9"/>
       <c r="T22" s="9"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
       <c r="AA22" s="9"/>
       <c r="AB22" s="8"/>
       <c r="AC22" s="8"/>
@@ -11965,15 +12014,15 @@
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
+      <c r="R23" s="10"/>
       <c r="S23" s="9"/>
       <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
       <c r="AA23" s="9"/>
       <c r="AB23" s="8"/>
       <c r="AC23" s="8"/>
@@ -12046,10 +12095,10 @@
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
@@ -12172,10 +12221,10 @@
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
       <c r="S28" s="9"/>
       <c r="T28" s="9"/>
       <c r="U28" s="9"/>
@@ -12213,20 +12262,20 @@
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
-      <c r="W29" s="8"/>
-      <c r="X29" s="8"/>
-      <c r="Y29" s="8"/>
-      <c r="Z29" s="8"/>
-      <c r="AA29" s="8"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
       <c r="AB29" s="8"/>
       <c r="AC29" s="8"/>
       <c r="AD29" s="8"/>
@@ -12256,7 +12305,7 @@
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
-      <c r="O30" s="37"/>
+      <c r="O30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
@@ -12298,7 +12347,7 @@
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
+      <c r="O31" s="37"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
@@ -12367,16 +12416,59 @@
       <c r="AM32" s="8"/>
       <c r="AN32" s="8"/>
     </row>
+    <row r="33" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="8"/>
+      <c r="W33" s="8"/>
+      <c r="X33" s="8"/>
+      <c r="Y33" s="8"/>
+      <c r="Z33" s="8"/>
+      <c r="AA33" s="8"/>
+      <c r="AB33" s="8"/>
+      <c r="AC33" s="8"/>
+      <c r="AD33" s="8"/>
+      <c r="AE33" s="8"/>
+      <c r="AF33" s="8"/>
+      <c r="AG33" s="8"/>
+      <c r="AH33" s="8"/>
+      <c r="AI33" s="8"/>
+      <c r="AJ33" s="8"/>
+      <c r="AK33" s="8"/>
+      <c r="AL33" s="8"/>
+      <c r="AM33" s="8"/>
+      <c r="AN33" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B10:C10"/>
+  <mergeCells count="10">
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
@@ -12386,6 +12478,1508 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C7DFF8-755B-45C0-9AF9-2A0F2FD99907}">
+  <dimension ref="A1:AO33"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="40" width="3.33203125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="32"/>
+      <c r="AK1" s="32"/>
+      <c r="AL1" s="32"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="32"/>
+    </row>
+    <row r="2" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A2" s="32"/>
+      <c r="B2" s="141" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+    </row>
+    <row r="3" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A3" s="32"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AL3" s="32"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+    </row>
+    <row r="4" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+    </row>
+    <row r="5" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A5" s="32"/>
+      <c r="B5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="W5" s="47"/>
+      <c r="X5" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD5" s="85"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47"/>
+      <c r="AM5" s="48"/>
+      <c r="AN5" s="32"/>
+    </row>
+    <row r="6" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A6" s="32"/>
+      <c r="B6" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="139"/>
+      <c r="W6" s="140"/>
+      <c r="X6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="AD6" s="82"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="30"/>
+      <c r="AM6" s="31"/>
+      <c r="AN6" s="32"/>
+      <c r="AO6" s="27"/>
+    </row>
+    <row r="7" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A7" s="32"/>
+      <c r="B7" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="140"/>
+      <c r="X7" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD7" s="82"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="31"/>
+      <c r="AN7" s="32"/>
+      <c r="AO7" s="27"/>
+    </row>
+    <row r="8" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A8" s="32"/>
+      <c r="B8" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="139">
+        <v>20</v>
+      </c>
+      <c r="W8" s="140"/>
+      <c r="X8" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="30"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="30"/>
+      <c r="AJ8" s="30"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="30"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="32"/>
+    </row>
+    <row r="9" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A9" s="32"/>
+      <c r="B9" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="140"/>
+      <c r="X9" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD9" s="82"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="31"/>
+      <c r="AN9" s="32"/>
+    </row>
+    <row r="10" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A10" s="32"/>
+      <c r="B10" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="140"/>
+      <c r="X10" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD10" s="82"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="30"/>
+      <c r="AJ10" s="30"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="30"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="32"/>
+    </row>
+    <row r="11" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A11" s="32"/>
+      <c r="B11" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="139">
+        <v>20</v>
+      </c>
+      <c r="W11" s="140"/>
+      <c r="X11" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="82"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="30"/>
+      <c r="AJ11" s="30"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="30"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="32"/>
+    </row>
+    <row r="12" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A12" s="32"/>
+      <c r="B12" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="140"/>
+      <c r="X12" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="30"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="32"/>
+    </row>
+    <row r="13" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="68"/>
+      <c r="AE13" s="68"/>
+      <c r="AF13" s="68"/>
+      <c r="AG13" s="68"/>
+      <c r="AH13" s="68"/>
+      <c r="AI13" s="68"/>
+      <c r="AJ13" s="68"/>
+      <c r="AK13" s="68"/>
+      <c r="AL13" s="68"/>
+      <c r="AM13" s="68"/>
+      <c r="AN13" s="32"/>
+    </row>
+    <row r="14" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
+      <c r="Y14" s="32"/>
+      <c r="Z14" s="32"/>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="32"/>
+      <c r="AC14" s="32"/>
+      <c r="AD14" s="32"/>
+      <c r="AE14" s="32"/>
+      <c r="AF14" s="32"/>
+      <c r="AG14" s="32"/>
+      <c r="AH14" s="32"/>
+      <c r="AI14" s="32"/>
+      <c r="AJ14" s="32"/>
+      <c r="AK14" s="32"/>
+      <c r="AL14" s="32"/>
+      <c r="AM14" s="32"/>
+      <c r="AN14" s="32"/>
+    </row>
+    <row r="15" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+      <c r="AA15" s="32"/>
+      <c r="AB15" s="32"/>
+      <c r="AC15" s="32"/>
+      <c r="AD15" s="32"/>
+      <c r="AE15" s="32"/>
+      <c r="AF15" s="32"/>
+      <c r="AG15" s="32"/>
+      <c r="AH15" s="32"/>
+      <c r="AI15" s="32"/>
+      <c r="AJ15" s="32"/>
+      <c r="AK15" s="32"/>
+      <c r="AL15" s="32"/>
+      <c r="AM15" s="32"/>
+      <c r="AN15" s="32"/>
+    </row>
+    <row r="16" spans="1:41" ht="14.1" customHeight="1">
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="32"/>
+      <c r="AD16" s="32"/>
+      <c r="AE16" s="32"/>
+      <c r="AF16" s="32"/>
+      <c r="AG16" s="32"/>
+      <c r="AH16" s="32"/>
+      <c r="AI16" s="32"/>
+      <c r="AJ16" s="32"/>
+      <c r="AK16" s="32"/>
+      <c r="AL16" s="32"/>
+      <c r="AM16" s="32"/>
+      <c r="AN16" s="32"/>
+    </row>
+    <row r="17" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="142"/>
+      <c r="W17" s="142"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="32"/>
+      <c r="AC17" s="32"/>
+      <c r="AD17" s="32"/>
+      <c r="AE17" s="32"/>
+      <c r="AF17" s="32"/>
+      <c r="AG17" s="32"/>
+      <c r="AH17" s="32"/>
+      <c r="AI17" s="32"/>
+      <c r="AJ17" s="32"/>
+      <c r="AK17" s="32"/>
+      <c r="AL17" s="32"/>
+      <c r="AM17" s="32"/>
+      <c r="AN17" s="32"/>
+    </row>
+    <row r="18" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="45"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="45"/>
+      <c r="U18" s="45"/>
+      <c r="V18" s="45"/>
+      <c r="W18" s="45"/>
+      <c r="X18" s="45"/>
+      <c r="Y18" s="45"/>
+      <c r="Z18" s="45"/>
+      <c r="AA18" s="45"/>
+      <c r="AB18" s="45"/>
+      <c r="AC18" s="45"/>
+      <c r="AD18" s="45"/>
+      <c r="AE18" s="45"/>
+      <c r="AF18" s="32"/>
+      <c r="AG18" s="32"/>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="32"/>
+      <c r="AJ18" s="32"/>
+      <c r="AK18" s="32"/>
+      <c r="AL18" s="32"/>
+      <c r="AM18" s="32"/>
+      <c r="AN18" s="32"/>
+    </row>
+    <row r="19" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="32"/>
+      <c r="AF19" s="32"/>
+      <c r="AG19" s="32"/>
+      <c r="AH19" s="32"/>
+      <c r="AI19" s="32"/>
+      <c r="AJ19" s="32"/>
+      <c r="AK19" s="32"/>
+      <c r="AL19" s="32"/>
+      <c r="AM19" s="32"/>
+      <c r="AN19" s="32"/>
+    </row>
+    <row r="20" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="32"/>
+      <c r="AJ20" s="32"/>
+      <c r="AK20" s="32"/>
+      <c r="AL20" s="32"/>
+      <c r="AM20" s="32"/>
+      <c r="AN20" s="32"/>
+    </row>
+    <row r="21" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="32"/>
+      <c r="AJ21" s="32"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="32"/>
+      <c r="AM21" s="32"/>
+      <c r="AN21" s="32"/>
+    </row>
+    <row r="22" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A22" s="32"/>
+      <c r="B22" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="52"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="52"/>
+      <c r="U22" s="52"/>
+      <c r="V22" s="52"/>
+      <c r="W22" s="52"/>
+      <c r="X22" s="52"/>
+      <c r="Y22" s="52"/>
+      <c r="Z22" s="52"/>
+      <c r="AA22" s="52"/>
+      <c r="AB22" s="52"/>
+      <c r="AC22" s="52"/>
+      <c r="AD22" s="52"/>
+      <c r="AE22" s="52"/>
+      <c r="AF22" s="47"/>
+      <c r="AG22" s="47"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="47"/>
+      <c r="AJ22" s="47"/>
+      <c r="AK22" s="47"/>
+      <c r="AL22" s="47"/>
+      <c r="AM22" s="48"/>
+      <c r="AN22" s="32"/>
+    </row>
+    <row r="23" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A23" s="32"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="55"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="56"/>
+      <c r="W23" s="56"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="54"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
+      <c r="AF23" s="54"/>
+      <c r="AG23" s="54"/>
+      <c r="AH23" s="54"/>
+      <c r="AI23" s="54"/>
+      <c r="AJ23" s="54"/>
+      <c r="AK23" s="54"/>
+      <c r="AL23" s="54"/>
+      <c r="AM23" s="57"/>
+      <c r="AN23" s="32"/>
+    </row>
+    <row r="24" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A24" s="32"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AA24" s="60"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="32"/>
+      <c r="AG24" s="32"/>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="32"/>
+      <c r="AJ24" s="32"/>
+      <c r="AK24" s="32"/>
+      <c r="AL24" s="32"/>
+      <c r="AM24" s="61"/>
+      <c r="AN24" s="32"/>
+    </row>
+    <row r="25" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A25" s="32"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="60"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="63"/>
+      <c r="V25" s="63"/>
+      <c r="W25" s="63"/>
+      <c r="X25" s="63"/>
+      <c r="Y25" s="63"/>
+      <c r="Z25" s="63"/>
+      <c r="AA25" s="60"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
+      <c r="AG25" s="32"/>
+      <c r="AH25" s="32"/>
+      <c r="AI25" s="32"/>
+      <c r="AJ25" s="32"/>
+      <c r="AK25" s="32"/>
+      <c r="AL25" s="32"/>
+      <c r="AM25" s="61"/>
+      <c r="AN25" s="32"/>
+    </row>
+    <row r="26" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A26" s="32"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="60"/>
+      <c r="S26" s="60"/>
+      <c r="T26" s="60"/>
+      <c r="U26" s="60"/>
+      <c r="V26" s="60"/>
+      <c r="W26" s="60"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="60"/>
+      <c r="AA26" s="60"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="61"/>
+      <c r="AN26" s="32"/>
+    </row>
+    <row r="27" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A27" s="32"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="60"/>
+      <c r="Z27" s="60"/>
+      <c r="AA27" s="60"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="61"/>
+      <c r="AN27" s="32"/>
+    </row>
+    <row r="28" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A28" s="32"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
+      <c r="S28" s="60"/>
+      <c r="T28" s="60"/>
+      <c r="U28" s="60"/>
+      <c r="V28" s="60"/>
+      <c r="W28" s="60"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="60"/>
+      <c r="Z28" s="60"/>
+      <c r="AA28" s="60"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
+      <c r="AG28" s="32"/>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="32"/>
+      <c r="AJ28" s="32"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="32"/>
+      <c r="AM28" s="61"/>
+      <c r="AN28" s="32"/>
+    </row>
+    <row r="29" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A29" s="32"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="60"/>
+      <c r="P29" s="60"/>
+      <c r="Q29" s="60"/>
+      <c r="R29" s="60"/>
+      <c r="S29" s="60"/>
+      <c r="T29" s="60"/>
+      <c r="U29" s="60"/>
+      <c r="V29" s="60"/>
+      <c r="W29" s="60"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="60"/>
+      <c r="Z29" s="60"/>
+      <c r="AA29" s="60"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="32"/>
+      <c r="AG29" s="32"/>
+      <c r="AH29" s="32"/>
+      <c r="AI29" s="32"/>
+      <c r="AJ29" s="32"/>
+      <c r="AK29" s="32"/>
+      <c r="AL29" s="32"/>
+      <c r="AM29" s="61"/>
+      <c r="AN29" s="32"/>
+    </row>
+    <row r="30" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A30" s="32"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="60"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="60"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="60"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="60"/>
+      <c r="V30" s="60"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="60"/>
+      <c r="Z30" s="60"/>
+      <c r="AA30" s="60"/>
+      <c r="AB30" s="32"/>
+      <c r="AC30" s="32"/>
+      <c r="AD30" s="32"/>
+      <c r="AE30" s="32"/>
+      <c r="AF30" s="32"/>
+      <c r="AG30" s="32"/>
+      <c r="AH30" s="32"/>
+      <c r="AI30" s="32"/>
+      <c r="AJ30" s="32"/>
+      <c r="AK30" s="32"/>
+      <c r="AL30" s="32"/>
+      <c r="AM30" s="61"/>
+      <c r="AN30" s="32"/>
+    </row>
+    <row r="31" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A31" s="32"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="65"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="65"/>
+      <c r="T31" s="65"/>
+      <c r="U31" s="65"/>
+      <c r="V31" s="65"/>
+      <c r="W31" s="65"/>
+      <c r="X31" s="65"/>
+      <c r="Y31" s="65"/>
+      <c r="Z31" s="65"/>
+      <c r="AA31" s="65"/>
+      <c r="AB31" s="65"/>
+      <c r="AC31" s="65"/>
+      <c r="AD31" s="65"/>
+      <c r="AE31" s="65"/>
+      <c r="AF31" s="65"/>
+      <c r="AG31" s="65"/>
+      <c r="AH31" s="65"/>
+      <c r="AI31" s="65"/>
+      <c r="AJ31" s="65"/>
+      <c r="AK31" s="65"/>
+      <c r="AL31" s="65"/>
+      <c r="AM31" s="67"/>
+      <c r="AN31" s="32"/>
+    </row>
+    <row r="32" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="32"/>
+      <c r="AF32" s="32"/>
+      <c r="AG32" s="32"/>
+      <c r="AH32" s="32"/>
+      <c r="AI32" s="32"/>
+      <c r="AJ32" s="32"/>
+      <c r="AK32" s="32"/>
+      <c r="AL32" s="32"/>
+      <c r="AM32" s="32"/>
+      <c r="AN32" s="32"/>
+    </row>
+    <row r="33" spans="1:40" ht="14.1" customHeight="1">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="8"/>
+      <c r="W33" s="8"/>
+      <c r="X33" s="8"/>
+      <c r="Y33" s="8"/>
+      <c r="Z33" s="8"/>
+      <c r="AA33" s="8"/>
+      <c r="AB33" s="8"/>
+      <c r="AC33" s="8"/>
+      <c r="AD33" s="8"/>
+      <c r="AE33" s="8"/>
+      <c r="AF33" s="8"/>
+      <c r="AG33" s="8"/>
+      <c r="AH33" s="8"/>
+      <c r="AI33" s="8"/>
+      <c r="AJ33" s="8"/>
+      <c r="AK33" s="8"/>
+      <c r="AL33" s="8"/>
+      <c r="AM33" s="8"/>
+      <c r="AN33" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B2:P3"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V7:W7"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC772643-3AE9-44E4-B2C8-0BAB171B7547}">
   <dimension ref="A1:AO35"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
@@ -12438,21 +14032,21 @@
     </row>
     <row r="2" spans="1:41" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
       <c r="O2" s="32"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -12482,19 +14076,19 @@
     </row>
     <row r="3" spans="1:41" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
       <c r="O3" s="32"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -12646,8 +14240,8 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="87"/>
-      <c r="W6" s="88"/>
+      <c r="V6" s="139"/>
+      <c r="W6" s="140"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -12699,8 +14293,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="88"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="29" t="s">
         <v>24</v>
       </c>
@@ -12752,8 +14346,8 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="88"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="140"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -12803,10 +14397,10 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="87">
+      <c r="V9" s="139">
         <v>100</v>
       </c>
-      <c r="W9" s="88"/>
+      <c r="W9" s="140"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -12858,10 +14452,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="87">
+      <c r="V10" s="139">
         <v>100</v>
       </c>
-      <c r="W10" s="88"/>
+      <c r="W10" s="140"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -12911,10 +14505,10 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="87">
+      <c r="V11" s="139">
         <v>8</v>
       </c>
-      <c r="W11" s="88"/>
+      <c r="W11" s="140"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -12949,7 +14543,7 @@
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
@@ -12958,14 +14552,16 @@
       <c r="O12" s="30"/>
       <c r="P12" s="30"/>
       <c r="Q12" s="29" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="R12" s="30"/>
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="88"/>
+      <c r="V12" s="139">
+        <v>4</v>
+      </c>
+      <c r="W12" s="140"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -12974,7 +14570,9 @@
       <c r="AA12" s="30"/>
       <c r="AB12" s="30"/>
       <c r="AC12" s="30"/>
-      <c r="AD12" s="29"/>
+      <c r="AD12" s="29" t="s">
+        <v>176</v>
+      </c>
       <c r="AE12" s="30"/>
       <c r="AF12" s="30"/>
       <c r="AG12" s="30"/>
@@ -13000,7 +14598,7 @@
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
       <c r="J13" s="29" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -13009,14 +14607,16 @@
       <c r="O13" s="30"/>
       <c r="P13" s="30"/>
       <c r="Q13" s="29" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="R13" s="30"/>
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="88"/>
+      <c r="V13" s="139">
+        <v>4</v>
+      </c>
+      <c r="W13" s="140"/>
       <c r="X13" s="29" t="s">
         <v>25</v>
       </c>
@@ -13025,7 +14625,9 @@
       <c r="AA13" s="30"/>
       <c r="AB13" s="30"/>
       <c r="AC13" s="30"/>
-      <c r="AD13" s="29"/>
+      <c r="AD13" s="29" t="s">
+        <v>176</v>
+      </c>
       <c r="AE13" s="30"/>
       <c r="AF13" s="30"/>
       <c r="AG13" s="30"/>
@@ -13066,8 +14668,8 @@
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="88"/>
+      <c r="V14" s="139"/>
+      <c r="W14" s="140"/>
       <c r="X14" s="29" t="s">
         <v>25</v>
       </c>
@@ -13119,8 +14721,8 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="88"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="140"/>
       <c r="X15" s="29" t="s">
         <v>25</v>
       </c>
@@ -13172,8 +14774,8 @@
       <c r="S16" s="30"/>
       <c r="T16" s="30"/>
       <c r="U16" s="31"/>
-      <c r="V16" s="87"/>
-      <c r="W16" s="88"/>
+      <c r="V16" s="139"/>
+      <c r="W16" s="140"/>
       <c r="X16" s="29" t="s">
         <v>25</v>
       </c>
@@ -13278,8 +14880,8 @@
       <c r="S18" s="30"/>
       <c r="T18" s="30"/>
       <c r="U18" s="31"/>
-      <c r="V18" s="87"/>
-      <c r="W18" s="88"/>
+      <c r="V18" s="139"/>
+      <c r="W18" s="140"/>
       <c r="X18" s="29" t="s">
         <v>25</v>
       </c>
@@ -13998,1508 +15600,6 @@
     <mergeCell ref="V10:W10"/>
     <mergeCell ref="V13:W13"/>
     <mergeCell ref="V12:W12"/>
-  </mergeCells>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C7DFF8-755B-45C0-9AF9-2A0F2FD99907}">
-  <dimension ref="A1:AO33"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
-  <cols>
-    <col min="1" max="40" width="3.33203125" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A1" s="32"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-    </row>
-    <row r="2" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A2" s="32"/>
-      <c r="B2" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-    </row>
-    <row r="3" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A3" s="32"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-    </row>
-    <row r="4" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="32"/>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="32"/>
-      <c r="AM4" s="32"/>
-      <c r="AN4" s="32"/>
-    </row>
-    <row r="5" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A5" s="32"/>
-      <c r="B5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="W5" s="47"/>
-      <c r="X5" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD5" s="85"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="47"/>
-      <c r="AL5" s="47"/>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="32"/>
-    </row>
-    <row r="6" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="87"/>
-      <c r="W6" s="88"/>
-      <c r="X6" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD6" s="82"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="31"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="27"/>
-    </row>
-    <row r="7" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="88"/>
-      <c r="X7" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AD7" s="82"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="32"/>
-      <c r="AO7" s="27"/>
-    </row>
-    <row r="8" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="87">
-        <v>20</v>
-      </c>
-      <c r="W8" s="88"/>
-      <c r="X8" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD8" s="82"/>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AH8" s="30"/>
-      <c r="AI8" s="30"/>
-      <c r="AJ8" s="30"/>
-      <c r="AK8" s="30"/>
-      <c r="AL8" s="30"/>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="32"/>
-    </row>
-    <row r="9" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A9" s="32"/>
-      <c r="B9" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="88"/>
-      <c r="X9" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="30"/>
-      <c r="AH9" s="30"/>
-      <c r="AI9" s="30"/>
-      <c r="AJ9" s="30"/>
-      <c r="AK9" s="30"/>
-      <c r="AL9" s="30"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="32"/>
-    </row>
-    <row r="10" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A10" s="32"/>
-      <c r="B10" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="87"/>
-      <c r="W10" s="88"/>
-      <c r="X10" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AD10" s="82"/>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="30"/>
-      <c r="AK10" s="30"/>
-      <c r="AL10" s="30"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="32"/>
-    </row>
-    <row r="11" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A11" s="32"/>
-      <c r="B11" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="87">
-        <v>20</v>
-      </c>
-      <c r="W11" s="88"/>
-      <c r="X11" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="29"/>
-      <c r="AD11" s="82"/>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="30"/>
-      <c r="AK11" s="30"/>
-      <c r="AL11" s="30"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="32"/>
-    </row>
-    <row r="12" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="88"/>
-      <c r="X12" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD12" s="82"/>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
-      <c r="AH12" s="30"/>
-      <c r="AI12" s="30"/>
-      <c r="AJ12" s="30"/>
-      <c r="AK12" s="30"/>
-      <c r="AL12" s="30"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="32"/>
-    </row>
-    <row r="13" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="32"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="32"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="68"/>
-      <c r="AE13" s="68"/>
-      <c r="AF13" s="68"/>
-      <c r="AG13" s="68"/>
-      <c r="AH13" s="68"/>
-      <c r="AI13" s="68"/>
-      <c r="AJ13" s="68"/>
-      <c r="AK13" s="68"/>
-      <c r="AL13" s="68"/>
-      <c r="AM13" s="68"/>
-      <c r="AN13" s="32"/>
-    </row>
-    <row r="14" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="32"/>
-      <c r="U14" s="32"/>
-      <c r="V14" s="32"/>
-      <c r="W14" s="32"/>
-      <c r="X14" s="32"/>
-      <c r="Y14" s="32"/>
-      <c r="Z14" s="32"/>
-      <c r="AA14" s="32"/>
-      <c r="AB14" s="32"/>
-      <c r="AC14" s="32"/>
-      <c r="AD14" s="32"/>
-      <c r="AE14" s="32"/>
-      <c r="AF14" s="32"/>
-      <c r="AG14" s="32"/>
-      <c r="AH14" s="32"/>
-      <c r="AI14" s="32"/>
-      <c r="AJ14" s="32"/>
-      <c r="AK14" s="32"/>
-      <c r="AL14" s="32"/>
-      <c r="AM14" s="32"/>
-      <c r="AN14" s="32"/>
-    </row>
-    <row r="15" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="32"/>
-      <c r="AA15" s="32"/>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="32"/>
-      <c r="AD15" s="32"/>
-      <c r="AE15" s="32"/>
-      <c r="AF15" s="32"/>
-      <c r="AG15" s="32"/>
-      <c r="AH15" s="32"/>
-      <c r="AI15" s="32"/>
-      <c r="AJ15" s="32"/>
-      <c r="AK15" s="32"/>
-      <c r="AL15" s="32"/>
-      <c r="AM15" s="32"/>
-      <c r="AN15" s="32"/>
-    </row>
-    <row r="16" spans="1:41" ht="14.1" customHeight="1">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="32"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="32"/>
-      <c r="AD16" s="32"/>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="32"/>
-      <c r="AG16" s="32"/>
-      <c r="AH16" s="32"/>
-      <c r="AI16" s="32"/>
-      <c r="AJ16" s="32"/>
-      <c r="AK16" s="32"/>
-      <c r="AL16" s="32"/>
-      <c r="AM16" s="32"/>
-      <c r="AN16" s="32"/>
-    </row>
-    <row r="17" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="59"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="142"/>
-      <c r="W17" s="142"/>
-      <c r="X17" s="32"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-      <c r="AA17" s="32"/>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="32"/>
-      <c r="AE17" s="32"/>
-      <c r="AF17" s="32"/>
-      <c r="AG17" s="32"/>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="32"/>
-      <c r="AJ17" s="32"/>
-      <c r="AK17" s="32"/>
-      <c r="AL17" s="32"/>
-      <c r="AM17" s="32"/>
-      <c r="AN17" s="32"/>
-    </row>
-    <row r="18" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-      <c r="U18" s="45"/>
-      <c r="V18" s="45"/>
-      <c r="W18" s="45"/>
-      <c r="X18" s="45"/>
-      <c r="Y18" s="45"/>
-      <c r="Z18" s="45"/>
-      <c r="AA18" s="45"/>
-      <c r="AB18" s="45"/>
-      <c r="AC18" s="45"/>
-      <c r="AD18" s="45"/>
-      <c r="AE18" s="45"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="32"/>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="32"/>
-      <c r="AJ18" s="32"/>
-      <c r="AK18" s="32"/>
-      <c r="AL18" s="32"/>
-      <c r="AM18" s="32"/>
-      <c r="AN18" s="32"/>
-    </row>
-    <row r="19" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A19" s="32"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="32"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="32"/>
-      <c r="U19" s="32"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="32"/>
-      <c r="AA19" s="32"/>
-      <c r="AB19" s="32"/>
-      <c r="AC19" s="32"/>
-      <c r="AD19" s="32"/>
-      <c r="AE19" s="32"/>
-      <c r="AF19" s="32"/>
-      <c r="AG19" s="32"/>
-      <c r="AH19" s="32"/>
-      <c r="AI19" s="32"/>
-      <c r="AJ19" s="32"/>
-      <c r="AK19" s="32"/>
-      <c r="AL19" s="32"/>
-      <c r="AM19" s="32"/>
-      <c r="AN19" s="32"/>
-    </row>
-    <row r="20" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="32"/>
-      <c r="U20" s="32"/>
-      <c r="V20" s="32"/>
-      <c r="W20" s="32"/>
-      <c r="X20" s="32"/>
-      <c r="Y20" s="32"/>
-      <c r="Z20" s="32"/>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="32"/>
-      <c r="AC20" s="32"/>
-      <c r="AD20" s="32"/>
-      <c r="AE20" s="32"/>
-      <c r="AF20" s="32"/>
-      <c r="AG20" s="32"/>
-      <c r="AH20" s="32"/>
-      <c r="AI20" s="32"/>
-      <c r="AJ20" s="32"/>
-      <c r="AK20" s="32"/>
-      <c r="AL20" s="32"/>
-      <c r="AM20" s="32"/>
-      <c r="AN20" s="32"/>
-    </row>
-    <row r="21" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="32"/>
-      <c r="T21" s="32"/>
-      <c r="U21" s="32"/>
-      <c r="V21" s="32"/>
-      <c r="W21" s="32"/>
-      <c r="X21" s="32"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="32"/>
-      <c r="AE21" s="32"/>
-      <c r="AF21" s="32"/>
-      <c r="AG21" s="32"/>
-      <c r="AH21" s="32"/>
-      <c r="AI21" s="32"/>
-      <c r="AJ21" s="32"/>
-      <c r="AK21" s="32"/>
-      <c r="AL21" s="32"/>
-      <c r="AM21" s="32"/>
-      <c r="AN21" s="32"/>
-    </row>
-    <row r="22" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A22" s="32"/>
-      <c r="B22" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="52"/>
-      <c r="R22" s="52"/>
-      <c r="S22" s="52"/>
-      <c r="T22" s="52"/>
-      <c r="U22" s="52"/>
-      <c r="V22" s="52"/>
-      <c r="W22" s="52"/>
-      <c r="X22" s="52"/>
-      <c r="Y22" s="52"/>
-      <c r="Z22" s="52"/>
-      <c r="AA22" s="52"/>
-      <c r="AB22" s="52"/>
-      <c r="AC22" s="52"/>
-      <c r="AD22" s="52"/>
-      <c r="AE22" s="52"/>
-      <c r="AF22" s="47"/>
-      <c r="AG22" s="47"/>
-      <c r="AH22" s="47"/>
-      <c r="AI22" s="47"/>
-      <c r="AJ22" s="47"/>
-      <c r="AK22" s="47"/>
-      <c r="AL22" s="47"/>
-      <c r="AM22" s="48"/>
-      <c r="AN22" s="32"/>
-    </row>
-    <row r="23" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A23" s="32"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="54"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="56"/>
-      <c r="W23" s="56"/>
-      <c r="X23" s="54"/>
-      <c r="Y23" s="54"/>
-      <c r="Z23" s="54"/>
-      <c r="AA23" s="54"/>
-      <c r="AB23" s="54"/>
-      <c r="AC23" s="54"/>
-      <c r="AD23" s="54"/>
-      <c r="AE23" s="54"/>
-      <c r="AF23" s="54"/>
-      <c r="AG23" s="54"/>
-      <c r="AH23" s="54"/>
-      <c r="AI23" s="54"/>
-      <c r="AJ23" s="54"/>
-      <c r="AK23" s="54"/>
-      <c r="AL23" s="54"/>
-      <c r="AM23" s="57"/>
-      <c r="AN23" s="32"/>
-    </row>
-    <row r="24" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A24" s="32"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="60"/>
-      <c r="M24" s="60"/>
-      <c r="N24" s="60"/>
-      <c r="O24" s="60"/>
-      <c r="P24" s="60"/>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="60"/>
-      <c r="S24" s="60"/>
-      <c r="T24" s="60"/>
-      <c r="U24" s="60"/>
-      <c r="V24" s="60"/>
-      <c r="W24" s="60"/>
-      <c r="X24" s="60"/>
-      <c r="Y24" s="60"/>
-      <c r="Z24" s="60"/>
-      <c r="AA24" s="60"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="32"/>
-      <c r="AD24" s="32"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="32"/>
-      <c r="AG24" s="32"/>
-      <c r="AH24" s="32"/>
-      <c r="AI24" s="32"/>
-      <c r="AJ24" s="32"/>
-      <c r="AK24" s="32"/>
-      <c r="AL24" s="32"/>
-      <c r="AM24" s="61"/>
-      <c r="AN24" s="32"/>
-    </row>
-    <row r="25" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A25" s="32"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="62"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="60"/>
-      <c r="U25" s="63"/>
-      <c r="V25" s="63"/>
-      <c r="W25" s="63"/>
-      <c r="X25" s="63"/>
-      <c r="Y25" s="63"/>
-      <c r="Z25" s="63"/>
-      <c r="AA25" s="60"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="32"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="32"/>
-      <c r="AG25" s="32"/>
-      <c r="AH25" s="32"/>
-      <c r="AI25" s="32"/>
-      <c r="AJ25" s="32"/>
-      <c r="AK25" s="32"/>
-      <c r="AL25" s="32"/>
-      <c r="AM25" s="61"/>
-      <c r="AN25" s="32"/>
-    </row>
-    <row r="26" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A26" s="32"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="60"/>
-      <c r="O26" s="60"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="60"/>
-      <c r="T26" s="60"/>
-      <c r="U26" s="60"/>
-      <c r="V26" s="60"/>
-      <c r="W26" s="60"/>
-      <c r="X26" s="60"/>
-      <c r="Y26" s="60"/>
-      <c r="Z26" s="60"/>
-      <c r="AA26" s="60"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="32"/>
-      <c r="AG26" s="32"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="32"/>
-      <c r="AJ26" s="32"/>
-      <c r="AK26" s="32"/>
-      <c r="AL26" s="32"/>
-      <c r="AM26" s="61"/>
-      <c r="AN26" s="32"/>
-    </row>
-    <row r="27" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A27" s="32"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="60"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="60"/>
-      <c r="Y27" s="60"/>
-      <c r="Z27" s="60"/>
-      <c r="AA27" s="60"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="32"/>
-      <c r="AG27" s="32"/>
-      <c r="AH27" s="32"/>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="61"/>
-      <c r="AN27" s="32"/>
-    </row>
-    <row r="28" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A28" s="32"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="60"/>
-      <c r="O28" s="60"/>
-      <c r="P28" s="60"/>
-      <c r="Q28" s="60"/>
-      <c r="R28" s="60"/>
-      <c r="S28" s="60"/>
-      <c r="T28" s="60"/>
-      <c r="U28" s="60"/>
-      <c r="V28" s="60"/>
-      <c r="W28" s="60"/>
-      <c r="X28" s="60"/>
-      <c r="Y28" s="60"/>
-      <c r="Z28" s="60"/>
-      <c r="AA28" s="60"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="32"/>
-      <c r="AG28" s="32"/>
-      <c r="AH28" s="32"/>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="61"/>
-      <c r="AN28" s="32"/>
-    </row>
-    <row r="29" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A29" s="32"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="60"/>
-      <c r="O29" s="60"/>
-      <c r="P29" s="60"/>
-      <c r="Q29" s="60"/>
-      <c r="R29" s="60"/>
-      <c r="S29" s="60"/>
-      <c r="T29" s="60"/>
-      <c r="U29" s="60"/>
-      <c r="V29" s="60"/>
-      <c r="W29" s="60"/>
-      <c r="X29" s="60"/>
-      <c r="Y29" s="60"/>
-      <c r="Z29" s="60"/>
-      <c r="AA29" s="60"/>
-      <c r="AB29" s="32"/>
-      <c r="AC29" s="32"/>
-      <c r="AD29" s="32"/>
-      <c r="AE29" s="32"/>
-      <c r="AF29" s="32"/>
-      <c r="AG29" s="32"/>
-      <c r="AH29" s="32"/>
-      <c r="AI29" s="32"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
-      <c r="AL29" s="32"/>
-      <c r="AM29" s="61"/>
-      <c r="AN29" s="32"/>
-    </row>
-    <row r="30" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A30" s="32"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="60"/>
-      <c r="O30" s="60"/>
-      <c r="P30" s="60"/>
-      <c r="Q30" s="60"/>
-      <c r="R30" s="60"/>
-      <c r="S30" s="60"/>
-      <c r="T30" s="60"/>
-      <c r="U30" s="60"/>
-      <c r="V30" s="60"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="60"/>
-      <c r="Y30" s="60"/>
-      <c r="Z30" s="60"/>
-      <c r="AA30" s="60"/>
-      <c r="AB30" s="32"/>
-      <c r="AC30" s="32"/>
-      <c r="AD30" s="32"/>
-      <c r="AE30" s="32"/>
-      <c r="AF30" s="32"/>
-      <c r="AG30" s="32"/>
-      <c r="AH30" s="32"/>
-      <c r="AI30" s="32"/>
-      <c r="AJ30" s="32"/>
-      <c r="AK30" s="32"/>
-      <c r="AL30" s="32"/>
-      <c r="AM30" s="61"/>
-      <c r="AN30" s="32"/>
-    </row>
-    <row r="31" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A31" s="32"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
-      <c r="N31" s="65"/>
-      <c r="O31" s="66"/>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="65"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
-      <c r="Z31" s="65"/>
-      <c r="AA31" s="65"/>
-      <c r="AB31" s="65"/>
-      <c r="AC31" s="65"/>
-      <c r="AD31" s="65"/>
-      <c r="AE31" s="65"/>
-      <c r="AF31" s="65"/>
-      <c r="AG31" s="65"/>
-      <c r="AH31" s="65"/>
-      <c r="AI31" s="65"/>
-      <c r="AJ31" s="65"/>
-      <c r="AK31" s="65"/>
-      <c r="AL31" s="65"/>
-      <c r="AM31" s="67"/>
-      <c r="AN31" s="32"/>
-    </row>
-    <row r="32" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
-      <c r="P32" s="32"/>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="32"/>
-      <c r="T32" s="32"/>
-      <c r="U32" s="32"/>
-      <c r="V32" s="32"/>
-      <c r="W32" s="32"/>
-      <c r="X32" s="32"/>
-      <c r="Y32" s="32"/>
-      <c r="Z32" s="32"/>
-      <c r="AA32" s="32"/>
-      <c r="AB32" s="32"/>
-      <c r="AC32" s="32"/>
-      <c r="AD32" s="32"/>
-      <c r="AE32" s="32"/>
-      <c r="AF32" s="32"/>
-      <c r="AG32" s="32"/>
-      <c r="AH32" s="32"/>
-      <c r="AI32" s="32"/>
-      <c r="AJ32" s="32"/>
-      <c r="AK32" s="32"/>
-      <c r="AL32" s="32"/>
-      <c r="AM32" s="32"/>
-      <c r="AN32" s="32"/>
-    </row>
-    <row r="33" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="8"/>
-      <c r="W33" s="8"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="8"/>
-      <c r="Z33" s="8"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="8"/>
-      <c r="AF33" s="8"/>
-      <c r="AG33" s="8"/>
-      <c r="AH33" s="8"/>
-      <c r="AI33" s="8"/>
-      <c r="AJ33" s="8"/>
-      <c r="AK33" s="8"/>
-      <c r="AL33" s="8"/>
-      <c r="AM33" s="8"/>
-      <c r="AN33" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B2:P3"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V7:W7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15559,23 +15659,23 @@
     </row>
     <row r="2" spans="1:41" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="141" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
       <c r="Q2" s="32"/>
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
@@ -15603,21 +15703,21 @@
     </row>
     <row r="3" spans="1:41" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
       <c r="S3" s="32"/>
@@ -15767,10 +15867,10 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="87">
+      <c r="V6" s="139">
         <v>20</v>
       </c>
-      <c r="W6" s="88"/>
+      <c r="W6" s="140"/>
       <c r="X6" s="29" t="s">
         <v>24</v>
       </c>
@@ -15819,8 +15919,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="88"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="29" t="s">
         <v>78</v>
       </c>
@@ -15872,10 +15972,10 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="87">
+      <c r="V8" s="139">
         <v>100</v>
       </c>
-      <c r="W8" s="88"/>
+      <c r="W8" s="140"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -15925,10 +16025,10 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="87">
+      <c r="V9" s="139">
         <v>100</v>
       </c>
-      <c r="W9" s="88"/>
+      <c r="W9" s="140"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -15978,10 +16078,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="87">
+      <c r="V10" s="139">
         <v>100</v>
       </c>
-      <c r="W10" s="88"/>
+      <c r="W10" s="140"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -16033,8 +16133,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="88"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="140"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
@@ -16086,8 +16186,8 @@
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="88"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="140"/>
       <c r="X12" s="29" t="s">
         <v>25</v>
       </c>
@@ -16139,8 +16239,8 @@
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="88"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="140"/>
       <c r="X13" s="29" t="s">
         <v>25</v>
       </c>
@@ -16191,8 +16291,8 @@
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="88"/>
+      <c r="V14" s="139"/>
+      <c r="W14" s="140"/>
       <c r="X14" s="29" t="s">
         <v>25</v>
       </c>
@@ -16243,10 +16343,10 @@
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31"/>
-      <c r="V15" s="87">
+      <c r="V15" s="139">
         <v>20</v>
       </c>
-      <c r="W15" s="88"/>
+      <c r="W15" s="140"/>
       <c r="X15" s="29" t="s">
         <v>25</v>
       </c>
@@ -16295,8 +16395,8 @@
       <c r="S16" s="30"/>
       <c r="T16" s="30"/>
       <c r="U16" s="31"/>
-      <c r="V16" s="87"/>
-      <c r="W16" s="88"/>
+      <c r="V16" s="139"/>
+      <c r="W16" s="140"/>
       <c r="X16" s="29" t="s">
         <v>25</v>
       </c>
@@ -17025,13 +17125,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5DE7B0-A097-47C4-994E-9AD67B30BEB7}">
-  <dimension ref="A1:AO28"/>
+  <dimension ref="A1:AN27"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="40" width="3.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="14.1" customHeight="1">
+    <row r="1" spans="1:40" ht="14.1" customHeight="1">
       <c r="A1" s="32"/>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -17073,33 +17173,33 @@
       <c r="AM1" s="32"/>
       <c r="AN1" s="32"/>
     </row>
-    <row r="2" spans="1:41" ht="14.1" customHeight="1">
+    <row r="2" spans="1:40" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="89" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
-      <c r="U2" s="89"/>
-      <c r="V2" s="89"/>
-      <c r="W2" s="89"/>
-      <c r="X2" s="89"/>
+      <c r="B2" s="141" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="141"/>
+      <c r="S2" s="141"/>
+      <c r="T2" s="141"/>
+      <c r="U2" s="141"/>
+      <c r="V2" s="141"/>
+      <c r="W2" s="141"/>
+      <c r="X2" s="141"/>
       <c r="Y2" s="32"/>
       <c r="Z2" s="32"/>
       <c r="AA2" s="32"/>
@@ -17117,31 +17217,31 @@
       <c r="AM2" s="32"/>
       <c r="AN2" s="32"/>
     </row>
-    <row r="3" spans="1:41" ht="14.1" customHeight="1">
+    <row r="3" spans="1:40" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="89"/>
-      <c r="U3" s="89"/>
-      <c r="V3" s="89"/>
-      <c r="W3" s="89"/>
-      <c r="X3" s="89"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="141"/>
+      <c r="S3" s="141"/>
+      <c r="T3" s="141"/>
+      <c r="U3" s="141"/>
+      <c r="V3" s="141"/>
+      <c r="W3" s="141"/>
+      <c r="X3" s="141"/>
       <c r="Y3" s="32"/>
       <c r="Z3" s="32"/>
       <c r="AA3" s="32"/>
@@ -17159,7 +17259,7 @@
       <c r="AM3" s="32"/>
       <c r="AN3" s="32"/>
     </row>
-    <row r="4" spans="1:41" ht="14.1" customHeight="1">
+    <row r="4" spans="1:40" ht="14.1" customHeight="1">
       <c r="A4" s="32"/>
       <c r="B4" s="32"/>
       <c r="C4" s="32"/>
@@ -17201,7 +17301,7 @@
       <c r="AM4" s="32"/>
       <c r="AN4" s="32"/>
     </row>
-    <row r="5" spans="1:41" ht="14.1" customHeight="1">
+    <row r="5" spans="1:40" ht="14.1" customHeight="1">
       <c r="A5" s="32"/>
       <c r="B5" s="46" t="s">
         <v>1</v>
@@ -17255,7 +17355,7 @@
       <c r="AM5" s="51"/>
       <c r="AN5" s="32"/>
     </row>
-    <row r="6" spans="1:41" ht="14.1" customHeight="1">
+    <row r="6" spans="1:40" ht="14.1" customHeight="1">
       <c r="A6" s="32"/>
       <c r="B6" s="29" t="s">
         <v>27</v>
@@ -17283,12 +17383,12 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="87">
+      <c r="V6" s="139">
         <v>20</v>
       </c>
-      <c r="W6" s="88"/>
+      <c r="W6" s="140"/>
       <c r="X6" s="29" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="Y6" s="30"/>
       <c r="Z6" s="30"/>
@@ -17307,10 +17407,10 @@
       <c r="AM6" s="31"/>
       <c r="AN6" s="32"/>
     </row>
-    <row r="7" spans="1:41" ht="14.1" customHeight="1">
+    <row r="7" spans="1:40" ht="14.1" customHeight="1">
       <c r="A7" s="32"/>
       <c r="B7" s="29" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -17320,7 +17420,7 @@
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
       <c r="J7" s="29" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -17329,16 +17429,14 @@
       <c r="O7" s="30"/>
       <c r="P7" s="30"/>
       <c r="Q7" s="29" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="R7" s="30"/>
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="87">
-        <v>100</v>
-      </c>
-      <c r="W7" s="88"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="29" t="s">
         <v>25</v>
       </c>
@@ -17347,7 +17445,9 @@
       <c r="AA7" s="30"/>
       <c r="AB7" s="30"/>
       <c r="AC7" s="30"/>
-      <c r="AD7" s="29"/>
+      <c r="AD7" s="29" t="s">
+        <v>161</v>
+      </c>
       <c r="AE7" s="30"/>
       <c r="AF7" s="30"/>
       <c r="AG7" s="30"/>
@@ -17358,12 +17458,11 @@
       <c r="AL7" s="30"/>
       <c r="AM7" s="31"/>
       <c r="AN7" s="32"/>
-      <c r="AO7" s="27"/>
-    </row>
-    <row r="8" spans="1:41" ht="14.1" customHeight="1">
+    </row>
+    <row r="8" spans="1:40" ht="14.1" customHeight="1">
       <c r="A8" s="32"/>
       <c r="B8" s="29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="30"/>
       <c r="D8" s="30"/>
@@ -17373,7 +17472,7 @@
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
       <c r="J8" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K8" s="30"/>
       <c r="L8" s="30"/>
@@ -17388,8 +17487,8 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="88"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="140"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -17412,10 +17511,10 @@
       <c r="AM8" s="31"/>
       <c r="AN8" s="32"/>
     </row>
-    <row r="9" spans="1:41" ht="14.1" customHeight="1">
+    <row r="9" spans="1:40" ht="14.1" customHeight="1">
       <c r="A9" s="32"/>
       <c r="B9" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
@@ -17425,7 +17524,7 @@
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
       <c r="J9" s="29" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
@@ -17434,14 +17533,16 @@
       <c r="O9" s="30"/>
       <c r="P9" s="30"/>
       <c r="Q9" s="29" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="R9" s="30"/>
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="88"/>
+      <c r="V9" s="139">
+        <v>20</v>
+      </c>
+      <c r="W9" s="140"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -17450,9 +17551,7 @@
       <c r="AA9" s="30"/>
       <c r="AB9" s="30"/>
       <c r="AC9" s="30"/>
-      <c r="AD9" s="29" t="s">
-        <v>161</v>
-      </c>
+      <c r="AD9" s="29"/>
       <c r="AE9" s="30"/>
       <c r="AF9" s="30"/>
       <c r="AG9" s="30"/>
@@ -17464,10 +17563,10 @@
       <c r="AM9" s="31"/>
       <c r="AN9" s="32"/>
     </row>
-    <row r="10" spans="1:41" ht="14.1" customHeight="1">
+    <row r="10" spans="1:40" ht="14.1" customHeight="1">
       <c r="A10" s="32"/>
       <c r="B10" s="29" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -17477,7 +17576,7 @@
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
       <c r="J10" s="29" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="K10" s="30"/>
       <c r="L10" s="30"/>
@@ -17486,16 +17585,14 @@
       <c r="O10" s="30"/>
       <c r="P10" s="30"/>
       <c r="Q10" s="29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R10" s="30"/>
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="87">
-        <v>20</v>
-      </c>
-      <c r="W10" s="88"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="140"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -17504,7 +17601,9 @@
       <c r="AA10" s="30"/>
       <c r="AB10" s="30"/>
       <c r="AC10" s="30"/>
-      <c r="AD10" s="29"/>
+      <c r="AD10" s="29" t="s">
+        <v>150</v>
+      </c>
       <c r="AE10" s="30"/>
       <c r="AF10" s="30"/>
       <c r="AG10" s="30"/>
@@ -17516,63 +17615,53 @@
       <c r="AM10" s="31"/>
       <c r="AN10" s="32"/>
     </row>
-    <row r="11" spans="1:41" ht="14.1" customHeight="1">
+    <row r="11" spans="1:40" ht="14.1" customHeight="1">
       <c r="A11" s="32"/>
-      <c r="B11" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="88"/>
-      <c r="X11" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="30"/>
-      <c r="AK11" s="30"/>
-      <c r="AL11" s="30"/>
-      <c r="AM11" s="31"/>
       <c r="AN11" s="32"/>
     </row>
-    <row r="12" spans="1:41" ht="14.1" customHeight="1">
+    <row r="12" spans="1:40" ht="14.1" customHeight="1">
       <c r="A12" s="32"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="59"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="142"/>
+      <c r="W12" s="142"/>
+      <c r="X12" s="32"/>
+      <c r="Y12" s="32"/>
+      <c r="Z12" s="32"/>
+      <c r="AA12" s="32"/>
+      <c r="AB12" s="32"/>
+      <c r="AC12" s="32"/>
+      <c r="AD12" s="32"/>
+      <c r="AE12" s="32"/>
+      <c r="AF12" s="32"/>
+      <c r="AG12" s="32"/>
+      <c r="AH12" s="32"/>
+      <c r="AI12" s="32"/>
+      <c r="AJ12" s="32"/>
+      <c r="AK12" s="32"/>
+      <c r="AL12" s="32"/>
+      <c r="AM12" s="32"/>
       <c r="AN12" s="32"/>
     </row>
-    <row r="13" spans="1:41" ht="14.1" customHeight="1">
+    <row r="13" spans="1:40" ht="14.1" customHeight="1">
       <c r="A13" s="32"/>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
@@ -17582,28 +17671,28 @@
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="59"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="142"/>
-      <c r="W13" s="142"/>
-      <c r="X13" s="32"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="32"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="32"/>
-      <c r="AE13" s="32"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="45"/>
+      <c r="U13" s="45"/>
+      <c r="V13" s="45"/>
+      <c r="W13" s="45"/>
+      <c r="X13" s="45"/>
+      <c r="Y13" s="45"/>
+      <c r="Z13" s="45"/>
+      <c r="AA13" s="45"/>
+      <c r="AB13" s="45"/>
+      <c r="AC13" s="45"/>
+      <c r="AD13" s="45"/>
+      <c r="AE13" s="45"/>
       <c r="AF13" s="32"/>
       <c r="AG13" s="32"/>
       <c r="AH13" s="32"/>
@@ -17614,7 +17703,7 @@
       <c r="AM13" s="32"/>
       <c r="AN13" s="32"/>
     </row>
-    <row r="14" spans="1:41" ht="14.1" customHeight="1">
+    <row r="14" spans="1:40" ht="14.1" customHeight="1">
       <c r="A14" s="32"/>
       <c r="B14" s="32"/>
       <c r="C14" s="32"/>
@@ -17624,28 +17713,28 @@
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
-      <c r="U14" s="45"/>
-      <c r="V14" s="45"/>
-      <c r="W14" s="45"/>
-      <c r="X14" s="45"/>
-      <c r="Y14" s="45"/>
-      <c r="Z14" s="45"/>
-      <c r="AA14" s="45"/>
-      <c r="AB14" s="45"/>
-      <c r="AC14" s="45"/>
-      <c r="AD14" s="45"/>
-      <c r="AE14" s="45"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
+      <c r="Y14" s="32"/>
+      <c r="Z14" s="32"/>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="32"/>
+      <c r="AC14" s="32"/>
+      <c r="AD14" s="32"/>
+      <c r="AE14" s="32"/>
       <c r="AF14" s="32"/>
       <c r="AG14" s="32"/>
       <c r="AH14" s="32"/>
@@ -17656,7 +17745,7 @@
       <c r="AM14" s="32"/>
       <c r="AN14" s="32"/>
     </row>
-    <row r="15" spans="1:41" ht="14.1" customHeight="1">
+    <row r="15" spans="1:40" ht="14.1" customHeight="1">
       <c r="A15" s="32"/>
       <c r="B15" s="32"/>
       <c r="C15" s="32"/>
@@ -17698,140 +17787,138 @@
       <c r="AM15" s="32"/>
       <c r="AN15" s="32"/>
     </row>
-    <row r="16" spans="1:41" ht="14.1" customHeight="1">
+    <row r="16" spans="1:40" ht="14.1" customHeight="1">
       <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="32"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="32"/>
-      <c r="AD16" s="32"/>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="32"/>
-      <c r="AG16" s="32"/>
-      <c r="AH16" s="32"/>
-      <c r="AI16" s="32"/>
-      <c r="AJ16" s="32"/>
-      <c r="AK16" s="32"/>
-      <c r="AL16" s="32"/>
-      <c r="AM16" s="32"/>
+      <c r="B16" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="52"/>
+      <c r="R16" s="52"/>
+      <c r="S16" s="52"/>
+      <c r="T16" s="52"/>
+      <c r="U16" s="52"/>
+      <c r="V16" s="52"/>
+      <c r="W16" s="52"/>
+      <c r="X16" s="52"/>
+      <c r="Y16" s="52"/>
+      <c r="Z16" s="52"/>
+      <c r="AA16" s="52"/>
+      <c r="AB16" s="52"/>
+      <c r="AC16" s="52"/>
+      <c r="AD16" s="52"/>
+      <c r="AE16" s="52"/>
+      <c r="AF16" s="47"/>
+      <c r="AG16" s="47"/>
+      <c r="AH16" s="47"/>
+      <c r="AI16" s="47"/>
+      <c r="AJ16" s="47"/>
+      <c r="AK16" s="47"/>
+      <c r="AL16" s="47"/>
+      <c r="AM16" s="48"/>
       <c r="AN16" s="32"/>
     </row>
     <row r="17" spans="1:40" ht="14.1" customHeight="1">
       <c r="A17" s="32"/>
-      <c r="B17" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="52"/>
-      <c r="U17" s="52"/>
-      <c r="V17" s="52"/>
-      <c r="W17" s="52"/>
-      <c r="X17" s="52"/>
-      <c r="Y17" s="52"/>
-      <c r="Z17" s="52"/>
-      <c r="AA17" s="52"/>
-      <c r="AB17" s="52"/>
-      <c r="AC17" s="52"/>
-      <c r="AD17" s="52"/>
-      <c r="AE17" s="52"/>
-      <c r="AF17" s="47"/>
-      <c r="AG17" s="47"/>
-      <c r="AH17" s="47"/>
-      <c r="AI17" s="47"/>
-      <c r="AJ17" s="47"/>
-      <c r="AK17" s="47"/>
-      <c r="AL17" s="47"/>
-      <c r="AM17" s="48"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="56"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="54"/>
+      <c r="Z17" s="54"/>
+      <c r="AA17" s="54"/>
+      <c r="AB17" s="54"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="54"/>
+      <c r="AF17" s="54"/>
+      <c r="AG17" s="54"/>
+      <c r="AH17" s="54"/>
+      <c r="AI17" s="54"/>
+      <c r="AJ17" s="54"/>
+      <c r="AK17" s="54"/>
+      <c r="AL17" s="54"/>
+      <c r="AM17" s="57"/>
       <c r="AN17" s="32"/>
     </row>
     <row r="18" spans="1:40" ht="14.1" customHeight="1">
       <c r="A18" s="32"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="54"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="54"/>
-      <c r="U18" s="54"/>
-      <c r="V18" s="56"/>
-      <c r="W18" s="56"/>
-      <c r="X18" s="54"/>
-      <c r="Y18" s="54"/>
-      <c r="Z18" s="54"/>
-      <c r="AA18" s="54"/>
-      <c r="AB18" s="54"/>
-      <c r="AC18" s="54"/>
-      <c r="AD18" s="54"/>
-      <c r="AE18" s="54"/>
-      <c r="AF18" s="54"/>
-      <c r="AG18" s="54"/>
-      <c r="AH18" s="54"/>
-      <c r="AI18" s="54"/>
-      <c r="AJ18" s="54"/>
-      <c r="AK18" s="54"/>
-      <c r="AL18" s="54"/>
-      <c r="AM18" s="57"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
+      <c r="W18" s="60"/>
+      <c r="X18" s="60"/>
+      <c r="Y18" s="60"/>
+      <c r="Z18" s="60"/>
+      <c r="AA18" s="60"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="32"/>
+      <c r="AD18" s="32"/>
+      <c r="AE18" s="32"/>
+      <c r="AF18" s="32"/>
+      <c r="AG18" s="32"/>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="32"/>
+      <c r="AJ18" s="32"/>
+      <c r="AK18" s="32"/>
+      <c r="AL18" s="32"/>
+      <c r="AM18" s="61"/>
       <c r="AN18" s="32"/>
     </row>
     <row r="19" spans="1:40" ht="14.1" customHeight="1">
       <c r="A19" s="32"/>
       <c r="B19" s="58"/>
-      <c r="C19" s="32" t="s">
-        <v>175</v>
-      </c>
+      <c r="C19" s="32"/>
       <c r="D19" s="32"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
@@ -17839,22 +17926,22 @@
       <c r="H19" s="32"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
       <c r="N19" s="60"/>
       <c r="O19" s="60"/>
       <c r="P19" s="60"/>
       <c r="Q19" s="60"/>
-      <c r="R19" s="60"/>
+      <c r="R19" s="62"/>
       <c r="S19" s="60"/>
       <c r="T19" s="60"/>
-      <c r="U19" s="60"/>
-      <c r="V19" s="60"/>
-      <c r="W19" s="60"/>
-      <c r="X19" s="60"/>
-      <c r="Y19" s="60"/>
-      <c r="Z19" s="60"/>
+      <c r="U19" s="63"/>
+      <c r="V19" s="63"/>
+      <c r="W19" s="63"/>
+      <c r="X19" s="63"/>
+      <c r="Y19" s="63"/>
+      <c r="Z19" s="63"/>
       <c r="AA19" s="60"/>
       <c r="AB19" s="32"/>
       <c r="AC19" s="32"/>
@@ -17888,15 +17975,15 @@
       <c r="O20" s="60"/>
       <c r="P20" s="60"/>
       <c r="Q20" s="60"/>
-      <c r="R20" s="62"/>
+      <c r="R20" s="60"/>
       <c r="S20" s="60"/>
       <c r="T20" s="60"/>
-      <c r="U20" s="63"/>
-      <c r="V20" s="63"/>
-      <c r="W20" s="63"/>
-      <c r="X20" s="63"/>
-      <c r="Y20" s="63"/>
-      <c r="Z20" s="63"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="60"/>
+      <c r="X20" s="60"/>
+      <c r="Y20" s="60"/>
+      <c r="Z20" s="60"/>
       <c r="AA20" s="60"/>
       <c r="AB20" s="32"/>
       <c r="AC20" s="32"/>
@@ -18082,86 +18169,86 @@
     </row>
     <row r="25" spans="1:40" ht="14.1" customHeight="1">
       <c r="A25" s="32"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="60"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="60"/>
-      <c r="U25" s="60"/>
-      <c r="V25" s="60"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="60"/>
-      <c r="Y25" s="60"/>
-      <c r="Z25" s="60"/>
-      <c r="AA25" s="60"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="32"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="32"/>
-      <c r="AG25" s="32"/>
-      <c r="AH25" s="32"/>
-      <c r="AI25" s="32"/>
-      <c r="AJ25" s="32"/>
-      <c r="AK25" s="32"/>
-      <c r="AL25" s="32"/>
-      <c r="AM25" s="61"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="66"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="65"/>
+      <c r="V25" s="65"/>
+      <c r="W25" s="65"/>
+      <c r="X25" s="65"/>
+      <c r="Y25" s="65"/>
+      <c r="Z25" s="65"/>
+      <c r="AA25" s="65"/>
+      <c r="AB25" s="65"/>
+      <c r="AC25" s="65"/>
+      <c r="AD25" s="65"/>
+      <c r="AE25" s="65"/>
+      <c r="AF25" s="65"/>
+      <c r="AG25" s="65"/>
+      <c r="AH25" s="65"/>
+      <c r="AI25" s="65"/>
+      <c r="AJ25" s="65"/>
+      <c r="AK25" s="65"/>
+      <c r="AL25" s="65"/>
+      <c r="AM25" s="67"/>
       <c r="AN25" s="32"/>
     </row>
     <row r="26" spans="1:40" ht="14.1" customHeight="1">
       <c r="A26" s="32"/>
-      <c r="B26" s="64"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="65"/>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="65"/>
-      <c r="S26" s="65"/>
-      <c r="T26" s="65"/>
-      <c r="U26" s="65"/>
-      <c r="V26" s="65"/>
-      <c r="W26" s="65"/>
-      <c r="X26" s="65"/>
-      <c r="Y26" s="65"/>
-      <c r="Z26" s="65"/>
-      <c r="AA26" s="65"/>
-      <c r="AB26" s="65"/>
-      <c r="AC26" s="65"/>
-      <c r="AD26" s="65"/>
-      <c r="AE26" s="65"/>
-      <c r="AF26" s="65"/>
-      <c r="AG26" s="65"/>
-      <c r="AH26" s="65"/>
-      <c r="AI26" s="65"/>
-      <c r="AJ26" s="65"/>
-      <c r="AK26" s="65"/>
-      <c r="AL26" s="65"/>
-      <c r="AM26" s="67"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="32"/>
       <c r="AN26" s="32"/>
     </row>
     <row r="27" spans="1:40" ht="14.1" customHeight="1">
@@ -18206,58 +18293,15 @@
       <c r="AM27" s="32"/>
       <c r="AN27" s="32"/>
     </row>
-    <row r="28" spans="1:40" ht="14.1" customHeight="1">
-      <c r="A28" s="32"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="32"/>
-      <c r="X28" s="32"/>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="32"/>
-      <c r="AG28" s="32"/>
-      <c r="AH28" s="32"/>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="32"/>
-      <c r="AN28" s="32"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="V13:W13"/>
+  <mergeCells count="7">
+    <mergeCell ref="V12:W12"/>
     <mergeCell ref="B2:X3"/>
+    <mergeCell ref="V7:W7"/>
     <mergeCell ref="V8:W8"/>
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
     <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18317,29 +18361,29 @@
     </row>
     <row r="2" spans="1:41" ht="14.1" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="141" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
-      <c r="U2" s="89"/>
-      <c r="V2" s="89"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="141"/>
+      <c r="S2" s="141"/>
+      <c r="T2" s="141"/>
+      <c r="U2" s="141"/>
+      <c r="V2" s="141"/>
       <c r="W2" s="32"/>
       <c r="X2" s="32"/>
       <c r="Y2" s="32"/>
@@ -18361,27 +18405,27 @@
     </row>
     <row r="3" spans="1:41" ht="14.1" customHeight="1">
       <c r="A3" s="32"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="89"/>
-      <c r="U3" s="89"/>
-      <c r="V3" s="89"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="141"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="141"/>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="141"/>
+      <c r="S3" s="141"/>
+      <c r="T3" s="141"/>
+      <c r="U3" s="141"/>
+      <c r="V3" s="141"/>
       <c r="W3" s="32"/>
       <c r="X3" s="32"/>
       <c r="Y3" s="32"/>
@@ -18525,10 +18569,10 @@
       <c r="S6" s="30"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31"/>
-      <c r="V6" s="87">
+      <c r="V6" s="139">
         <v>20</v>
       </c>
-      <c r="W6" s="88"/>
+      <c r="W6" s="140"/>
       <c r="X6" s="29" t="s">
         <v>76</v>
       </c>
@@ -18580,8 +18624,8 @@
       <c r="S7" s="30"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="88"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="29" t="s">
         <v>76</v>
       </c>
@@ -18632,8 +18676,8 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="88"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="140"/>
       <c r="X8" s="29" t="s">
         <v>25</v>
       </c>
@@ -18684,8 +18728,8 @@
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="88"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="140"/>
       <c r="X9" s="29" t="s">
         <v>25</v>
       </c>
@@ -18736,10 +18780,10 @@
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31"/>
-      <c r="V10" s="87">
+      <c r="V10" s="139">
         <v>20</v>
       </c>
-      <c r="W10" s="88"/>
+      <c r="W10" s="140"/>
       <c r="X10" s="29" t="s">
         <v>25</v>
       </c>
@@ -18788,8 +18832,8 @@
       <c r="S11" s="30"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="88"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="140"/>
       <c r="X11" s="29" t="s">
         <v>25</v>
       </c>
